--- a/output/2024-07-09.xlsx
+++ b/output/2024-07-09.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="F14" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="G14" t="n">
-        <v>280.2</v>
+        <v>253.5</v>
       </c>
       <c r="H14" t="n">
-        <v>50.1</v>
+        <v>50.6</v>
       </c>
       <c r="I14" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>26.64</v>
+        <v>-35.41</v>
       </c>
       <c r="K14" t="n">
-        <v>31.52</v>
+        <v>-92.20999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>41.27</v>
+        <v>98.77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:44:37</t>
+          <t>04:44:57</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="F15" t="n">
-        <v>9.06</v>
+        <v>8.5</v>
       </c>
       <c r="G15" t="n">
-        <v>257.9</v>
+        <v>259.5</v>
       </c>
       <c r="H15" t="n">
-        <v>50.2</v>
+        <v>49.7</v>
       </c>
       <c r="I15" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>-47.88</v>
+        <v>29.96</v>
       </c>
       <c r="K15" t="n">
-        <v>-10.27</v>
+        <v>-26.11</v>
       </c>
       <c r="L15" t="n">
-        <v>48.97</v>
+        <v>39.74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:45:31</t>
+          <t>04:46:45</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="F16" t="n">
-        <v>9.4</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>270</v>
+        <v>276.5</v>
       </c>
       <c r="H16" t="n">
-        <v>49.9</v>
+        <v>51.1</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>48.36</v>
+        <v>26.18</v>
       </c>
       <c r="K16" t="n">
-        <v>-159.37</v>
+        <v>-36.98</v>
       </c>
       <c r="L16" t="n">
-        <v>166.55</v>
+        <v>45.31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:50:12</t>
+          <t>04:52:10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.68</v>
+        <v>2.04</v>
       </c>
       <c r="F17" t="n">
-        <v>8.92</v>
+        <v>9.32</v>
       </c>
       <c r="G17" t="n">
-        <v>277</v>
+        <v>271.9</v>
       </c>
       <c r="H17" t="n">
-        <v>43</v>
+        <v>43.4</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>-142.95</v>
+        <v>43.1</v>
       </c>
       <c r="K17" t="n">
-        <v>17.11</v>
+        <v>-36.98</v>
       </c>
       <c r="L17" t="n">
-        <v>143.97</v>
+        <v>56.79</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:51:33</t>
+          <t>04:53:05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.31</v>
+        <v>1.87</v>
       </c>
       <c r="F18" t="n">
-        <v>9.66</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>263.9</v>
+        <v>263.2</v>
       </c>
       <c r="H18" t="n">
-        <v>53.2</v>
+        <v>51</v>
       </c>
       <c r="I18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>38.86</v>
+        <v>-49.5</v>
       </c>
       <c r="K18" t="n">
-        <v>28.82</v>
+        <v>131.1</v>
       </c>
       <c r="L18" t="n">
-        <v>48.38</v>
+        <v>140.14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:53:34</t>
+          <t>04:55:20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="F19" t="n">
-        <v>9.84</v>
+        <v>8.94</v>
       </c>
       <c r="G19" t="n">
-        <v>270.4</v>
+        <v>262.4</v>
       </c>
       <c r="H19" t="n">
-        <v>45.1</v>
+        <v>51.7</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>112.52</v>
+        <v>32.86</v>
       </c>
       <c r="K19" t="n">
-        <v>57.67</v>
+        <v>-228.29</v>
       </c>
       <c r="L19" t="n">
-        <v>126.43</v>
+        <v>230.64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:58:09</t>
+          <t>05:01:15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="F20" t="n">
-        <v>8.67</v>
+        <v>8.48</v>
       </c>
       <c r="G20" t="n">
-        <v>264.2</v>
+        <v>268.6</v>
       </c>
       <c r="H20" t="n">
-        <v>45.8</v>
+        <v>47.3</v>
       </c>
       <c r="I20" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>30.77</v>
+        <v>-135.79</v>
       </c>
       <c r="K20" t="n">
-        <v>118.13</v>
+        <v>37.21</v>
       </c>
       <c r="L20" t="n">
-        <v>122.07</v>
+        <v>140.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:59:31</t>
+          <t>05:03:07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.37</v>
+        <v>1.14</v>
       </c>
       <c r="F21" t="n">
-        <v>8.85</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>270.5</v>
+        <v>283</v>
       </c>
       <c r="H21" t="n">
-        <v>52.8</v>
+        <v>47.7</v>
       </c>
       <c r="I21" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>197.38</v>
+        <v>99.12</v>
       </c>
       <c r="K21" t="n">
-        <v>142.64</v>
+        <v>3.37</v>
       </c>
       <c r="L21" t="n">
-        <v>243.53</v>
+        <v>99.18000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:00:45</t>
+          <t>05:05:17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.6</v>
+        <v>2.03</v>
       </c>
       <c r="F22" t="n">
-        <v>8.68</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>267</v>
+        <v>269.6</v>
       </c>
       <c r="H22" t="n">
-        <v>54.6</v>
+        <v>50.6</v>
       </c>
       <c r="I22" t="n">
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-66.14</v>
+        <v>119.96</v>
       </c>
       <c r="K22" t="n">
-        <v>122.96</v>
+        <v>-46.59</v>
       </c>
       <c r="L22" t="n">
-        <v>139.62</v>
+        <v>128.68</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:06:59</t>
+          <t>05:10:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.38</v>
+        <v>2.47</v>
       </c>
       <c r="F23" t="n">
-        <v>8.76</v>
+        <v>9.4</v>
       </c>
       <c r="G23" t="n">
-        <v>275.9</v>
+        <v>259.6</v>
       </c>
       <c r="H23" t="n">
         <v>50.6</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>148.97</v>
+        <v>-11.96</v>
       </c>
       <c r="K23" t="n">
-        <v>-66.52</v>
+        <v>-106.97</v>
       </c>
       <c r="L23" t="n">
-        <v>163.14</v>
+        <v>107.63</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:08:09</t>
+          <t>05:12:12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="F24" t="n">
-        <v>8.550000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="G24" t="n">
-        <v>267.1</v>
+        <v>258.3</v>
       </c>
       <c r="H24" t="n">
-        <v>51.6</v>
+        <v>50.8</v>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-320.5</v>
+        <v>52.03</v>
       </c>
       <c r="K24" t="n">
-        <v>108.65</v>
+        <v>-133.78</v>
       </c>
       <c r="L24" t="n">
-        <v>338.42</v>
+        <v>143.54</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:09:12</t>
+          <t>05:14:13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.64</v>
+        <v>2.58</v>
       </c>
       <c r="F25" t="n">
-        <v>9.34</v>
+        <v>9.07</v>
       </c>
       <c r="G25" t="n">
-        <v>275.2</v>
+        <v>265.5</v>
       </c>
       <c r="H25" t="n">
-        <v>46.8</v>
+        <v>45.8</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>-47.03</v>
+        <v>184.08</v>
       </c>
       <c r="K25" t="n">
-        <v>44.71</v>
+        <v>5.71</v>
       </c>
       <c r="L25" t="n">
-        <v>64.89</v>
+        <v>184.17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:13:50</t>
+          <t>05:18:20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.61</v>
+        <v>2.32</v>
       </c>
       <c r="F26" t="n">
-        <v>8.369999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="G26" t="n">
-        <v>260.3</v>
+        <v>270.5</v>
       </c>
       <c r="H26" t="n">
-        <v>51.3</v>
+        <v>48.9</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>-451.98</v>
+        <v>-228.64</v>
       </c>
       <c r="K26" t="n">
-        <v>91.02</v>
+        <v>-173.26</v>
       </c>
       <c r="L26" t="n">
-        <v>461.05</v>
+        <v>286.88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:15:45</t>
+          <t>05:20:13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="F27" t="n">
-        <v>9.369999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="G27" t="n">
-        <v>272.5</v>
+        <v>270.1</v>
       </c>
       <c r="H27" t="n">
-        <v>47.7</v>
+        <v>51.4</v>
       </c>
       <c r="I27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-305.8</v>
+        <v>-97.05</v>
       </c>
       <c r="K27" t="n">
-        <v>28.16</v>
+        <v>62.08</v>
       </c>
       <c r="L27" t="n">
-        <v>307.09</v>
+        <v>115.21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:17:15</t>
+          <t>05:21:19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.51</v>
+        <v>1.81</v>
       </c>
       <c r="F28" t="n">
         <v>9.109999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>280.3</v>
+        <v>255</v>
       </c>
       <c r="H28" t="n">
-        <v>53.3</v>
+        <v>50.8</v>
       </c>
       <c r="I28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>-603.99</v>
+        <v>-67.53</v>
       </c>
       <c r="K28" t="n">
-        <v>-28.14</v>
+        <v>74.08</v>
       </c>
       <c r="L28" t="n">
-        <v>604.64</v>
+        <v>100.25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:27:01</t>
+          <t>05:30:14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="F29" t="n">
-        <v>9.18</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>275.1</v>
+        <v>278.4</v>
       </c>
       <c r="H29" t="n">
-        <v>47.6</v>
+        <v>38.7</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>70.55</v>
+        <v>-36.43</v>
       </c>
       <c r="K29" t="n">
-        <v>-86.19</v>
+        <v>115.23</v>
       </c>
       <c r="L29" t="n">
-        <v>111.38</v>
+        <v>120.85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:28:56</t>
+          <t>05:31:37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.11</v>
+        <v>2.47</v>
       </c>
       <c r="F30" t="n">
-        <v>8.25</v>
+        <v>9.51</v>
       </c>
       <c r="G30" t="n">
-        <v>257.8</v>
+        <v>260.6</v>
       </c>
       <c r="H30" t="n">
-        <v>48.4</v>
+        <v>47.3</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>45.19</v>
+        <v>-77.66</v>
       </c>
       <c r="K30" t="n">
-        <v>31.52</v>
+        <v>49.58</v>
       </c>
       <c r="L30" t="n">
-        <v>55.1</v>
+        <v>92.14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:30:04</t>
+          <t>05:33:50</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="F31" t="n">
-        <v>8.6</v>
+        <v>9.81</v>
       </c>
       <c r="G31" t="n">
-        <v>282.5</v>
+        <v>263.4</v>
       </c>
       <c r="H31" t="n">
-        <v>49</v>
+        <v>46.1</v>
       </c>
       <c r="I31" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>140.83</v>
+        <v>-32.88</v>
       </c>
       <c r="K31" t="n">
-        <v>87.34</v>
+        <v>-15.56</v>
       </c>
       <c r="L31" t="n">
-        <v>165.71</v>
+        <v>36.38</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:33:09</t>
+          <t>05:38:22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="F32" t="n">
-        <v>9.800000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="G32" t="n">
-        <v>254</v>
+        <v>269.3</v>
       </c>
       <c r="H32" t="n">
-        <v>45</v>
+        <v>50.4</v>
       </c>
       <c r="I32" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.01</v>
+        <v>138.13</v>
       </c>
       <c r="K32" t="n">
-        <v>37.88</v>
+        <v>-77.23</v>
       </c>
       <c r="L32" t="n">
-        <v>37.88</v>
+        <v>158.25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:35:27</t>
+          <t>05:39:28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.29</v>
+        <v>1.83</v>
       </c>
       <c r="F33" t="n">
-        <v>9.26</v>
+        <v>9.85</v>
       </c>
       <c r="G33" t="n">
-        <v>278.4</v>
+        <v>263.6</v>
       </c>
       <c r="H33" t="n">
-        <v>54.4</v>
+        <v>54.2</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>115.91</v>
+        <v>-11.27</v>
       </c>
       <c r="K33" t="n">
-        <v>-187.81</v>
+        <v>105.91</v>
       </c>
       <c r="L33" t="n">
-        <v>220.7</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:37:28</t>
+          <t>05:41:56</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.29</v>
+        <v>2.07</v>
       </c>
       <c r="F34" t="n">
-        <v>9.19</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>275.1</v>
+        <v>262.9</v>
       </c>
       <c r="H34" t="n">
-        <v>45.4</v>
+        <v>53.1</v>
       </c>
       <c r="I34" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>87.89</v>
+        <v>55.54</v>
       </c>
       <c r="K34" t="n">
-        <v>-195.61</v>
+        <v>38.37</v>
       </c>
       <c r="L34" t="n">
-        <v>214.45</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:43:39</t>
+          <t>05:46:31</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.26</v>
+        <v>2.49</v>
       </c>
       <c r="F35" t="n">
-        <v>9.619999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="G35" t="n">
-        <v>266.7</v>
+        <v>290.2</v>
       </c>
       <c r="H35" t="n">
-        <v>50.3</v>
+        <v>39.3</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-55.35</v>
+        <v>37.43</v>
       </c>
       <c r="K35" t="n">
-        <v>-35.1</v>
+        <v>-238.71</v>
       </c>
       <c r="L35" t="n">
-        <v>65.54000000000001</v>
+        <v>241.63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:44:40</t>
+          <t>05:47:48</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="F36" t="n">
-        <v>9.35</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>268</v>
+        <v>261.2</v>
       </c>
       <c r="H36" t="n">
-        <v>53.1</v>
+        <v>51.3</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>-141.99</v>
+        <v>-42.79</v>
       </c>
       <c r="K36" t="n">
-        <v>229.9</v>
+        <v>240.78</v>
       </c>
       <c r="L36" t="n">
-        <v>270.21</v>
+        <v>244.56</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:46:58</t>
+          <t>05:50:21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="F37" t="n">
-        <v>9.51</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>265.1</v>
+        <v>257.1</v>
       </c>
       <c r="H37" t="n">
-        <v>48.3</v>
+        <v>49.8</v>
       </c>
       <c r="I37" t="n">
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>-23.13</v>
+        <v>13.31</v>
       </c>
       <c r="K37" t="n">
-        <v>-145.71</v>
+        <v>-122.98</v>
       </c>
       <c r="L37" t="n">
-        <v>147.54</v>
+        <v>123.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:51:41</t>
+          <t>05:53:45</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="F38" t="n">
-        <v>9.470000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="G38" t="n">
-        <v>265.4</v>
+        <v>269.8</v>
       </c>
       <c r="H38" t="n">
-        <v>47</v>
+        <v>48.2</v>
       </c>
       <c r="I38" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>7.86</v>
+        <v>113.48</v>
       </c>
       <c r="K38" t="n">
-        <v>-86.41</v>
+        <v>-283.81</v>
       </c>
       <c r="L38" t="n">
-        <v>86.77</v>
+        <v>305.65</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:53:36</t>
+          <t>05:56:05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.61</v>
+        <v>1.68</v>
       </c>
       <c r="F39" t="n">
-        <v>9.19</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>273.6</v>
+        <v>280.3</v>
       </c>
       <c r="H39" t="n">
-        <v>48</v>
+        <v>52.3</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.33</v>
+        <v>-189.8</v>
       </c>
       <c r="K39" t="n">
-        <v>476.14</v>
+        <v>52.33</v>
       </c>
       <c r="L39" t="n">
-        <v>476.15</v>
+        <v>196.88</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:55:25</t>
+          <t>05:58:19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.93</v>
+        <v>3.07</v>
       </c>
       <c r="F40" t="n">
-        <v>9.26</v>
+        <v>8.56</v>
       </c>
       <c r="G40" t="n">
-        <v>262.6</v>
+        <v>277.9</v>
       </c>
       <c r="H40" t="n">
-        <v>51</v>
+        <v>48.2</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J40" t="n">
-        <v>135.27</v>
+        <v>-112.84</v>
       </c>
       <c r="K40" t="n">
-        <v>36.47</v>
+        <v>167.97</v>
       </c>
       <c r="L40" t="n">
-        <v>140.1</v>
+        <v>202.35</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:59:59</t>
+          <t>06:03:53</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.67</v>
+        <v>2.47</v>
       </c>
       <c r="F41" t="n">
-        <v>8.91</v>
+        <v>8.92</v>
       </c>
       <c r="G41" t="n">
-        <v>275</v>
+        <v>261.6</v>
       </c>
       <c r="H41" t="n">
-        <v>48.9</v>
+        <v>52.2</v>
       </c>
       <c r="I41" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-100.42</v>
+        <v>-67.06999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>157.53</v>
+        <v>391.22</v>
       </c>
       <c r="L41" t="n">
-        <v>186.82</v>
+        <v>396.93</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:01:23</t>
+          <t>06:05:35</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.14</v>
+        <v>2.42</v>
       </c>
       <c r="F42" t="n">
-        <v>9.390000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>279.6</v>
+        <v>250.9</v>
       </c>
       <c r="H42" t="n">
-        <v>47.6</v>
+        <v>51.1</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J42" t="n">
-        <v>207.43</v>
+        <v>277.28</v>
       </c>
       <c r="K42" t="n">
-        <v>132.86</v>
+        <v>44.46</v>
       </c>
       <c r="L42" t="n">
-        <v>246.34</v>
+        <v>280.82</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:03:43</t>
+          <t>06:07:42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.39</v>
+        <v>2.65</v>
       </c>
       <c r="F43" t="n">
-        <v>8.94</v>
+        <v>9.02</v>
       </c>
       <c r="G43" t="n">
-        <v>277.4</v>
+        <v>270.6</v>
       </c>
       <c r="H43" t="n">
-        <v>51.1</v>
+        <v>48.1</v>
       </c>
       <c r="I43" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-459.14</v>
+        <v>-390.81</v>
       </c>
       <c r="K43" t="n">
-        <v>182.66</v>
+        <v>100.12</v>
       </c>
       <c r="L43" t="n">
-        <v>494.14</v>
+        <v>403.43</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:12:54</t>
+          <t>06:18:03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.82</v>
+        <v>2.46</v>
       </c>
       <c r="F44" t="n">
-        <v>9.470000000000001</v>
+        <v>9.52</v>
       </c>
       <c r="G44" t="n">
-        <v>282.6</v>
+        <v>266.7</v>
       </c>
       <c r="H44" t="n">
-        <v>50.8</v>
+        <v>46.5</v>
       </c>
       <c r="I44" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.73</v>
+        <v>-99.12</v>
       </c>
       <c r="K44" t="n">
-        <v>61.83</v>
+        <v>104.81</v>
       </c>
       <c r="L44" t="n">
-        <v>61.94</v>
+        <v>144.26</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:15:30</t>
+          <t>06:19:30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.96</v>
+        <v>2.36</v>
       </c>
       <c r="F45" t="n">
-        <v>8.890000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="G45" t="n">
-        <v>281.7</v>
+        <v>276.2</v>
       </c>
       <c r="H45" t="n">
-        <v>47.9</v>
+        <v>57.4</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J45" t="n">
-        <v>-102.22</v>
+        <v>-49</v>
       </c>
       <c r="K45" t="n">
-        <v>-80.42</v>
+        <v>-38.55</v>
       </c>
       <c r="L45" t="n">
-        <v>130.06</v>
+        <v>62.35</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:17:59</t>
+          <t>06:20:18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="F46" t="n">
-        <v>9.609999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="G46" t="n">
-        <v>268.3</v>
+        <v>258.5</v>
       </c>
       <c r="H46" t="n">
-        <v>52.5</v>
+        <v>48.4</v>
       </c>
       <c r="I46" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.05</v>
+        <v>31.23</v>
       </c>
       <c r="K46" t="n">
-        <v>-33.15</v>
+        <v>-84.31</v>
       </c>
       <c r="L46" t="n">
-        <v>34.94</v>
+        <v>89.91</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:21:49</t>
+          <t>06:24:13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2014,31 +2014,31 @@
         <v>2.39</v>
       </c>
       <c r="F47" t="n">
-        <v>9.25</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>265.7</v>
+        <v>288.5</v>
       </c>
       <c r="H47" t="n">
-        <v>52.7</v>
+        <v>37.6</v>
       </c>
       <c r="I47" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>34.39</v>
+        <v>-115.53</v>
       </c>
       <c r="K47" t="n">
-        <v>-20.15</v>
+        <v>-72.69</v>
       </c>
       <c r="L47" t="n">
-        <v>39.86</v>
+        <v>136.49</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:23:44</t>
+          <t>06:25:12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="F48" t="n">
-        <v>8.6</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>273.1</v>
+        <v>276.5</v>
       </c>
       <c r="H48" t="n">
-        <v>51.8</v>
+        <v>48.3</v>
       </c>
       <c r="I48" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>-20.73</v>
       </c>
       <c r="K48" t="n">
-        <v>55.07</v>
+        <v>-41.36</v>
       </c>
       <c r="L48" t="n">
-        <v>55.16</v>
+        <v>46.26</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:24:56</t>
+          <t>06:27:06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.82</v>
+        <v>2.08</v>
       </c>
       <c r="F49" t="n">
-        <v>8.25</v>
+        <v>8.83</v>
       </c>
       <c r="G49" t="n">
-        <v>261.2</v>
+        <v>258.8</v>
       </c>
       <c r="H49" t="n">
-        <v>45.2</v>
+        <v>51.1</v>
       </c>
       <c r="I49" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>54.69</v>
+        <v>-93.87</v>
       </c>
       <c r="K49" t="n">
-        <v>-7.16</v>
+        <v>16.47</v>
       </c>
       <c r="L49" t="n">
-        <v>55.16</v>
+        <v>95.31</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:29:31</t>
+          <t>06:31:15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="F50" t="n">
-        <v>9.9</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>259.5</v>
+        <v>270.4</v>
       </c>
       <c r="H50" t="n">
-        <v>48</v>
+        <v>43.8</v>
       </c>
       <c r="I50" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J50" t="n">
-        <v>31.04</v>
+        <v>70.63</v>
       </c>
       <c r="K50" t="n">
-        <v>-10.96</v>
+        <v>119.45</v>
       </c>
       <c r="L50" t="n">
-        <v>32.92</v>
+        <v>138.76</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:31:16</t>
+          <t>06:32:30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="F51" t="n">
-        <v>9.98</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>266.2</v>
+        <v>276.9</v>
       </c>
       <c r="H51" t="n">
-        <v>46.5</v>
+        <v>57</v>
       </c>
       <c r="I51" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-80.65000000000001</v>
+        <v>67.94</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.92</v>
+        <v>-167.35</v>
       </c>
       <c r="L51" t="n">
-        <v>80.8</v>
+        <v>180.61</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:32:35</t>
+          <t>06:33:56</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="F52" t="n">
-        <v>8.1</v>
+        <v>8.81</v>
       </c>
       <c r="G52" t="n">
-        <v>260.7</v>
+        <v>265.4</v>
       </c>
       <c r="H52" t="n">
-        <v>50.1</v>
+        <v>46.4</v>
       </c>
       <c r="I52" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J52" t="n">
-        <v>263.04</v>
+        <v>114.85</v>
       </c>
       <c r="K52" t="n">
-        <v>-47.73</v>
+        <v>32.74</v>
       </c>
       <c r="L52" t="n">
-        <v>267.34</v>
+        <v>119.43</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:36:42</t>
+          <t>06:37:42</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.58</v>
+        <v>2.26</v>
       </c>
       <c r="F53" t="n">
-        <v>8.99</v>
+        <v>8.84</v>
       </c>
       <c r="G53" t="n">
-        <v>267.2</v>
+        <v>261.4</v>
       </c>
       <c r="H53" t="n">
-        <v>49.7</v>
+        <v>43</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J53" t="n">
-        <v>-108.2</v>
+        <v>146.09</v>
       </c>
       <c r="K53" t="n">
-        <v>63.19</v>
+        <v>-28.24</v>
       </c>
       <c r="L53" t="n">
-        <v>125.3</v>
+        <v>148.79</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:39:12</t>
+          <t>06:40:09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="F54" t="n">
-        <v>9.949999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>263.9</v>
+        <v>266.9</v>
       </c>
       <c r="H54" t="n">
-        <v>45.2</v>
+        <v>48.2</v>
       </c>
       <c r="I54" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>-327.81</v>
+        <v>7.13</v>
       </c>
       <c r="K54" t="n">
-        <v>249.31</v>
+        <v>-347.83</v>
       </c>
       <c r="L54" t="n">
-        <v>411.84</v>
+        <v>347.9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:40:14</t>
+          <t>06:40:56</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.55</v>
+        <v>2.02</v>
       </c>
       <c r="F55" t="n">
-        <v>9.67</v>
+        <v>8.9</v>
       </c>
       <c r="G55" t="n">
-        <v>274.2</v>
+        <v>271.3</v>
       </c>
       <c r="H55" t="n">
-        <v>42.8</v>
+        <v>54.1</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J55" t="n">
-        <v>-164.6</v>
+        <v>287.36</v>
       </c>
       <c r="K55" t="n">
-        <v>443.64</v>
+        <v>222.95</v>
       </c>
       <c r="L55" t="n">
-        <v>473.19</v>
+        <v>363.71</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:43:17</t>
+          <t>06:45:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="F56" t="n">
-        <v>9.65</v>
+        <v>9.17</v>
       </c>
       <c r="G56" t="n">
-        <v>264.2</v>
+        <v>261.9</v>
       </c>
       <c r="H56" t="n">
-        <v>48.9</v>
+        <v>49.2</v>
       </c>
       <c r="I56" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>-106.51</v>
+        <v>-90.51000000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.05</v>
+        <v>-377.95</v>
       </c>
       <c r="L56" t="n">
-        <v>106.51</v>
+        <v>388.63</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:45:43</t>
+          <t>06:46:44</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.17</v>
+        <v>1.89</v>
       </c>
       <c r="F57" t="n">
-        <v>9.82</v>
+        <v>9.48</v>
       </c>
       <c r="G57" t="n">
-        <v>259.9</v>
+        <v>254.3</v>
       </c>
       <c r="H57" t="n">
-        <v>48.3</v>
+        <v>49.7</v>
       </c>
       <c r="I57" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-126.43</v>
+        <v>-15.86</v>
       </c>
       <c r="K57" t="n">
-        <v>-58.86</v>
+        <v>-133.19</v>
       </c>
       <c r="L57" t="n">
-        <v>139.46</v>
+        <v>134.13</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:47:34</t>
+          <t>06:49:10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.23</v>
+        <v>2.8</v>
       </c>
       <c r="F58" t="n">
-        <v>8.970000000000001</v>
+        <v>9.77</v>
       </c>
       <c r="G58" t="n">
-        <v>261.2</v>
+        <v>271.8</v>
       </c>
       <c r="H58" t="n">
-        <v>50</v>
+        <v>56.5</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J58" t="n">
-        <v>-155.62</v>
+        <v>61.74</v>
       </c>
       <c r="K58" t="n">
-        <v>-227.63</v>
+        <v>363.51</v>
       </c>
       <c r="L58" t="n">
-        <v>275.74</v>
+        <v>368.71</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:56:57</t>
+          <t>06:57:32</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.39</v>
+        <v>2.58</v>
       </c>
       <c r="F59" t="n">
-        <v>9.44</v>
+        <v>9.74</v>
       </c>
       <c r="G59" t="n">
-        <v>266.1</v>
+        <v>276.4</v>
       </c>
       <c r="H59" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="I59" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>0.9399999999999999</v>
+        <v>-72.34</v>
       </c>
       <c r="K59" t="n">
-        <v>13.38</v>
+        <v>-85.56</v>
       </c>
       <c r="L59" t="n">
-        <v>13.41</v>
+        <v>112.05</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:57:58</t>
+          <t>06:58:58</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="F60" t="n">
-        <v>9.800000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="G60" t="n">
-        <v>251.5</v>
+        <v>271.7</v>
       </c>
       <c r="H60" t="n">
-        <v>48.8</v>
+        <v>52</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>73.73</v>
+        <v>-117.42</v>
       </c>
       <c r="K60" t="n">
-        <v>-87.56999999999999</v>
+        <v>131.6</v>
       </c>
       <c r="L60" t="n">
-        <v>114.48</v>
+        <v>176.37</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:59:52</t>
+          <t>07:01:24</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.59</v>
+        <v>2.41</v>
       </c>
       <c r="F61" t="n">
-        <v>9.130000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="G61" t="n">
-        <v>274.6</v>
+        <v>263.9</v>
       </c>
       <c r="H61" t="n">
-        <v>47.9</v>
+        <v>52.6</v>
       </c>
       <c r="I61" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>34.49</v>
+        <v>209.66</v>
       </c>
       <c r="K61" t="n">
-        <v>26.67</v>
+        <v>-80.91</v>
       </c>
       <c r="L61" t="n">
-        <v>43.6</v>
+        <v>224.73</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:04:00</t>
+          <t>07:07:39</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.39</v>
+        <v>1.96</v>
       </c>
       <c r="F62" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="G62" t="n">
-        <v>275.9</v>
+        <v>259.4</v>
       </c>
       <c r="H62" t="n">
-        <v>38.4</v>
+        <v>42.1</v>
       </c>
       <c r="I62" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>63.92</v>
+        <v>-44.93</v>
       </c>
       <c r="K62" t="n">
-        <v>-188.25</v>
+        <v>1.52</v>
       </c>
       <c r="L62" t="n">
-        <v>198.81</v>
+        <v>44.96</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:05:47</t>
+          <t>07:09:16</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.51</v>
+        <v>3.21</v>
       </c>
       <c r="F63" t="n">
-        <v>9.09</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>272.1</v>
+        <v>261.5</v>
       </c>
       <c r="H63" t="n">
-        <v>51.1</v>
+        <v>46.3</v>
       </c>
       <c r="I63" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-58.62</v>
+        <v>-128.65</v>
       </c>
       <c r="K63" t="n">
-        <v>-148.22</v>
+        <v>-158.95</v>
       </c>
       <c r="L63" t="n">
-        <v>159.39</v>
+        <v>204.49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:06:59</t>
+          <t>07:11:32</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="F64" t="n">
-        <v>9</v>
+        <v>9.24</v>
       </c>
       <c r="G64" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H64" t="n">
-        <v>50.8</v>
+        <v>44.6</v>
       </c>
       <c r="I64" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-6.16</v>
+        <v>-51.12</v>
       </c>
       <c r="K64" t="n">
-        <v>-118.59</v>
+        <v>121.2</v>
       </c>
       <c r="L64" t="n">
-        <v>118.75</v>
+        <v>131.54</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:11:17</t>
+          <t>07:15:36</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="F65" t="n">
-        <v>9.52</v>
+        <v>9.73</v>
       </c>
       <c r="G65" t="n">
-        <v>269.9</v>
+        <v>280</v>
       </c>
       <c r="H65" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
       <c r="I65" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>78.04000000000001</v>
+        <v>198.05</v>
       </c>
       <c r="K65" t="n">
-        <v>308.56</v>
+        <v>-112.75</v>
       </c>
       <c r="L65" t="n">
-        <v>318.28</v>
+        <v>227.9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:12:53</t>
+          <t>07:17:46</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="F66" t="n">
-        <v>9.01</v>
+        <v>9.42</v>
       </c>
       <c r="G66" t="n">
         <v>259.6</v>
       </c>
       <c r="H66" t="n">
-        <v>47.7</v>
+        <v>56.4</v>
       </c>
       <c r="I66" t="n">
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>47.65</v>
+        <v>87.36</v>
       </c>
       <c r="K66" t="n">
-        <v>213.88</v>
+        <v>-43.97</v>
       </c>
       <c r="L66" t="n">
-        <v>219.12</v>
+        <v>97.81</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:14:28</t>
+          <t>07:19:14</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="F67" t="n">
-        <v>9.16</v>
+        <v>9.98</v>
       </c>
       <c r="G67" t="n">
-        <v>267</v>
+        <v>268.5</v>
       </c>
       <c r="H67" t="n">
-        <v>50.1</v>
+        <v>49.5</v>
       </c>
       <c r="I67" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J67" t="n">
-        <v>-105.9</v>
+        <v>57.18</v>
       </c>
       <c r="K67" t="n">
-        <v>-116.61</v>
+        <v>20.08</v>
       </c>
       <c r="L67" t="n">
-        <v>157.52</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:18:27</t>
+          <t>07:23:58</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="F68" t="n">
-        <v>9.699999999999999</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>258.2</v>
+        <v>262.8</v>
       </c>
       <c r="H68" t="n">
-        <v>47.4</v>
+        <v>49</v>
       </c>
       <c r="I68" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-58.62</v>
+        <v>-339.48</v>
       </c>
       <c r="K68" t="n">
-        <v>48.1</v>
+        <v>-150.73</v>
       </c>
       <c r="L68" t="n">
-        <v>75.83</v>
+        <v>371.44</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:19:59</t>
+          <t>07:25:09</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.69</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
-        <v>8.390000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>256.3</v>
+        <v>276.7</v>
       </c>
       <c r="H69" t="n">
-        <v>49.7</v>
+        <v>48.4</v>
       </c>
       <c r="I69" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>-48.4</v>
+        <v>-157.72</v>
       </c>
       <c r="K69" t="n">
-        <v>-140.68</v>
+        <v>145.81</v>
       </c>
       <c r="L69" t="n">
-        <v>148.78</v>
+        <v>214.79</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:21:01</t>
+          <t>07:26:46</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.18</v>
+        <v>2.78</v>
       </c>
       <c r="F70" t="n">
-        <v>10.26</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>265.5</v>
+        <v>257.2</v>
       </c>
       <c r="H70" t="n">
-        <v>49.6</v>
+        <v>50.4</v>
       </c>
       <c r="I70" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>-29.31</v>
+        <v>52.45</v>
       </c>
       <c r="K70" t="n">
-        <v>21.14</v>
+        <v>-145.25</v>
       </c>
       <c r="L70" t="n">
-        <v>36.14</v>
+        <v>154.43</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:26:21</t>
+          <t>07:30:23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.61</v>
+        <v>2.32</v>
       </c>
       <c r="F71" t="n">
-        <v>9.449999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="G71" t="n">
-        <v>258.7</v>
+        <v>269.5</v>
       </c>
       <c r="H71" t="n">
-        <v>47.6</v>
+        <v>51.3</v>
       </c>
       <c r="I71" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>-47.11</v>
+        <v>-270.88</v>
       </c>
       <c r="K71" t="n">
-        <v>315.47</v>
+        <v>-138.91</v>
       </c>
       <c r="L71" t="n">
-        <v>318.96</v>
+        <v>304.42</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:28:16</t>
+          <t>07:31:48</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.67</v>
+        <v>3.14</v>
       </c>
       <c r="F72" t="n">
-        <v>9.35</v>
+        <v>9.25</v>
       </c>
       <c r="G72" t="n">
-        <v>278.6</v>
+        <v>274</v>
       </c>
       <c r="H72" t="n">
-        <v>51.3</v>
+        <v>56.5</v>
       </c>
       <c r="I72" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>373.81</v>
+        <v>22.87</v>
       </c>
       <c r="K72" t="n">
-        <v>266.2</v>
+        <v>-270.83</v>
       </c>
       <c r="L72" t="n">
-        <v>458.9</v>
+        <v>271.79</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:30:37</t>
+          <t>07:34:17</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.29</v>
+        <v>2.86</v>
       </c>
       <c r="F73" t="n">
-        <v>9.5</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>281.1</v>
+        <v>267.2</v>
       </c>
       <c r="H73" t="n">
-        <v>46</v>
+        <v>45.2</v>
       </c>
       <c r="I73" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-150.51</v>
+        <v>-64.23999999999999</v>
       </c>
       <c r="K73" t="n">
-        <v>-50.16</v>
+        <v>240.7</v>
       </c>
       <c r="L73" t="n">
-        <v>158.65</v>
+        <v>249.12</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:41:17</t>
+          <t>07:42:28</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.72</v>
+        <v>2.2</v>
       </c>
       <c r="F74" t="n">
-        <v>8.640000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="G74" t="n">
-        <v>259.8</v>
+        <v>270</v>
       </c>
       <c r="H74" t="n">
-        <v>57.9</v>
+        <v>52.7</v>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>29.56</v>
+        <v>74.84</v>
       </c>
       <c r="K74" t="n">
-        <v>26.38</v>
+        <v>-81.77</v>
       </c>
       <c r="L74" t="n">
-        <v>39.62</v>
+        <v>110.85</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:42:34</t>
+          <t>07:44:27</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="F75" t="n">
-        <v>9.94</v>
+        <v>8.76</v>
       </c>
       <c r="G75" t="n">
-        <v>281.8</v>
+        <v>278.1</v>
       </c>
       <c r="H75" t="n">
-        <v>45.3</v>
+        <v>42.9</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J75" t="n">
-        <v>24</v>
+        <v>-46.04</v>
       </c>
       <c r="K75" t="n">
-        <v>37.97</v>
+        <v>-21.42</v>
       </c>
       <c r="L75" t="n">
-        <v>44.92</v>
+        <v>50.78</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:43:13</t>
+          <t>07:46:09</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.65</v>
+        <v>2.14</v>
       </c>
       <c r="F76" t="n">
-        <v>9.119999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G76" t="n">
-        <v>276.4</v>
+        <v>275.2</v>
       </c>
       <c r="H76" t="n">
-        <v>43.3</v>
+        <v>49.1</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>7.63</v>
+        <v>-120.62</v>
       </c>
       <c r="K76" t="n">
-        <v>26.4</v>
+        <v>-99.47</v>
       </c>
       <c r="L76" t="n">
-        <v>27.48</v>
+        <v>156.35</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:48:23</t>
+          <t>07:52:03</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.37</v>
+        <v>2.92</v>
       </c>
       <c r="F77" t="n">
-        <v>9.76</v>
+        <v>9.32</v>
       </c>
       <c r="G77" t="n">
-        <v>269.6</v>
+        <v>271.9</v>
       </c>
       <c r="H77" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="I77" t="n">
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-59.57</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-30.43</v>
+        <v>-116.05</v>
       </c>
       <c r="L77" t="n">
-        <v>66.89</v>
+        <v>134.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:50:42</t>
+          <t>07:53:17</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="F78" t="n">
-        <v>9.220000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="G78" t="n">
-        <v>263.9</v>
+        <v>281.4</v>
       </c>
       <c r="H78" t="n">
-        <v>41.4</v>
+        <v>54.4</v>
       </c>
       <c r="I78" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-8.73</v>
+        <v>179.82</v>
       </c>
       <c r="K78" t="n">
-        <v>-89.06999999999999</v>
+        <v>-104.52</v>
       </c>
       <c r="L78" t="n">
-        <v>89.48999999999999</v>
+        <v>207.99</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:51:31</t>
+          <t>07:54:47</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.28</v>
+        <v>2.51</v>
       </c>
       <c r="F79" t="n">
-        <v>9.529999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="G79" t="n">
-        <v>270.5</v>
+        <v>269.3</v>
       </c>
       <c r="H79" t="n">
-        <v>51.5</v>
+        <v>51.8</v>
       </c>
       <c r="I79" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>11.42</v>
+        <v>-21.11</v>
       </c>
       <c r="K79" t="n">
-        <v>39.53</v>
+        <v>-79.28</v>
       </c>
       <c r="L79" t="n">
-        <v>41.15</v>
+        <v>82.04000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:56:03</t>
+          <t>07:57:54</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="F80" t="n">
-        <v>9.23</v>
+        <v>8.35</v>
       </c>
       <c r="G80" t="n">
-        <v>273.3</v>
+        <v>265.2</v>
       </c>
       <c r="H80" t="n">
-        <v>46.3</v>
+        <v>56.1</v>
       </c>
       <c r="I80" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>178.56</v>
+        <v>68.33</v>
       </c>
       <c r="K80" t="n">
-        <v>-39.56</v>
+        <v>-23.72</v>
       </c>
       <c r="L80" t="n">
-        <v>182.89</v>
+        <v>72.33</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:58:11</t>
+          <t>08:00:01</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3442,31 +3442,31 @@
         <v>2.29</v>
       </c>
       <c r="F81" t="n">
-        <v>9.67</v>
+        <v>9.33</v>
       </c>
       <c r="G81" t="n">
-        <v>259.6</v>
+        <v>253.4</v>
       </c>
       <c r="H81" t="n">
-        <v>52.2</v>
+        <v>48.9</v>
       </c>
       <c r="I81" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-108.71</v>
+        <v>14.69</v>
       </c>
       <c r="K81" t="n">
-        <v>-177.74</v>
+        <v>-131.66</v>
       </c>
       <c r="L81" t="n">
-        <v>208.35</v>
+        <v>132.47</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:59:34</t>
+          <t>08:02:14</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.65</v>
+        <v>2.13</v>
       </c>
       <c r="F82" t="n">
-        <v>9.42</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>269.6</v>
+        <v>266.7</v>
       </c>
       <c r="H82" t="n">
-        <v>51.2</v>
+        <v>54.8</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-208.07</v>
+        <v>13.64</v>
       </c>
       <c r="K82" t="n">
-        <v>63.22</v>
+        <v>-69.5</v>
       </c>
       <c r="L82" t="n">
-        <v>217.46</v>
+        <v>70.81999999999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:04:27</t>
+          <t>08:06:48</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="F83" t="n">
-        <v>9.539999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>252.5</v>
+        <v>271.1</v>
       </c>
       <c r="H83" t="n">
-        <v>51.8</v>
+        <v>49.7</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-209.48</v>
+        <v>-114.17</v>
       </c>
       <c r="K83" t="n">
-        <v>78.02</v>
+        <v>-42.64</v>
       </c>
       <c r="L83" t="n">
-        <v>223.53</v>
+        <v>121.88</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:05:37</t>
+          <t>08:09:21</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="F84" t="n">
-        <v>9.35</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G84" t="n">
-        <v>260.6</v>
+        <v>265.6</v>
       </c>
       <c r="H84" t="n">
-        <v>52.9</v>
+        <v>43.8</v>
       </c>
       <c r="I84" t="n">
         <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>-97.47</v>
+        <v>356.83</v>
       </c>
       <c r="K84" t="n">
-        <v>-306.04</v>
+        <v>-170.73</v>
       </c>
       <c r="L84" t="n">
-        <v>321.18</v>
+        <v>395.57</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:07:49</t>
+          <t>08:11:03</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.29</v>
+        <v>2.81</v>
       </c>
       <c r="F85" t="n">
-        <v>9.06</v>
+        <v>9.42</v>
       </c>
       <c r="G85" t="n">
-        <v>273.2</v>
+        <v>257.2</v>
       </c>
       <c r="H85" t="n">
-        <v>48.9</v>
+        <v>51.9</v>
       </c>
       <c r="I85" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J85" t="n">
-        <v>177.95</v>
+        <v>-31.93</v>
       </c>
       <c r="K85" t="n">
-        <v>-43.56</v>
+        <v>-70.88</v>
       </c>
       <c r="L85" t="n">
-        <v>183.21</v>
+        <v>77.73999999999999</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:12:49</t>
+          <t>08:14:43</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="F86" t="n">
-        <v>8.66</v>
+        <v>9.07</v>
       </c>
       <c r="G86" t="n">
-        <v>276.1</v>
+        <v>259.9</v>
       </c>
       <c r="H86" t="n">
-        <v>51.1</v>
+        <v>49.5</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>408.09</v>
+        <v>-190.25</v>
       </c>
       <c r="K86" t="n">
-        <v>-432.71</v>
+        <v>-4.19</v>
       </c>
       <c r="L86" t="n">
-        <v>594.79</v>
+        <v>190.3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:14:38</t>
+          <t>08:15:54</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="F87" t="n">
-        <v>8.529999999999999</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>252.1</v>
+        <v>247.6</v>
       </c>
       <c r="H87" t="n">
-        <v>50</v>
+        <v>44.3</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>34.98</v>
+        <v>29.47</v>
       </c>
       <c r="K87" t="n">
-        <v>-126.17</v>
+        <v>198.51</v>
       </c>
       <c r="L87" t="n">
-        <v>130.93</v>
+        <v>200.68</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:16:37</t>
+          <t>08:17:52</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="F88" t="n">
-        <v>9.140000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="G88" t="n">
-        <v>274.7</v>
+        <v>264</v>
       </c>
       <c r="H88" t="n">
-        <v>53.5</v>
+        <v>47.7</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>-196.73</v>
+        <v>-64.08</v>
       </c>
       <c r="K88" t="n">
-        <v>517.17</v>
+        <v>398.68</v>
       </c>
       <c r="L88" t="n">
-        <v>553.3200000000001</v>
+        <v>403.79</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-09.xlsx
+++ b/output/2024-07-09.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-35.41</v>
+        <v>-22.46</v>
       </c>
       <c r="K14" t="n">
-        <v>-92.20999999999999</v>
+        <v>-58.5</v>
       </c>
       <c r="L14" t="n">
-        <v>98.77</v>
+        <v>62.66</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>29.96</v>
+        <v>35.4</v>
       </c>
       <c r="K15" t="n">
-        <v>-26.11</v>
+        <v>-30.85</v>
       </c>
       <c r="L15" t="n">
-        <v>39.74</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>26.18</v>
+        <v>21.45</v>
       </c>
       <c r="K16" t="n">
-        <v>-36.98</v>
+        <v>-30.3</v>
       </c>
       <c r="L16" t="n">
-        <v>45.31</v>
+        <v>37.12</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>43.1</v>
+        <v>43.7</v>
       </c>
       <c r="K17" t="n">
-        <v>-36.98</v>
+        <v>-37.49</v>
       </c>
       <c r="L17" t="n">
-        <v>56.79</v>
+        <v>57.58</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-49.5</v>
+        <v>-37.88</v>
       </c>
       <c r="K18" t="n">
-        <v>131.1</v>
+        <v>100.32</v>
       </c>
       <c r="L18" t="n">
-        <v>140.14</v>
+        <v>107.23</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>32.86</v>
+        <v>22.25</v>
       </c>
       <c r="K19" t="n">
-        <v>-228.29</v>
+        <v>-154.55</v>
       </c>
       <c r="L19" t="n">
-        <v>230.64</v>
+        <v>156.14</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-135.79</v>
+        <v>-117.09</v>
       </c>
       <c r="K20" t="n">
-        <v>37.21</v>
+        <v>32.08</v>
       </c>
       <c r="L20" t="n">
-        <v>140.8</v>
+        <v>121.41</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>99.12</v>
+        <v>113.92</v>
       </c>
       <c r="K21" t="n">
-        <v>3.37</v>
+        <v>3.88</v>
       </c>
       <c r="L21" t="n">
-        <v>99.18000000000001</v>
+        <v>113.99</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>119.96</v>
+        <v>112.1</v>
       </c>
       <c r="K22" t="n">
-        <v>-46.59</v>
+        <v>-43.54</v>
       </c>
       <c r="L22" t="n">
-        <v>128.68</v>
+        <v>120.26</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>-11.96</v>
+        <v>-14.67</v>
       </c>
       <c r="K23" t="n">
-        <v>-106.97</v>
+        <v>-131.12</v>
       </c>
       <c r="L23" t="n">
-        <v>107.63</v>
+        <v>131.94</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>52.03</v>
+        <v>59.32</v>
       </c>
       <c r="K24" t="n">
-        <v>-133.78</v>
+        <v>-152.52</v>
       </c>
       <c r="L24" t="n">
-        <v>143.54</v>
+        <v>163.65</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>184.08</v>
+        <v>200.69</v>
       </c>
       <c r="K25" t="n">
-        <v>5.71</v>
+        <v>6.23</v>
       </c>
       <c r="L25" t="n">
-        <v>184.17</v>
+        <v>200.79</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>-228.64</v>
+        <v>-221.64</v>
       </c>
       <c r="K26" t="n">
-        <v>-173.26</v>
+        <v>-167.96</v>
       </c>
       <c r="L26" t="n">
-        <v>286.88</v>
+        <v>278.09</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-97.05</v>
+        <v>-162.23</v>
       </c>
       <c r="K27" t="n">
-        <v>62.08</v>
+        <v>103.77</v>
       </c>
       <c r="L27" t="n">
-        <v>115.21</v>
+        <v>192.58</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>-67.53</v>
+        <v>-116.99</v>
       </c>
       <c r="K28" t="n">
-        <v>74.08</v>
+        <v>128.34</v>
       </c>
       <c r="L28" t="n">
-        <v>100.25</v>
+        <v>173.66</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>-36.43</v>
+        <v>-27.72</v>
       </c>
       <c r="K29" t="n">
-        <v>115.23</v>
+        <v>87.66</v>
       </c>
       <c r="L29" t="n">
-        <v>120.85</v>
+        <v>91.93000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-77.66</v>
+        <v>-66.65000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>49.58</v>
+        <v>42.55</v>
       </c>
       <c r="L30" t="n">
-        <v>92.14</v>
+        <v>79.08</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-32.88</v>
+        <v>-37.4</v>
       </c>
       <c r="K31" t="n">
-        <v>-15.56</v>
+        <v>-17.7</v>
       </c>
       <c r="L31" t="n">
-        <v>36.38</v>
+        <v>41.37</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>138.13</v>
+        <v>99.59</v>
       </c>
       <c r="K32" t="n">
-        <v>-77.23</v>
+        <v>-55.68</v>
       </c>
       <c r="L32" t="n">
-        <v>158.25</v>
+        <v>114.1</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-11.27</v>
+        <v>-8.35</v>
       </c>
       <c r="K33" t="n">
-        <v>105.91</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>106.5</v>
+        <v>78.95</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>55.54</v>
+        <v>49.8</v>
       </c>
       <c r="K34" t="n">
-        <v>38.37</v>
+        <v>34.4</v>
       </c>
       <c r="L34" t="n">
-        <v>67.5</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>37.43</v>
+        <v>35.55</v>
       </c>
       <c r="K35" t="n">
-        <v>-238.71</v>
+        <v>-226.71</v>
       </c>
       <c r="L35" t="n">
-        <v>241.63</v>
+        <v>229.48</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>-42.79</v>
+        <v>-28.45</v>
       </c>
       <c r="K36" t="n">
-        <v>240.78</v>
+        <v>160.1</v>
       </c>
       <c r="L36" t="n">
-        <v>244.56</v>
+        <v>162.61</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>13.31</v>
+        <v>12.79</v>
       </c>
       <c r="K37" t="n">
-        <v>-122.98</v>
+        <v>-118.13</v>
       </c>
       <c r="L37" t="n">
-        <v>123.7</v>
+        <v>118.82</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>113.48</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>-283.81</v>
+        <v>-208.02</v>
       </c>
       <c r="L38" t="n">
-        <v>305.65</v>
+        <v>224.03</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>30</v>
       </c>
       <c r="J39" t="n">
-        <v>-189.8</v>
+        <v>-169.78</v>
       </c>
       <c r="K39" t="n">
-        <v>52.33</v>
+        <v>46.81</v>
       </c>
       <c r="L39" t="n">
-        <v>196.88</v>
+        <v>176.11</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>30</v>
       </c>
       <c r="J40" t="n">
-        <v>-112.84</v>
+        <v>-122.96</v>
       </c>
       <c r="K40" t="n">
-        <v>167.97</v>
+        <v>183.04</v>
       </c>
       <c r="L40" t="n">
-        <v>202.35</v>
+        <v>220.5</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-67.06999999999999</v>
+        <v>-66.45</v>
       </c>
       <c r="K41" t="n">
-        <v>391.22</v>
+        <v>387.61</v>
       </c>
       <c r="L41" t="n">
-        <v>396.93</v>
+        <v>393.26</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>30</v>
       </c>
       <c r="J42" t="n">
-        <v>277.28</v>
+        <v>279.5</v>
       </c>
       <c r="K42" t="n">
-        <v>44.46</v>
+        <v>44.81</v>
       </c>
       <c r="L42" t="n">
-        <v>280.82</v>
+        <v>283.07</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-390.81</v>
+        <v>-433.85</v>
       </c>
       <c r="K43" t="n">
-        <v>100.12</v>
+        <v>111.15</v>
       </c>
       <c r="L43" t="n">
-        <v>403.43</v>
+        <v>447.86</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-99.12</v>
+        <v>-75.26000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>104.81</v>
+        <v>79.59</v>
       </c>
       <c r="L44" t="n">
-        <v>144.26</v>
+        <v>109.54</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>30</v>
       </c>
       <c r="J45" t="n">
-        <v>-49</v>
+        <v>-39.22</v>
       </c>
       <c r="K45" t="n">
-        <v>-38.55</v>
+        <v>-30.86</v>
       </c>
       <c r="L45" t="n">
-        <v>62.35</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>31.23</v>
+        <v>29.4</v>
       </c>
       <c r="K46" t="n">
-        <v>-84.31</v>
+        <v>-79.36</v>
       </c>
       <c r="L46" t="n">
-        <v>89.91</v>
+        <v>84.63</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>-115.53</v>
+        <v>-85.92</v>
       </c>
       <c r="K47" t="n">
-        <v>-72.69</v>
+        <v>-54.06</v>
       </c>
       <c r="L47" t="n">
-        <v>136.49</v>
+        <v>101.51</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-20.73</v>
+        <v>-23.6</v>
       </c>
       <c r="K48" t="n">
-        <v>-41.36</v>
+        <v>-47.09</v>
       </c>
       <c r="L48" t="n">
-        <v>46.26</v>
+        <v>52.68</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>-93.87</v>
+        <v>-72.7</v>
       </c>
       <c r="K49" t="n">
-        <v>16.47</v>
+        <v>12.75</v>
       </c>
       <c r="L49" t="n">
-        <v>95.31</v>
+        <v>73.81</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>29</v>
       </c>
       <c r="J50" t="n">
-        <v>70.63</v>
+        <v>72.22</v>
       </c>
       <c r="K50" t="n">
-        <v>119.45</v>
+        <v>122.15</v>
       </c>
       <c r="L50" t="n">
-        <v>138.76</v>
+        <v>141.9</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>67.94</v>
+        <v>66.84</v>
       </c>
       <c r="K51" t="n">
-        <v>-167.35</v>
+        <v>-164.65</v>
       </c>
       <c r="L51" t="n">
-        <v>180.61</v>
+        <v>177.7</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>27</v>
       </c>
       <c r="J52" t="n">
-        <v>114.85</v>
+        <v>134.26</v>
       </c>
       <c r="K52" t="n">
-        <v>32.74</v>
+        <v>38.27</v>
       </c>
       <c r="L52" t="n">
-        <v>119.43</v>
+        <v>139.6</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>29</v>
       </c>
       <c r="J53" t="n">
-        <v>146.09</v>
+        <v>151.9</v>
       </c>
       <c r="K53" t="n">
-        <v>-28.24</v>
+        <v>-29.36</v>
       </c>
       <c r="L53" t="n">
-        <v>148.79</v>
+        <v>154.71</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>7.13</v>
+        <v>6.45</v>
       </c>
       <c r="K54" t="n">
-        <v>-347.83</v>
+        <v>-314.88</v>
       </c>
       <c r="L54" t="n">
-        <v>347.9</v>
+        <v>314.95</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>30</v>
       </c>
       <c r="J55" t="n">
-        <v>287.36</v>
+        <v>202.5</v>
       </c>
       <c r="K55" t="n">
-        <v>222.95</v>
+        <v>157.1</v>
       </c>
       <c r="L55" t="n">
-        <v>363.71</v>
+        <v>256.29</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>-90.51000000000001</v>
+        <v>-105.68</v>
       </c>
       <c r="K56" t="n">
-        <v>-377.95</v>
+        <v>-441.3</v>
       </c>
       <c r="L56" t="n">
-        <v>388.63</v>
+        <v>453.78</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-15.86</v>
+        <v>-28.26</v>
       </c>
       <c r="K57" t="n">
-        <v>-133.19</v>
+        <v>-237.34</v>
       </c>
       <c r="L57" t="n">
-        <v>134.13</v>
+        <v>239.02</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>30</v>
       </c>
       <c r="J58" t="n">
-        <v>61.74</v>
+        <v>61.06</v>
       </c>
       <c r="K58" t="n">
-        <v>363.51</v>
+        <v>359.5</v>
       </c>
       <c r="L58" t="n">
-        <v>368.71</v>
+        <v>364.65</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-72.34</v>
+        <v>-60.48</v>
       </c>
       <c r="K59" t="n">
-        <v>-85.56</v>
+        <v>-71.53</v>
       </c>
       <c r="L59" t="n">
-        <v>112.05</v>
+        <v>93.67</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>-117.42</v>
+        <v>-71.39</v>
       </c>
       <c r="K60" t="n">
-        <v>131.6</v>
+        <v>80.02</v>
       </c>
       <c r="L60" t="n">
-        <v>176.37</v>
+        <v>107.23</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>209.66</v>
+        <v>143.33</v>
       </c>
       <c r="K61" t="n">
-        <v>-80.91</v>
+        <v>-55.31</v>
       </c>
       <c r="L61" t="n">
-        <v>224.73</v>
+        <v>153.63</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>-44.93</v>
+        <v>-49.71</v>
       </c>
       <c r="K62" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="L62" t="n">
-        <v>44.96</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-128.65</v>
+        <v>-120.22</v>
       </c>
       <c r="K63" t="n">
-        <v>-158.95</v>
+        <v>-148.54</v>
       </c>
       <c r="L63" t="n">
-        <v>204.49</v>
+        <v>191.1</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-51.12</v>
+        <v>-42.36</v>
       </c>
       <c r="K64" t="n">
-        <v>121.2</v>
+        <v>100.43</v>
       </c>
       <c r="L64" t="n">
-        <v>131.54</v>
+        <v>109</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>198.05</v>
+        <v>191.36</v>
       </c>
       <c r="K65" t="n">
-        <v>-112.75</v>
+        <v>-108.95</v>
       </c>
       <c r="L65" t="n">
-        <v>227.9</v>
+        <v>220.2</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>87.36</v>
+        <v>112.73</v>
       </c>
       <c r="K66" t="n">
-        <v>-43.97</v>
+        <v>-56.74</v>
       </c>
       <c r="L66" t="n">
-        <v>97.81</v>
+        <v>126.21</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>30</v>
       </c>
       <c r="J67" t="n">
-        <v>57.18</v>
+        <v>79.8</v>
       </c>
       <c r="K67" t="n">
-        <v>20.08</v>
+        <v>28.02</v>
       </c>
       <c r="L67" t="n">
-        <v>60.6</v>
+        <v>84.58</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-339.48</v>
+        <v>-302.82</v>
       </c>
       <c r="K68" t="n">
-        <v>-150.73</v>
+        <v>-134.45</v>
       </c>
       <c r="L68" t="n">
-        <v>371.44</v>
+        <v>331.33</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>-157.72</v>
+        <v>-129.72</v>
       </c>
       <c r="K69" t="n">
-        <v>145.81</v>
+        <v>119.92</v>
       </c>
       <c r="L69" t="n">
-        <v>214.79</v>
+        <v>176.65</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>52.45</v>
+        <v>63.27</v>
       </c>
       <c r="K70" t="n">
-        <v>-145.25</v>
+        <v>-175.2</v>
       </c>
       <c r="L70" t="n">
-        <v>154.43</v>
+        <v>186.27</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>-270.88</v>
+        <v>-272.43</v>
       </c>
       <c r="K71" t="n">
-        <v>-138.91</v>
+        <v>-139.71</v>
       </c>
       <c r="L71" t="n">
-        <v>304.42</v>
+        <v>306.16</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>22.87</v>
+        <v>28.65</v>
       </c>
       <c r="K72" t="n">
-        <v>-270.83</v>
+        <v>-339.22</v>
       </c>
       <c r="L72" t="n">
-        <v>271.79</v>
+        <v>340.43</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-64.23999999999999</v>
+        <v>-75.08</v>
       </c>
       <c r="K73" t="n">
-        <v>240.7</v>
+        <v>281.31</v>
       </c>
       <c r="L73" t="n">
-        <v>249.12</v>
+        <v>291.15</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>74.84</v>
+        <v>53.82</v>
       </c>
       <c r="K74" t="n">
-        <v>-81.77</v>
+        <v>-58.8</v>
       </c>
       <c r="L74" t="n">
-        <v>110.85</v>
+        <v>79.70999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>29</v>
       </c>
       <c r="J75" t="n">
-        <v>-46.04</v>
+        <v>-36.18</v>
       </c>
       <c r="K75" t="n">
-        <v>-21.42</v>
+        <v>-16.83</v>
       </c>
       <c r="L75" t="n">
-        <v>50.78</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>-120.62</v>
+        <v>-65.33</v>
       </c>
       <c r="K76" t="n">
-        <v>-99.47</v>
+        <v>-53.88</v>
       </c>
       <c r="L76" t="n">
-        <v>156.35</v>
+        <v>84.68000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>67.98999999999999</v>
+        <v>70.47</v>
       </c>
       <c r="K77" t="n">
-        <v>-116.05</v>
+        <v>-120.29</v>
       </c>
       <c r="L77" t="n">
-        <v>134.5</v>
+        <v>139.41</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>179.82</v>
+        <v>147.16</v>
       </c>
       <c r="K78" t="n">
-        <v>-104.52</v>
+        <v>-85.54000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>207.99</v>
+        <v>170.22</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-21.11</v>
+        <v>-20.41</v>
       </c>
       <c r="K79" t="n">
-        <v>-79.28</v>
+        <v>-76.67</v>
       </c>
       <c r="L79" t="n">
-        <v>82.04000000000001</v>
+        <v>79.34</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>68.33</v>
+        <v>92.25</v>
       </c>
       <c r="K80" t="n">
-        <v>-23.72</v>
+        <v>-32.03</v>
       </c>
       <c r="L80" t="n">
-        <v>72.33</v>
+        <v>97.65000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>14.69</v>
+        <v>14.33</v>
       </c>
       <c r="K81" t="n">
-        <v>-131.66</v>
+        <v>-128.44</v>
       </c>
       <c r="L81" t="n">
-        <v>132.47</v>
+        <v>129.24</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>13.64</v>
+        <v>16.07</v>
       </c>
       <c r="K82" t="n">
-        <v>-69.5</v>
+        <v>-81.90000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>70.81999999999999</v>
+        <v>83.45999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-114.17</v>
+        <v>-150.22</v>
       </c>
       <c r="K83" t="n">
-        <v>-42.64</v>
+        <v>-56.11</v>
       </c>
       <c r="L83" t="n">
-        <v>121.88</v>
+        <v>160.36</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>356.83</v>
+        <v>364.89</v>
       </c>
       <c r="K84" t="n">
-        <v>-170.73</v>
+        <v>-174.59</v>
       </c>
       <c r="L84" t="n">
-        <v>395.57</v>
+        <v>404.51</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>30</v>
       </c>
       <c r="J85" t="n">
-        <v>-31.93</v>
+        <v>-52.07</v>
       </c>
       <c r="K85" t="n">
-        <v>-70.88</v>
+        <v>-115.56</v>
       </c>
       <c r="L85" t="n">
-        <v>77.73999999999999</v>
+        <v>126.75</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-190.25</v>
+        <v>-270.91</v>
       </c>
       <c r="K86" t="n">
-        <v>-4.19</v>
+        <v>-5.97</v>
       </c>
       <c r="L86" t="n">
-        <v>190.3</v>
+        <v>270.98</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>29.47</v>
+        <v>33.08</v>
       </c>
       <c r="K87" t="n">
-        <v>198.51</v>
+        <v>222.82</v>
       </c>
       <c r="L87" t="n">
-        <v>200.68</v>
+        <v>225.26</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>-64.08</v>
+        <v>-65.45</v>
       </c>
       <c r="K88" t="n">
-        <v>398.68</v>
+        <v>407.18</v>
       </c>
       <c r="L88" t="n">
-        <v>403.79</v>
+        <v>412.41</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-09.xlsx
+++ b/output/2024-07-09.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-22.46</v>
+        <v>-23.74</v>
       </c>
       <c r="K14" t="n">
-        <v>-58.5</v>
+        <v>-61.82</v>
       </c>
       <c r="L14" t="n">
-        <v>62.66</v>
+        <v>66.23</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>35.4</v>
+        <v>29.17</v>
       </c>
       <c r="K15" t="n">
-        <v>-30.85</v>
+        <v>-25.42</v>
       </c>
       <c r="L15" t="n">
-        <v>46.95</v>
+        <v>38.69</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>21.45</v>
+        <v>23.62</v>
       </c>
       <c r="K16" t="n">
-        <v>-30.3</v>
+        <v>-33.36</v>
       </c>
       <c r="L16" t="n">
-        <v>37.12</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>43.7</v>
+        <v>43.18</v>
       </c>
       <c r="K17" t="n">
-        <v>-37.49</v>
+        <v>-37.04</v>
       </c>
       <c r="L17" t="n">
-        <v>57.58</v>
+        <v>56.89</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-37.88</v>
+        <v>-32.98</v>
       </c>
       <c r="K18" t="n">
-        <v>100.32</v>
+        <v>87.34</v>
       </c>
       <c r="L18" t="n">
-        <v>107.23</v>
+        <v>93.36</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>22.25</v>
+        <v>20.37</v>
       </c>
       <c r="K19" t="n">
-        <v>-154.55</v>
+        <v>-141.51</v>
       </c>
       <c r="L19" t="n">
-        <v>156.14</v>
+        <v>142.97</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-117.09</v>
+        <v>-100.49</v>
       </c>
       <c r="K20" t="n">
-        <v>32.08</v>
+        <v>27.53</v>
       </c>
       <c r="L20" t="n">
-        <v>121.41</v>
+        <v>104.2</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>113.92</v>
+        <v>80.81</v>
       </c>
       <c r="K21" t="n">
-        <v>3.88</v>
+        <v>2.75</v>
       </c>
       <c r="L21" t="n">
-        <v>113.99</v>
+        <v>80.84999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>112.1</v>
+        <v>91.73</v>
       </c>
       <c r="K22" t="n">
-        <v>-43.54</v>
+        <v>-35.63</v>
       </c>
       <c r="L22" t="n">
-        <v>120.26</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>-14.67</v>
+        <v>-11.92</v>
       </c>
       <c r="K23" t="n">
-        <v>-131.12</v>
+        <v>-106.59</v>
       </c>
       <c r="L23" t="n">
-        <v>131.94</v>
+        <v>107.26</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>59.32</v>
+        <v>41.08</v>
       </c>
       <c r="K24" t="n">
-        <v>-152.52</v>
+        <v>-105.62</v>
       </c>
       <c r="L24" t="n">
-        <v>163.65</v>
+        <v>113.32</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>200.69</v>
+        <v>145.71</v>
       </c>
       <c r="K25" t="n">
-        <v>6.23</v>
+        <v>4.52</v>
       </c>
       <c r="L25" t="n">
-        <v>200.79</v>
+        <v>145.78</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>-221.64</v>
+        <v>-163.54</v>
       </c>
       <c r="K26" t="n">
-        <v>-167.96</v>
+        <v>-123.93</v>
       </c>
       <c r="L26" t="n">
-        <v>278.09</v>
+        <v>205.2</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-162.23</v>
+        <v>-103.52</v>
       </c>
       <c r="K27" t="n">
-        <v>103.77</v>
+        <v>66.22</v>
       </c>
       <c r="L27" t="n">
-        <v>192.58</v>
+        <v>122.88</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>-116.99</v>
+        <v>-74.77</v>
       </c>
       <c r="K28" t="n">
-        <v>128.34</v>
+        <v>82.02</v>
       </c>
       <c r="L28" t="n">
-        <v>173.66</v>
+        <v>110.98</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>-27.72</v>
+        <v>-28</v>
       </c>
       <c r="K29" t="n">
-        <v>87.66</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>91.93000000000001</v>
+        <v>92.89</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-66.65000000000001</v>
+        <v>-63.34</v>
       </c>
       <c r="K30" t="n">
-        <v>42.55</v>
+        <v>40.43</v>
       </c>
       <c r="L30" t="n">
-        <v>79.08</v>
+        <v>75.15000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-37.4</v>
+        <v>-33.94</v>
       </c>
       <c r="K31" t="n">
-        <v>-17.7</v>
+        <v>-16.06</v>
       </c>
       <c r="L31" t="n">
-        <v>41.37</v>
+        <v>37.55</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>99.59</v>
+        <v>97.62</v>
       </c>
       <c r="K32" t="n">
-        <v>-55.68</v>
+        <v>-54.58</v>
       </c>
       <c r="L32" t="n">
-        <v>114.1</v>
+        <v>111.85</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-8.35</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>78.51000000000001</v>
+        <v>77.89</v>
       </c>
       <c r="L33" t="n">
-        <v>78.95</v>
+        <v>78.33</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>49.8</v>
+        <v>51.99</v>
       </c>
       <c r="K34" t="n">
-        <v>34.4</v>
+        <v>35.92</v>
       </c>
       <c r="L34" t="n">
-        <v>60.52</v>
+        <v>63.19</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>35.55</v>
+        <v>25.17</v>
       </c>
       <c r="K35" t="n">
-        <v>-226.71</v>
+        <v>-160.51</v>
       </c>
       <c r="L35" t="n">
-        <v>229.48</v>
+        <v>162.47</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>-28.45</v>
+        <v>-26.3</v>
       </c>
       <c r="K36" t="n">
-        <v>160.1</v>
+        <v>148</v>
       </c>
       <c r="L36" t="n">
-        <v>162.61</v>
+        <v>150.32</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>12.79</v>
+        <v>10.72</v>
       </c>
       <c r="K37" t="n">
-        <v>-118.13</v>
+        <v>-99.03</v>
       </c>
       <c r="L37" t="n">
-        <v>118.82</v>
+        <v>99.61</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>83.18000000000001</v>
+        <v>68.69</v>
       </c>
       <c r="K38" t="n">
-        <v>-208.02</v>
+        <v>-171.8</v>
       </c>
       <c r="L38" t="n">
-        <v>224.03</v>
+        <v>185.02</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>30</v>
       </c>
       <c r="J39" t="n">
-        <v>-169.78</v>
+        <v>-130.17</v>
       </c>
       <c r="K39" t="n">
-        <v>46.81</v>
+        <v>35.89</v>
       </c>
       <c r="L39" t="n">
-        <v>176.11</v>
+        <v>135.02</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>30</v>
       </c>
       <c r="J40" t="n">
-        <v>-122.96</v>
+        <v>-94.64</v>
       </c>
       <c r="K40" t="n">
-        <v>183.04</v>
+        <v>140.88</v>
       </c>
       <c r="L40" t="n">
-        <v>220.5</v>
+        <v>169.71</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-66.45</v>
+        <v>-43.77</v>
       </c>
       <c r="K41" t="n">
-        <v>387.61</v>
+        <v>255.32</v>
       </c>
       <c r="L41" t="n">
-        <v>393.26</v>
+        <v>259.05</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>30</v>
       </c>
       <c r="J42" t="n">
-        <v>279.5</v>
+        <v>204.52</v>
       </c>
       <c r="K42" t="n">
-        <v>44.81</v>
+        <v>32.79</v>
       </c>
       <c r="L42" t="n">
-        <v>283.07</v>
+        <v>207.13</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-433.85</v>
+        <v>-258.63</v>
       </c>
       <c r="K43" t="n">
-        <v>111.15</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>447.86</v>
+        <v>266.98</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-75.26000000000001</v>
+        <v>-68.93000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>79.59</v>
+        <v>72.89</v>
       </c>
       <c r="L44" t="n">
-        <v>109.54</v>
+        <v>100.32</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>30</v>
       </c>
       <c r="J45" t="n">
-        <v>-39.22</v>
+        <v>-45.92</v>
       </c>
       <c r="K45" t="n">
-        <v>-30.86</v>
+        <v>-36.13</v>
       </c>
       <c r="L45" t="n">
-        <v>49.9</v>
+        <v>58.43</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>29.4</v>
+        <v>26.46</v>
       </c>
       <c r="K46" t="n">
-        <v>-79.36</v>
+        <v>-71.43000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>84.63</v>
+        <v>76.18000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>-85.92</v>
+        <v>-87.40000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>-54.06</v>
+        <v>-54.99</v>
       </c>
       <c r="L47" t="n">
-        <v>101.51</v>
+        <v>103.26</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-23.6</v>
+        <v>-25.46</v>
       </c>
       <c r="K48" t="n">
-        <v>-47.09</v>
+        <v>-50.81</v>
       </c>
       <c r="L48" t="n">
-        <v>52.68</v>
+        <v>56.83</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>-72.7</v>
+        <v>-76.06</v>
       </c>
       <c r="K49" t="n">
-        <v>12.75</v>
+        <v>13.34</v>
       </c>
       <c r="L49" t="n">
-        <v>73.81</v>
+        <v>77.22</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>29</v>
       </c>
       <c r="J50" t="n">
-        <v>72.22</v>
+        <v>61.59</v>
       </c>
       <c r="K50" t="n">
-        <v>122.15</v>
+        <v>104.16</v>
       </c>
       <c r="L50" t="n">
-        <v>141.9</v>
+        <v>121.01</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>66.84</v>
+        <v>48.69</v>
       </c>
       <c r="K51" t="n">
-        <v>-164.65</v>
+        <v>-119.93</v>
       </c>
       <c r="L51" t="n">
-        <v>177.7</v>
+        <v>129.44</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>27</v>
       </c>
       <c r="J52" t="n">
-        <v>134.26</v>
+        <v>105.43</v>
       </c>
       <c r="K52" t="n">
-        <v>38.27</v>
+        <v>30.05</v>
       </c>
       <c r="L52" t="n">
-        <v>139.6</v>
+        <v>109.63</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>29</v>
       </c>
       <c r="J53" t="n">
-        <v>151.9</v>
+        <v>120.23</v>
       </c>
       <c r="K53" t="n">
-        <v>-29.36</v>
+        <v>-23.24</v>
       </c>
       <c r="L53" t="n">
-        <v>154.71</v>
+        <v>122.46</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>6.45</v>
+        <v>4.63</v>
       </c>
       <c r="K54" t="n">
-        <v>-314.88</v>
+        <v>-225.92</v>
       </c>
       <c r="L54" t="n">
-        <v>314.95</v>
+        <v>225.97</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>30</v>
       </c>
       <c r="J55" t="n">
-        <v>202.5</v>
+        <v>165.96</v>
       </c>
       <c r="K55" t="n">
-        <v>157.1</v>
+        <v>128.76</v>
       </c>
       <c r="L55" t="n">
-        <v>256.29</v>
+        <v>210.05</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>-105.68</v>
+        <v>-66.08</v>
       </c>
       <c r="K56" t="n">
-        <v>-441.3</v>
+        <v>-275.93</v>
       </c>
       <c r="L56" t="n">
-        <v>453.78</v>
+        <v>283.73</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-28.26</v>
+        <v>-15.51</v>
       </c>
       <c r="K57" t="n">
-        <v>-237.34</v>
+        <v>-130.24</v>
       </c>
       <c r="L57" t="n">
-        <v>239.02</v>
+        <v>131.16</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>30</v>
       </c>
       <c r="J58" t="n">
-        <v>61.06</v>
+        <v>43.46</v>
       </c>
       <c r="K58" t="n">
-        <v>359.5</v>
+        <v>255.87</v>
       </c>
       <c r="L58" t="n">
-        <v>364.65</v>
+        <v>259.54</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-60.48</v>
+        <v>-56.4</v>
       </c>
       <c r="K59" t="n">
-        <v>-71.53</v>
+        <v>-66.70999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>93.67</v>
+        <v>87.36</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>-71.39</v>
+        <v>-80.56999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>80.02</v>
+        <v>90.3</v>
       </c>
       <c r="L60" t="n">
-        <v>107.23</v>
+        <v>121.02</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>143.33</v>
+        <v>127.81</v>
       </c>
       <c r="K61" t="n">
-        <v>-55.31</v>
+        <v>-49.32</v>
       </c>
       <c r="L61" t="n">
-        <v>153.63</v>
+        <v>136.99</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>-49.71</v>
+        <v>-50.61</v>
       </c>
       <c r="K62" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="L62" t="n">
-        <v>49.73</v>
+        <v>50.64</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-120.22</v>
+        <v>-95.43000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>-148.54</v>
+        <v>-117.91</v>
       </c>
       <c r="L63" t="n">
-        <v>191.1</v>
+        <v>151.69</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-42.36</v>
+        <v>-38.13</v>
       </c>
       <c r="K64" t="n">
-        <v>100.43</v>
+        <v>90.42</v>
       </c>
       <c r="L64" t="n">
-        <v>109</v>
+        <v>98.13</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>191.36</v>
+        <v>135.65</v>
       </c>
       <c r="K65" t="n">
-        <v>-108.95</v>
+        <v>-77.23</v>
       </c>
       <c r="L65" t="n">
-        <v>220.2</v>
+        <v>156.1</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>112.73</v>
+        <v>88.52</v>
       </c>
       <c r="K66" t="n">
-        <v>-56.74</v>
+        <v>-44.56</v>
       </c>
       <c r="L66" t="n">
-        <v>126.21</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>30</v>
       </c>
       <c r="J67" t="n">
-        <v>79.8</v>
+        <v>73.45</v>
       </c>
       <c r="K67" t="n">
-        <v>28.02</v>
+        <v>25.79</v>
       </c>
       <c r="L67" t="n">
-        <v>84.58</v>
+        <v>77.84999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-302.82</v>
+        <v>-205.27</v>
       </c>
       <c r="K68" t="n">
-        <v>-134.45</v>
+        <v>-91.14</v>
       </c>
       <c r="L68" t="n">
-        <v>331.33</v>
+        <v>224.6</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>-129.72</v>
+        <v>-105.5</v>
       </c>
       <c r="K69" t="n">
-        <v>119.92</v>
+        <v>97.53</v>
       </c>
       <c r="L69" t="n">
-        <v>176.65</v>
+        <v>143.67</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>63.27</v>
+        <v>47.3</v>
       </c>
       <c r="K70" t="n">
-        <v>-175.2</v>
+        <v>-130.97</v>
       </c>
       <c r="L70" t="n">
-        <v>186.27</v>
+        <v>139.25</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>-272.43</v>
+        <v>-190.71</v>
       </c>
       <c r="K71" t="n">
-        <v>-139.71</v>
+        <v>-97.8</v>
       </c>
       <c r="L71" t="n">
-        <v>306.16</v>
+        <v>214.33</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>28.65</v>
+        <v>18.95</v>
       </c>
       <c r="K72" t="n">
-        <v>-339.22</v>
+        <v>-224.44</v>
       </c>
       <c r="L72" t="n">
-        <v>340.43</v>
+        <v>225.24</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-75.08</v>
+        <v>-53.23</v>
       </c>
       <c r="K73" t="n">
-        <v>281.31</v>
+        <v>199.44</v>
       </c>
       <c r="L73" t="n">
-        <v>291.15</v>
+        <v>206.42</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>53.82</v>
+        <v>52.15</v>
       </c>
       <c r="K74" t="n">
-        <v>-58.8</v>
+        <v>-56.98</v>
       </c>
       <c r="L74" t="n">
-        <v>79.70999999999999</v>
+        <v>77.23999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>29</v>
       </c>
       <c r="J75" t="n">
-        <v>-36.18</v>
+        <v>-42.58</v>
       </c>
       <c r="K75" t="n">
-        <v>-16.83</v>
+        <v>-19.81</v>
       </c>
       <c r="L75" t="n">
-        <v>39.9</v>
+        <v>46.97</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>-65.33</v>
+        <v>-76.52</v>
       </c>
       <c r="K76" t="n">
-        <v>-53.88</v>
+        <v>-63.11</v>
       </c>
       <c r="L76" t="n">
-        <v>84.68000000000001</v>
+        <v>99.19</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>70.47</v>
+        <v>55.13</v>
       </c>
       <c r="K77" t="n">
-        <v>-120.29</v>
+        <v>-94.09999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>139.41</v>
+        <v>109.06</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>147.16</v>
+        <v>122.3</v>
       </c>
       <c r="K78" t="n">
-        <v>-85.54000000000001</v>
+        <v>-71.09</v>
       </c>
       <c r="L78" t="n">
-        <v>170.22</v>
+        <v>141.46</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-20.41</v>
+        <v>-19.51</v>
       </c>
       <c r="K79" t="n">
-        <v>-76.67</v>
+        <v>-73.28</v>
       </c>
       <c r="L79" t="n">
-        <v>79.34</v>
+        <v>75.83</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>92.25</v>
+        <v>74.64</v>
       </c>
       <c r="K80" t="n">
-        <v>-32.03</v>
+        <v>-25.91</v>
       </c>
       <c r="L80" t="n">
-        <v>97.65000000000001</v>
+        <v>79.01000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>14.33</v>
+        <v>11.71</v>
       </c>
       <c r="K81" t="n">
-        <v>-128.44</v>
+        <v>-104.96</v>
       </c>
       <c r="L81" t="n">
-        <v>129.24</v>
+        <v>105.61</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>16.07</v>
+        <v>14.09</v>
       </c>
       <c r="K82" t="n">
-        <v>-81.90000000000001</v>
+        <v>-71.81</v>
       </c>
       <c r="L82" t="n">
-        <v>83.45999999999999</v>
+        <v>73.18000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-150.22</v>
+        <v>-98.22</v>
       </c>
       <c r="K83" t="n">
-        <v>-56.11</v>
+        <v>-36.69</v>
       </c>
       <c r="L83" t="n">
-        <v>160.36</v>
+        <v>104.85</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>364.89</v>
+        <v>221.17</v>
       </c>
       <c r="K84" t="n">
-        <v>-174.59</v>
+        <v>-105.82</v>
       </c>
       <c r="L84" t="n">
-        <v>404.51</v>
+        <v>245.19</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>30</v>
       </c>
       <c r="J85" t="n">
-        <v>-52.07</v>
+        <v>-40.92</v>
       </c>
       <c r="K85" t="n">
-        <v>-115.56</v>
+        <v>-90.81999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>126.75</v>
+        <v>99.61</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-270.91</v>
+        <v>-151.79</v>
       </c>
       <c r="K86" t="n">
-        <v>-5.97</v>
+        <v>-3.34</v>
       </c>
       <c r="L86" t="n">
-        <v>270.98</v>
+        <v>151.83</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>33.08</v>
+        <v>22.6</v>
       </c>
       <c r="K87" t="n">
-        <v>222.82</v>
+        <v>152.22</v>
       </c>
       <c r="L87" t="n">
-        <v>225.26</v>
+        <v>153.89</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>-65.45</v>
+        <v>-42.39</v>
       </c>
       <c r="K88" t="n">
-        <v>407.18</v>
+        <v>263.7</v>
       </c>
       <c r="L88" t="n">
-        <v>412.41</v>
+        <v>267.09</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-09.xlsx
+++ b/output/2024-07-09.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-23.74</v>
+        <v>-22.78</v>
       </c>
       <c r="K14" t="n">
-        <v>-61.82</v>
+        <v>-59.31</v>
       </c>
       <c r="L14" t="n">
-        <v>66.23</v>
+        <v>63.53</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>29.17</v>
+        <v>28.55</v>
       </c>
       <c r="K15" t="n">
-        <v>-25.42</v>
+        <v>-24.88</v>
       </c>
       <c r="L15" t="n">
-        <v>38.69</v>
+        <v>37.87</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>23.62</v>
+        <v>22.53</v>
       </c>
       <c r="K16" t="n">
-        <v>-33.36</v>
+        <v>-31.83</v>
       </c>
       <c r="L16" t="n">
-        <v>40.87</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>43.18</v>
+        <v>42.28</v>
       </c>
       <c r="K17" t="n">
-        <v>-37.04</v>
+        <v>-36.27</v>
       </c>
       <c r="L17" t="n">
-        <v>56.89</v>
+        <v>55.71</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-32.98</v>
+        <v>-32.85</v>
       </c>
       <c r="K18" t="n">
-        <v>87.34</v>
+        <v>87</v>
       </c>
       <c r="L18" t="n">
-        <v>93.36</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>20.37</v>
+        <v>20.47</v>
       </c>
       <c r="K19" t="n">
-        <v>-141.51</v>
+        <v>-142.2</v>
       </c>
       <c r="L19" t="n">
-        <v>142.97</v>
+        <v>143.66</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-100.49</v>
+        <v>-103.91</v>
       </c>
       <c r="K20" t="n">
-        <v>27.53</v>
+        <v>28.47</v>
       </c>
       <c r="L20" t="n">
-        <v>104.2</v>
+        <v>107.74</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>80.81</v>
+        <v>85.42</v>
       </c>
       <c r="K21" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="L21" t="n">
-        <v>80.84999999999999</v>
+        <v>85.47</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>91.73</v>
+        <v>95.83</v>
       </c>
       <c r="K22" t="n">
-        <v>-35.63</v>
+        <v>-37.22</v>
       </c>
       <c r="L22" t="n">
-        <v>98.40000000000001</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>-11.92</v>
+        <v>-12.57</v>
       </c>
       <c r="K23" t="n">
-        <v>-106.59</v>
+        <v>-112.37</v>
       </c>
       <c r="L23" t="n">
-        <v>107.26</v>
+        <v>113.07</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>41.08</v>
+        <v>44.59</v>
       </c>
       <c r="K24" t="n">
-        <v>-105.62</v>
+        <v>-114.65</v>
       </c>
       <c r="L24" t="n">
-        <v>113.32</v>
+        <v>123.01</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>145.71</v>
+        <v>154.23</v>
       </c>
       <c r="K25" t="n">
-        <v>4.52</v>
+        <v>4.78</v>
       </c>
       <c r="L25" t="n">
-        <v>145.78</v>
+        <v>154.3</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>-163.54</v>
+        <v>-174.26</v>
       </c>
       <c r="K26" t="n">
-        <v>-123.93</v>
+        <v>-132.05</v>
       </c>
       <c r="L26" t="n">
-        <v>205.2</v>
+        <v>218.64</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-103.52</v>
+        <v>-113.03</v>
       </c>
       <c r="K27" t="n">
-        <v>66.22</v>
+        <v>72.3</v>
       </c>
       <c r="L27" t="n">
-        <v>122.88</v>
+        <v>134.18</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>-74.77</v>
+        <v>-81.34</v>
       </c>
       <c r="K28" t="n">
-        <v>82.02</v>
+        <v>89.23</v>
       </c>
       <c r="L28" t="n">
-        <v>110.98</v>
+        <v>120.74</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>-28</v>
+        <v>-26.58</v>
       </c>
       <c r="K29" t="n">
-        <v>88.56999999999999</v>
+        <v>84.06</v>
       </c>
       <c r="L29" t="n">
-        <v>92.89</v>
+        <v>88.16</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-63.34</v>
+        <v>-61.53</v>
       </c>
       <c r="K30" t="n">
-        <v>40.43</v>
+        <v>39.28</v>
       </c>
       <c r="L30" t="n">
-        <v>75.15000000000001</v>
+        <v>72.98999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-33.94</v>
+        <v>-32.91</v>
       </c>
       <c r="K31" t="n">
-        <v>-16.06</v>
+        <v>-15.57</v>
       </c>
       <c r="L31" t="n">
-        <v>37.55</v>
+        <v>36.41</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>97.62</v>
+        <v>97.11</v>
       </c>
       <c r="K32" t="n">
-        <v>-54.58</v>
+        <v>-54.29</v>
       </c>
       <c r="L32" t="n">
-        <v>111.85</v>
+        <v>111.25</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-8.289999999999999</v>
+        <v>-8.15</v>
       </c>
       <c r="K33" t="n">
-        <v>77.89</v>
+        <v>76.56</v>
       </c>
       <c r="L33" t="n">
-        <v>78.33</v>
+        <v>76.98999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>51.99</v>
+        <v>51.34</v>
       </c>
       <c r="K34" t="n">
-        <v>35.92</v>
+        <v>35.47</v>
       </c>
       <c r="L34" t="n">
-        <v>63.19</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>25.17</v>
+        <v>26.29</v>
       </c>
       <c r="K35" t="n">
-        <v>-160.51</v>
+        <v>-167.69</v>
       </c>
       <c r="L35" t="n">
-        <v>162.47</v>
+        <v>169.73</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>-26.3</v>
+        <v>-27.02</v>
       </c>
       <c r="K36" t="n">
-        <v>148</v>
+        <v>152.05</v>
       </c>
       <c r="L36" t="n">
-        <v>150.32</v>
+        <v>154.43</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>10.72</v>
+        <v>11.19</v>
       </c>
       <c r="K37" t="n">
-        <v>-99.03</v>
+        <v>-103.34</v>
       </c>
       <c r="L37" t="n">
-        <v>99.61</v>
+        <v>103.94</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>68.69</v>
+        <v>72.63</v>
       </c>
       <c r="K38" t="n">
-        <v>-171.8</v>
+        <v>-181.65</v>
       </c>
       <c r="L38" t="n">
-        <v>185.02</v>
+        <v>195.63</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>30</v>
       </c>
       <c r="J39" t="n">
-        <v>-130.17</v>
+        <v>-138.93</v>
       </c>
       <c r="K39" t="n">
-        <v>35.89</v>
+        <v>38.3</v>
       </c>
       <c r="L39" t="n">
-        <v>135.02</v>
+        <v>144.11</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>30</v>
       </c>
       <c r="J40" t="n">
-        <v>-94.64</v>
+        <v>-98.81999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>140.88</v>
+        <v>147.1</v>
       </c>
       <c r="L40" t="n">
-        <v>169.71</v>
+        <v>177.21</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-43.77</v>
+        <v>-47.35</v>
       </c>
       <c r="K41" t="n">
-        <v>255.32</v>
+        <v>276.17</v>
       </c>
       <c r="L41" t="n">
-        <v>259.05</v>
+        <v>280.2</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>30</v>
       </c>
       <c r="J42" t="n">
-        <v>204.52</v>
+        <v>218.35</v>
       </c>
       <c r="K42" t="n">
-        <v>32.79</v>
+        <v>35.01</v>
       </c>
       <c r="L42" t="n">
-        <v>207.13</v>
+        <v>221.14</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-258.63</v>
+        <v>-280.78</v>
       </c>
       <c r="K43" t="n">
-        <v>66.26000000000001</v>
+        <v>71.94</v>
       </c>
       <c r="L43" t="n">
-        <v>266.98</v>
+        <v>289.85</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-68.93000000000001</v>
+        <v>-67.23999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>72.89</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>100.32</v>
+        <v>97.86</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>30</v>
       </c>
       <c r="J45" t="n">
-        <v>-45.92</v>
+        <v>-44.2</v>
       </c>
       <c r="K45" t="n">
-        <v>-36.13</v>
+        <v>-34.78</v>
       </c>
       <c r="L45" t="n">
-        <v>58.43</v>
+        <v>56.24</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>26.46</v>
+        <v>25.88</v>
       </c>
       <c r="K46" t="n">
-        <v>-71.43000000000001</v>
+        <v>-69.86</v>
       </c>
       <c r="L46" t="n">
-        <v>76.18000000000001</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>-87.40000000000001</v>
+        <v>-85.03</v>
       </c>
       <c r="K47" t="n">
-        <v>-54.99</v>
+        <v>-53.5</v>
       </c>
       <c r="L47" t="n">
-        <v>103.26</v>
+        <v>100.47</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-25.46</v>
+        <v>-24.97</v>
       </c>
       <c r="K48" t="n">
-        <v>-50.81</v>
+        <v>-49.83</v>
       </c>
       <c r="L48" t="n">
-        <v>56.83</v>
+        <v>55.74</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>-76.06</v>
+        <v>-74.92</v>
       </c>
       <c r="K49" t="n">
-        <v>13.34</v>
+        <v>13.14</v>
       </c>
       <c r="L49" t="n">
-        <v>77.22</v>
+        <v>76.06</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>29</v>
       </c>
       <c r="J50" t="n">
-        <v>61.59</v>
+        <v>63</v>
       </c>
       <c r="K50" t="n">
-        <v>104.16</v>
+        <v>106.55</v>
       </c>
       <c r="L50" t="n">
-        <v>121.01</v>
+        <v>123.78</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>48.69</v>
+        <v>52.13</v>
       </c>
       <c r="K51" t="n">
-        <v>-119.93</v>
+        <v>-128.42</v>
       </c>
       <c r="L51" t="n">
-        <v>129.44</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>27</v>
       </c>
       <c r="J52" t="n">
-        <v>105.43</v>
+        <v>109.5</v>
       </c>
       <c r="K52" t="n">
-        <v>30.05</v>
+        <v>31.21</v>
       </c>
       <c r="L52" t="n">
-        <v>109.63</v>
+        <v>113.86</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>29</v>
       </c>
       <c r="J53" t="n">
-        <v>120.23</v>
+        <v>126.54</v>
       </c>
       <c r="K53" t="n">
-        <v>-23.24</v>
+        <v>-24.46</v>
       </c>
       <c r="L53" t="n">
-        <v>122.46</v>
+        <v>128.88</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>4.63</v>
+        <v>4.91</v>
       </c>
       <c r="K54" t="n">
-        <v>-225.92</v>
+        <v>-239.6</v>
       </c>
       <c r="L54" t="n">
-        <v>225.97</v>
+        <v>239.65</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>30</v>
       </c>
       <c r="J55" t="n">
-        <v>165.96</v>
+        <v>176.98</v>
       </c>
       <c r="K55" t="n">
-        <v>128.76</v>
+        <v>137.31</v>
       </c>
       <c r="L55" t="n">
-        <v>210.05</v>
+        <v>224</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>-66.08</v>
+        <v>-70.79000000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>-275.93</v>
+        <v>-295.61</v>
       </c>
       <c r="L56" t="n">
-        <v>283.73</v>
+        <v>303.96</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-15.51</v>
+        <v>-17.2</v>
       </c>
       <c r="K57" t="n">
-        <v>-130.24</v>
+        <v>-144.43</v>
       </c>
       <c r="L57" t="n">
-        <v>131.16</v>
+        <v>145.45</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>30</v>
       </c>
       <c r="J58" t="n">
-        <v>43.46</v>
+        <v>46.58</v>
       </c>
       <c r="K58" t="n">
-        <v>255.87</v>
+        <v>274.24</v>
       </c>
       <c r="L58" t="n">
-        <v>259.54</v>
+        <v>278.16</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-56.4</v>
+        <v>-54.85</v>
       </c>
       <c r="K59" t="n">
-        <v>-66.70999999999999</v>
+        <v>-64.87</v>
       </c>
       <c r="L59" t="n">
-        <v>87.36</v>
+        <v>84.95</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>-80.56999999999999</v>
+        <v>-76.97</v>
       </c>
       <c r="K60" t="n">
-        <v>90.3</v>
+        <v>86.27</v>
       </c>
       <c r="L60" t="n">
-        <v>121.02</v>
+        <v>115.62</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>127.81</v>
+        <v>126.37</v>
       </c>
       <c r="K61" t="n">
-        <v>-49.32</v>
+        <v>-48.76</v>
       </c>
       <c r="L61" t="n">
-        <v>136.99</v>
+        <v>135.45</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>-50.61</v>
+        <v>-49.08</v>
       </c>
       <c r="K62" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="L62" t="n">
-        <v>50.64</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-95.43000000000001</v>
+        <v>-97.28</v>
       </c>
       <c r="K63" t="n">
-        <v>-117.91</v>
+        <v>-120.19</v>
       </c>
       <c r="L63" t="n">
-        <v>151.69</v>
+        <v>154.63</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-38.13</v>
+        <v>-38.04</v>
       </c>
       <c r="K64" t="n">
-        <v>90.42</v>
+        <v>90.2</v>
       </c>
       <c r="L64" t="n">
-        <v>98.13</v>
+        <v>97.89</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>135.65</v>
+        <v>144.32</v>
       </c>
       <c r="K65" t="n">
-        <v>-77.23</v>
+        <v>-82.17</v>
       </c>
       <c r="L65" t="n">
-        <v>156.1</v>
+        <v>166.07</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>88.52</v>
+        <v>93.22</v>
       </c>
       <c r="K66" t="n">
-        <v>-44.56</v>
+        <v>-46.92</v>
       </c>
       <c r="L66" t="n">
-        <v>99.09999999999999</v>
+        <v>104.37</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>30</v>
       </c>
       <c r="J67" t="n">
-        <v>73.45</v>
+        <v>75.27</v>
       </c>
       <c r="K67" t="n">
-        <v>25.79</v>
+        <v>26.43</v>
       </c>
       <c r="L67" t="n">
-        <v>77.84999999999999</v>
+        <v>79.78</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-205.27</v>
+        <v>-221.12</v>
       </c>
       <c r="K68" t="n">
-        <v>-91.14</v>
+        <v>-98.18000000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>224.6</v>
+        <v>241.94</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>-105.5</v>
+        <v>-111.66</v>
       </c>
       <c r="K69" t="n">
-        <v>97.53</v>
+        <v>103.22</v>
       </c>
       <c r="L69" t="n">
-        <v>143.67</v>
+        <v>152.06</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>47.3</v>
+        <v>49.98</v>
       </c>
       <c r="K70" t="n">
-        <v>-130.97</v>
+        <v>-138.39</v>
       </c>
       <c r="L70" t="n">
-        <v>139.25</v>
+        <v>147.14</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>-190.71</v>
+        <v>-205.14</v>
       </c>
       <c r="K71" t="n">
-        <v>-97.8</v>
+        <v>-105.2</v>
       </c>
       <c r="L71" t="n">
-        <v>214.33</v>
+        <v>230.54</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>18.95</v>
+        <v>20.38</v>
       </c>
       <c r="K72" t="n">
-        <v>-224.44</v>
+        <v>-241.38</v>
       </c>
       <c r="L72" t="n">
-        <v>225.24</v>
+        <v>242.23</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-53.23</v>
+        <v>-56.13</v>
       </c>
       <c r="K73" t="n">
-        <v>199.44</v>
+        <v>210.32</v>
       </c>
       <c r="L73" t="n">
-        <v>206.42</v>
+        <v>217.69</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>52.15</v>
+        <v>51.31</v>
       </c>
       <c r="K74" t="n">
-        <v>-56.98</v>
+        <v>-56.06</v>
       </c>
       <c r="L74" t="n">
-        <v>77.23999999999999</v>
+        <v>75.98999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>29</v>
       </c>
       <c r="J75" t="n">
-        <v>-42.58</v>
+        <v>-40.41</v>
       </c>
       <c r="K75" t="n">
-        <v>-19.81</v>
+        <v>-18.8</v>
       </c>
       <c r="L75" t="n">
-        <v>46.97</v>
+        <v>44.57</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>-76.52</v>
+        <v>-73.26000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>-63.11</v>
+        <v>-60.41</v>
       </c>
       <c r="L76" t="n">
-        <v>99.19</v>
+        <v>94.95999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>55.13</v>
+        <v>56.6</v>
       </c>
       <c r="K77" t="n">
-        <v>-94.09999999999999</v>
+        <v>-96.61</v>
       </c>
       <c r="L77" t="n">
-        <v>109.06</v>
+        <v>111.98</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>122.3</v>
+        <v>125.14</v>
       </c>
       <c r="K78" t="n">
-        <v>-71.09</v>
+        <v>-72.73999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>141.46</v>
+        <v>144.74</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-19.51</v>
+        <v>-19.52</v>
       </c>
       <c r="K79" t="n">
-        <v>-73.28</v>
+        <v>-73.31999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>75.83</v>
+        <v>75.87</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>74.64</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>-25.91</v>
+        <v>-27.28</v>
       </c>
       <c r="L80" t="n">
-        <v>79.01000000000001</v>
+        <v>83.17</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>11.71</v>
+        <v>12.21</v>
       </c>
       <c r="K81" t="n">
-        <v>-104.96</v>
+        <v>-109.39</v>
       </c>
       <c r="L81" t="n">
-        <v>105.61</v>
+        <v>110.07</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>14.09</v>
+        <v>14.72</v>
       </c>
       <c r="K82" t="n">
-        <v>-71.81</v>
+        <v>-75.03</v>
       </c>
       <c r="L82" t="n">
-        <v>73.18000000000001</v>
+        <v>76.45999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-98.22</v>
+        <v>-107.46</v>
       </c>
       <c r="K83" t="n">
-        <v>-36.69</v>
+        <v>-40.14</v>
       </c>
       <c r="L83" t="n">
-        <v>104.85</v>
+        <v>114.71</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>221.17</v>
+        <v>238</v>
       </c>
       <c r="K84" t="n">
-        <v>-105.82</v>
+        <v>-113.87</v>
       </c>
       <c r="L84" t="n">
-        <v>245.19</v>
+        <v>263.84</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>30</v>
       </c>
       <c r="J85" t="n">
-        <v>-40.92</v>
+        <v>-43.05</v>
       </c>
       <c r="K85" t="n">
-        <v>-90.81999999999999</v>
+        <v>-95.55</v>
       </c>
       <c r="L85" t="n">
-        <v>99.61</v>
+        <v>104.8</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-151.79</v>
+        <v>-168.08</v>
       </c>
       <c r="K86" t="n">
-        <v>-3.34</v>
+        <v>-3.7</v>
       </c>
       <c r="L86" t="n">
-        <v>151.83</v>
+        <v>168.12</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>22.6</v>
+        <v>24.19</v>
       </c>
       <c r="K87" t="n">
-        <v>152.22</v>
+        <v>162.92</v>
       </c>
       <c r="L87" t="n">
-        <v>153.89</v>
+        <v>164.7</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>-42.39</v>
+        <v>-45.46</v>
       </c>
       <c r="K88" t="n">
-        <v>263.7</v>
+        <v>282.83</v>
       </c>
       <c r="L88" t="n">
-        <v>267.09</v>
+        <v>286.46</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-09.xlsx
+++ b/output/2024-07-09.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-22.78</v>
+        <v>-16.64</v>
       </c>
       <c r="K14" t="n">
-        <v>-59.31</v>
+        <v>-43.33</v>
       </c>
       <c r="L14" t="n">
-        <v>63.53</v>
+        <v>46.41</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>28.55</v>
+        <v>21.41</v>
       </c>
       <c r="K15" t="n">
-        <v>-24.88</v>
+        <v>-18.66</v>
       </c>
       <c r="L15" t="n">
-        <v>37.87</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>22.53</v>
+        <v>16.58</v>
       </c>
       <c r="K16" t="n">
-        <v>-31.83</v>
+        <v>-23.42</v>
       </c>
       <c r="L16" t="n">
-        <v>39</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>42.28</v>
+        <v>29.87</v>
       </c>
       <c r="K17" t="n">
-        <v>-36.27</v>
+        <v>-25.62</v>
       </c>
       <c r="L17" t="n">
-        <v>55.71</v>
+        <v>39.35</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-32.85</v>
+        <v>-24.48</v>
       </c>
       <c r="K18" t="n">
-        <v>87</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>93</v>
+        <v>69.29000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>20.47</v>
+        <v>13.93</v>
       </c>
       <c r="K19" t="n">
-        <v>-142.2</v>
+        <v>-96.78</v>
       </c>
       <c r="L19" t="n">
-        <v>143.66</v>
+        <v>97.77</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-103.91</v>
+        <v>-72.84</v>
       </c>
       <c r="K20" t="n">
-        <v>28.47</v>
+        <v>19.96</v>
       </c>
       <c r="L20" t="n">
-        <v>107.74</v>
+        <v>75.52</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>85.42</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>2.91</v>
+        <v>2.18</v>
       </c>
       <c r="L21" t="n">
-        <v>85.47</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>95.83</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-37.22</v>
+        <v>-26.18</v>
       </c>
       <c r="L22" t="n">
-        <v>102.8</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>-12.57</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-112.37</v>
+        <v>-73.52</v>
       </c>
       <c r="L23" t="n">
-        <v>113.07</v>
+        <v>73.98</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>44.59</v>
+        <v>31.69</v>
       </c>
       <c r="K24" t="n">
-        <v>-114.65</v>
+        <v>-81.48999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>123.01</v>
+        <v>87.43000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>154.23</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>4.78</v>
+        <v>3.07</v>
       </c>
       <c r="L25" t="n">
-        <v>154.3</v>
+        <v>98.95</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>-174.26</v>
+        <v>-117.41</v>
       </c>
       <c r="K26" t="n">
-        <v>-132.05</v>
+        <v>-88.97</v>
       </c>
       <c r="L26" t="n">
-        <v>218.64</v>
+        <v>147.31</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-113.03</v>
+        <v>-81.02</v>
       </c>
       <c r="K27" t="n">
-        <v>72.3</v>
+        <v>51.82</v>
       </c>
       <c r="L27" t="n">
-        <v>134.18</v>
+        <v>96.18000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>-81.34</v>
+        <v>-61.01</v>
       </c>
       <c r="K28" t="n">
-        <v>89.23</v>
+        <v>66.92</v>
       </c>
       <c r="L28" t="n">
-        <v>120.74</v>
+        <v>90.56</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>-26.58</v>
+        <v>-16.08</v>
       </c>
       <c r="K29" t="n">
-        <v>84.06</v>
+        <v>50.84</v>
       </c>
       <c r="L29" t="n">
-        <v>88.16</v>
+        <v>53.32</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-61.53</v>
+        <v>-38.42</v>
       </c>
       <c r="K30" t="n">
-        <v>39.28</v>
+        <v>24.53</v>
       </c>
       <c r="L30" t="n">
-        <v>72.98999999999999</v>
+        <v>45.58</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-32.91</v>
+        <v>-24.31</v>
       </c>
       <c r="K31" t="n">
-        <v>-15.57</v>
+        <v>-11.5</v>
       </c>
       <c r="L31" t="n">
-        <v>36.41</v>
+        <v>26.89</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>97.11</v>
+        <v>63.83</v>
       </c>
       <c r="K32" t="n">
-        <v>-54.29</v>
+        <v>-35.69</v>
       </c>
       <c r="L32" t="n">
-        <v>111.25</v>
+        <v>73.13</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-8.15</v>
+        <v>-6.11</v>
       </c>
       <c r="K33" t="n">
-        <v>76.56</v>
+        <v>57.42</v>
       </c>
       <c r="L33" t="n">
-        <v>76.98999999999999</v>
+        <v>57.74</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>51.34</v>
+        <v>35.95</v>
       </c>
       <c r="K34" t="n">
-        <v>35.47</v>
+        <v>24.84</v>
       </c>
       <c r="L34" t="n">
-        <v>62.4</v>
+        <v>43.69</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>26.29</v>
+        <v>16.11</v>
       </c>
       <c r="K35" t="n">
-        <v>-167.69</v>
+        <v>-102.71</v>
       </c>
       <c r="L35" t="n">
-        <v>169.73</v>
+        <v>103.97</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>-27.02</v>
+        <v>-19.54</v>
       </c>
       <c r="K36" t="n">
-        <v>152.05</v>
+        <v>109.95</v>
       </c>
       <c r="L36" t="n">
-        <v>154.43</v>
+        <v>111.67</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>11.19</v>
+        <v>7.61</v>
       </c>
       <c r="K37" t="n">
-        <v>-103.34</v>
+        <v>-70.33</v>
       </c>
       <c r="L37" t="n">
-        <v>103.94</v>
+        <v>70.73999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>72.63</v>
+        <v>51.99</v>
       </c>
       <c r="K38" t="n">
-        <v>-181.65</v>
+        <v>-130.01</v>
       </c>
       <c r="L38" t="n">
-        <v>195.63</v>
+        <v>140.02</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>30</v>
       </c>
       <c r="J39" t="n">
-        <v>-138.93</v>
+        <v>-104.2</v>
       </c>
       <c r="K39" t="n">
-        <v>38.3</v>
+        <v>28.73</v>
       </c>
       <c r="L39" t="n">
-        <v>144.11</v>
+        <v>108.08</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>30</v>
       </c>
       <c r="J40" t="n">
-        <v>-98.81999999999999</v>
+        <v>-58.61</v>
       </c>
       <c r="K40" t="n">
-        <v>147.1</v>
+        <v>87.25</v>
       </c>
       <c r="L40" t="n">
-        <v>177.21</v>
+        <v>105.11</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-47.35</v>
+        <v>-30.93</v>
       </c>
       <c r="K41" t="n">
-        <v>276.17</v>
+        <v>180.4</v>
       </c>
       <c r="L41" t="n">
-        <v>280.2</v>
+        <v>183.03</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>30</v>
       </c>
       <c r="J42" t="n">
-        <v>218.35</v>
+        <v>144.09</v>
       </c>
       <c r="K42" t="n">
-        <v>35.01</v>
+        <v>23.1</v>
       </c>
       <c r="L42" t="n">
-        <v>221.14</v>
+        <v>145.93</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-280.78</v>
+        <v>-177.03</v>
       </c>
       <c r="K43" t="n">
-        <v>71.94</v>
+        <v>45.35</v>
       </c>
       <c r="L43" t="n">
-        <v>289.85</v>
+        <v>182.74</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-67.23999999999999</v>
+        <v>-42.08</v>
       </c>
       <c r="K44" t="n">
-        <v>71.09999999999999</v>
+        <v>44.5</v>
       </c>
       <c r="L44" t="n">
-        <v>97.86</v>
+        <v>61.24</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>30</v>
       </c>
       <c r="J45" t="n">
-        <v>-44.2</v>
+        <v>-28.32</v>
       </c>
       <c r="K45" t="n">
-        <v>-34.78</v>
+        <v>-22.28</v>
       </c>
       <c r="L45" t="n">
-        <v>56.24</v>
+        <v>36.04</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>25.88</v>
+        <v>15.85</v>
       </c>
       <c r="K46" t="n">
-        <v>-69.86</v>
+        <v>-42.78</v>
       </c>
       <c r="L46" t="n">
-        <v>74.5</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>-85.03</v>
+        <v>-54.64</v>
       </c>
       <c r="K47" t="n">
-        <v>-53.5</v>
+        <v>-34.38</v>
       </c>
       <c r="L47" t="n">
-        <v>100.47</v>
+        <v>64.56</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-24.97</v>
+        <v>-16.25</v>
       </c>
       <c r="K48" t="n">
-        <v>-49.83</v>
+        <v>-32.42</v>
       </c>
       <c r="L48" t="n">
-        <v>55.74</v>
+        <v>36.27</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>-74.92</v>
+        <v>-52.31</v>
       </c>
       <c r="K49" t="n">
-        <v>13.14</v>
+        <v>9.18</v>
       </c>
       <c r="L49" t="n">
-        <v>76.06</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>29</v>
       </c>
       <c r="J50" t="n">
-        <v>63</v>
+        <v>36.58</v>
       </c>
       <c r="K50" t="n">
-        <v>106.55</v>
+        <v>61.87</v>
       </c>
       <c r="L50" t="n">
-        <v>123.78</v>
+        <v>71.88</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>52.13</v>
+        <v>33.88</v>
       </c>
       <c r="K51" t="n">
-        <v>-128.42</v>
+        <v>-83.45</v>
       </c>
       <c r="L51" t="n">
-        <v>138.6</v>
+        <v>90.06999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>27</v>
       </c>
       <c r="J52" t="n">
-        <v>109.5</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>31.21</v>
+        <v>18.58</v>
       </c>
       <c r="L52" t="n">
-        <v>113.86</v>
+        <v>67.77</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>29</v>
       </c>
       <c r="J53" t="n">
-        <v>126.54</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>-24.46</v>
+        <v>-16.68</v>
       </c>
       <c r="L53" t="n">
-        <v>128.88</v>
+        <v>87.89</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>4.91</v>
+        <v>3.08</v>
       </c>
       <c r="K54" t="n">
-        <v>-239.6</v>
+        <v>-150.5</v>
       </c>
       <c r="L54" t="n">
-        <v>239.65</v>
+        <v>150.53</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>30</v>
       </c>
       <c r="J55" t="n">
-        <v>176.98</v>
+        <v>127.27</v>
       </c>
       <c r="K55" t="n">
-        <v>137.31</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>224</v>
+        <v>161.08</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>-70.79000000000001</v>
+        <v>-40.02</v>
       </c>
       <c r="K56" t="n">
-        <v>-295.61</v>
+        <v>-167.13</v>
       </c>
       <c r="L56" t="n">
-        <v>303.96</v>
+        <v>171.85</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-17.2</v>
+        <v>-12.77</v>
       </c>
       <c r="K57" t="n">
-        <v>-144.43</v>
+        <v>-107.27</v>
       </c>
       <c r="L57" t="n">
-        <v>145.45</v>
+        <v>108.03</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>30</v>
       </c>
       <c r="J58" t="n">
-        <v>46.58</v>
+        <v>28.55</v>
       </c>
       <c r="K58" t="n">
-        <v>274.24</v>
+        <v>168.1</v>
       </c>
       <c r="L58" t="n">
-        <v>278.16</v>
+        <v>170.51</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-54.85</v>
+        <v>-33.45</v>
       </c>
       <c r="K59" t="n">
-        <v>-64.87</v>
+        <v>-39.56</v>
       </c>
       <c r="L59" t="n">
-        <v>84.95</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>-76.97</v>
+        <v>-47.13</v>
       </c>
       <c r="K60" t="n">
-        <v>86.27</v>
+        <v>52.83</v>
       </c>
       <c r="L60" t="n">
-        <v>115.62</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>126.37</v>
+        <v>80</v>
       </c>
       <c r="K61" t="n">
-        <v>-48.76</v>
+        <v>-30.87</v>
       </c>
       <c r="L61" t="n">
-        <v>135.45</v>
+        <v>85.76000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>-49.08</v>
+        <v>-35.52</v>
       </c>
       <c r="K62" t="n">
-        <v>1.66</v>
+        <v>1.2</v>
       </c>
       <c r="L62" t="n">
-        <v>49.1</v>
+        <v>35.54</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-97.28</v>
+        <v>-52.89</v>
       </c>
       <c r="K63" t="n">
-        <v>-120.19</v>
+        <v>-65.34</v>
       </c>
       <c r="L63" t="n">
-        <v>154.63</v>
+        <v>84.06</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-38.04</v>
+        <v>-25.07</v>
       </c>
       <c r="K64" t="n">
-        <v>90.2</v>
+        <v>59.44</v>
       </c>
       <c r="L64" t="n">
-        <v>97.89</v>
+        <v>64.52</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>144.32</v>
+        <v>88.64</v>
       </c>
       <c r="K65" t="n">
-        <v>-82.17</v>
+        <v>-50.46</v>
       </c>
       <c r="L65" t="n">
-        <v>166.07</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>93.22</v>
+        <v>55.49</v>
       </c>
       <c r="K66" t="n">
-        <v>-46.92</v>
+        <v>-27.93</v>
       </c>
       <c r="L66" t="n">
-        <v>104.37</v>
+        <v>62.13</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>30</v>
       </c>
       <c r="J67" t="n">
-        <v>75.27</v>
+        <v>46.11</v>
       </c>
       <c r="K67" t="n">
-        <v>26.43</v>
+        <v>16.19</v>
       </c>
       <c r="L67" t="n">
-        <v>79.78</v>
+        <v>48.87</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-221.12</v>
+        <v>-146.05</v>
       </c>
       <c r="K68" t="n">
-        <v>-98.18000000000001</v>
+        <v>-64.84</v>
       </c>
       <c r="L68" t="n">
-        <v>241.94</v>
+        <v>159.8</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>-111.66</v>
+        <v>-80.67</v>
       </c>
       <c r="K69" t="n">
-        <v>103.22</v>
+        <v>74.58</v>
       </c>
       <c r="L69" t="n">
-        <v>152.06</v>
+        <v>109.87</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>49.98</v>
+        <v>30.98</v>
       </c>
       <c r="K70" t="n">
-        <v>-138.39</v>
+        <v>-85.79000000000001</v>
       </c>
       <c r="L70" t="n">
-        <v>147.14</v>
+        <v>91.20999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>-205.14</v>
+        <v>-138.22</v>
       </c>
       <c r="K71" t="n">
-        <v>-105.2</v>
+        <v>-70.88</v>
       </c>
       <c r="L71" t="n">
-        <v>230.54</v>
+        <v>155.33</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>20.38</v>
+        <v>11.77</v>
       </c>
       <c r="K72" t="n">
-        <v>-241.38</v>
+        <v>-139.39</v>
       </c>
       <c r="L72" t="n">
-        <v>242.23</v>
+        <v>139.89</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-56.13</v>
+        <v>-34.03</v>
       </c>
       <c r="K73" t="n">
-        <v>210.32</v>
+        <v>127.52</v>
       </c>
       <c r="L73" t="n">
-        <v>217.69</v>
+        <v>131.99</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>51.31</v>
+        <v>34.28</v>
       </c>
       <c r="K74" t="n">
-        <v>-56.06</v>
+        <v>-37.46</v>
       </c>
       <c r="L74" t="n">
-        <v>75.98999999999999</v>
+        <v>50.78</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>29</v>
       </c>
       <c r="J75" t="n">
-        <v>-40.41</v>
+        <v>-27.64</v>
       </c>
       <c r="K75" t="n">
-        <v>-18.8</v>
+        <v>-12.86</v>
       </c>
       <c r="L75" t="n">
-        <v>44.57</v>
+        <v>30.48</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>-73.26000000000001</v>
+        <v>-49.8</v>
       </c>
       <c r="K76" t="n">
-        <v>-60.41</v>
+        <v>-41.07</v>
       </c>
       <c r="L76" t="n">
-        <v>94.95999999999999</v>
+        <v>64.55</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>56.6</v>
+        <v>32.42</v>
       </c>
       <c r="K77" t="n">
-        <v>-96.61</v>
+        <v>-55.34</v>
       </c>
       <c r="L77" t="n">
-        <v>111.98</v>
+        <v>64.14</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>125.14</v>
+        <v>75.73</v>
       </c>
       <c r="K78" t="n">
-        <v>-72.73999999999999</v>
+        <v>-44.02</v>
       </c>
       <c r="L78" t="n">
-        <v>144.74</v>
+        <v>87.59</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-19.52</v>
+        <v>-12.19</v>
       </c>
       <c r="K79" t="n">
-        <v>-73.31999999999999</v>
+        <v>-45.78</v>
       </c>
       <c r="L79" t="n">
-        <v>75.87</v>
+        <v>47.38</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>78.56999999999999</v>
+        <v>49.88</v>
       </c>
       <c r="K80" t="n">
-        <v>-27.28</v>
+        <v>-17.32</v>
       </c>
       <c r="L80" t="n">
-        <v>83.17</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>12.21</v>
+        <v>7.91</v>
       </c>
       <c r="K81" t="n">
-        <v>-109.39</v>
+        <v>-70.87</v>
       </c>
       <c r="L81" t="n">
-        <v>110.07</v>
+        <v>71.31</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>14.72</v>
+        <v>10.02</v>
       </c>
       <c r="K82" t="n">
-        <v>-75.03</v>
+        <v>-51.06</v>
       </c>
       <c r="L82" t="n">
-        <v>76.45999999999999</v>
+        <v>52.03</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-107.46</v>
+        <v>-75.34999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>-40.14</v>
+        <v>-28.15</v>
       </c>
       <c r="L83" t="n">
-        <v>114.71</v>
+        <v>80.44</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>238</v>
+        <v>147.53</v>
       </c>
       <c r="K84" t="n">
-        <v>-113.87</v>
+        <v>-70.59</v>
       </c>
       <c r="L84" t="n">
-        <v>263.84</v>
+        <v>163.55</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>30</v>
       </c>
       <c r="J85" t="n">
-        <v>-43.05</v>
+        <v>-26.56</v>
       </c>
       <c r="K85" t="n">
-        <v>-95.55</v>
+        <v>-58.95</v>
       </c>
       <c r="L85" t="n">
-        <v>104.8</v>
+        <v>64.65000000000001</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-168.08</v>
+        <v>-122.17</v>
       </c>
       <c r="K86" t="n">
-        <v>-3.7</v>
+        <v>-2.69</v>
       </c>
       <c r="L86" t="n">
-        <v>168.12</v>
+        <v>122.2</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>24.19</v>
+        <v>17.79</v>
       </c>
       <c r="K87" t="n">
-        <v>162.92</v>
+        <v>119.84</v>
       </c>
       <c r="L87" t="n">
-        <v>164.7</v>
+        <v>121.15</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>-45.46</v>
+        <v>-28.39</v>
       </c>
       <c r="K88" t="n">
-        <v>282.83</v>
+        <v>176.63</v>
       </c>
       <c r="L88" t="n">
-        <v>286.46</v>
+        <v>178.9</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-09.xlsx
+++ b/output/2024-07-09.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-16.64</v>
+        <v>-16.36</v>
       </c>
       <c r="K14" t="n">
-        <v>-43.33</v>
+        <v>-42.61</v>
       </c>
       <c r="L14" t="n">
-        <v>46.41</v>
+        <v>45.64</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>21.41</v>
+        <v>22.75</v>
       </c>
       <c r="K15" t="n">
-        <v>-18.66</v>
+        <v>-19.83</v>
       </c>
       <c r="L15" t="n">
-        <v>28.4</v>
+        <v>30.18</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>16.58</v>
+        <v>17.31</v>
       </c>
       <c r="K16" t="n">
-        <v>-23.42</v>
+        <v>-24.46</v>
       </c>
       <c r="L16" t="n">
-        <v>28.7</v>
+        <v>29.97</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>29.87</v>
+        <v>31.56</v>
       </c>
       <c r="K17" t="n">
-        <v>-25.62</v>
+        <v>-27.08</v>
       </c>
       <c r="L17" t="n">
-        <v>39.35</v>
+        <v>41.58</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-24.48</v>
+        <v>-24.04</v>
       </c>
       <c r="K18" t="n">
-        <v>64.81999999999999</v>
+        <v>63.66</v>
       </c>
       <c r="L18" t="n">
-        <v>69.29000000000001</v>
+        <v>68.05</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>13.93</v>
+        <v>13.3</v>
       </c>
       <c r="K19" t="n">
-        <v>-96.78</v>
+        <v>-92.40000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>97.77</v>
+        <v>93.36</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-72.84</v>
+        <v>-73.69</v>
       </c>
       <c r="K20" t="n">
-        <v>19.96</v>
+        <v>20.19</v>
       </c>
       <c r="L20" t="n">
-        <v>75.52</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>64.06999999999999</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="L21" t="n">
-        <v>64.09999999999999</v>
+        <v>66.08</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>67.40000000000001</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-26.18</v>
+        <v>-26.73</v>
       </c>
       <c r="L22" t="n">
-        <v>72.3</v>
+        <v>73.83</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>-8.220000000000001</v>
+        <v>-8.74</v>
       </c>
       <c r="K23" t="n">
-        <v>-73.52</v>
+        <v>-78.17</v>
       </c>
       <c r="L23" t="n">
-        <v>73.98</v>
+        <v>78.66</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>31.69</v>
+        <v>32.88</v>
       </c>
       <c r="K24" t="n">
-        <v>-81.48999999999999</v>
+        <v>-84.53</v>
       </c>
       <c r="L24" t="n">
-        <v>87.43000000000001</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>98.90000000000001</v>
+        <v>101.31</v>
       </c>
       <c r="K25" t="n">
-        <v>3.07</v>
+        <v>3.14</v>
       </c>
       <c r="L25" t="n">
-        <v>98.95</v>
+        <v>101.36</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>-117.41</v>
+        <v>-118.34</v>
       </c>
       <c r="K26" t="n">
-        <v>-88.97</v>
+        <v>-89.67</v>
       </c>
       <c r="L26" t="n">
-        <v>147.31</v>
+        <v>148.48</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-81.02</v>
+        <v>-88.11</v>
       </c>
       <c r="K27" t="n">
-        <v>51.82</v>
+        <v>56.36</v>
       </c>
       <c r="L27" t="n">
-        <v>96.18000000000001</v>
+        <v>104.6</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>-61.01</v>
+        <v>-66.63</v>
       </c>
       <c r="K28" t="n">
-        <v>66.92</v>
+        <v>73.09</v>
       </c>
       <c r="L28" t="n">
-        <v>90.56</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>-16.08</v>
+        <v>-15.99</v>
       </c>
       <c r="K29" t="n">
-        <v>50.84</v>
+        <v>50.56</v>
       </c>
       <c r="L29" t="n">
-        <v>53.32</v>
+        <v>53.03</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-38.42</v>
+        <v>-39.05</v>
       </c>
       <c r="K30" t="n">
-        <v>24.53</v>
+        <v>24.93</v>
       </c>
       <c r="L30" t="n">
-        <v>45.58</v>
+        <v>46.33</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-24.31</v>
+        <v>-26.16</v>
       </c>
       <c r="K31" t="n">
-        <v>-11.5</v>
+        <v>-12.38</v>
       </c>
       <c r="L31" t="n">
-        <v>26.89</v>
+        <v>28.94</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>63.83</v>
+        <v>62.66</v>
       </c>
       <c r="K32" t="n">
-        <v>-35.69</v>
+        <v>-35.03</v>
       </c>
       <c r="L32" t="n">
-        <v>73.13</v>
+        <v>71.79000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-6.11</v>
+        <v>-6.1</v>
       </c>
       <c r="K33" t="n">
-        <v>57.42</v>
+        <v>57.36</v>
       </c>
       <c r="L33" t="n">
-        <v>57.74</v>
+        <v>57.68</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>35.95</v>
+        <v>37.51</v>
       </c>
       <c r="K34" t="n">
-        <v>24.84</v>
+        <v>25.91</v>
       </c>
       <c r="L34" t="n">
-        <v>43.69</v>
+        <v>45.59</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>16.11</v>
+        <v>15.96</v>
       </c>
       <c r="K35" t="n">
-        <v>-102.71</v>
+        <v>-101.79</v>
       </c>
       <c r="L35" t="n">
-        <v>103.97</v>
+        <v>103.03</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>-19.54</v>
+        <v>-18.89</v>
       </c>
       <c r="K36" t="n">
-        <v>109.95</v>
+        <v>106.28</v>
       </c>
       <c r="L36" t="n">
-        <v>111.67</v>
+        <v>107.94</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>7.61</v>
+        <v>7.85</v>
       </c>
       <c r="K37" t="n">
-        <v>-70.33</v>
+        <v>-72.48999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>70.73999999999999</v>
+        <v>72.91</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>51.99</v>
+        <v>50.48</v>
       </c>
       <c r="K38" t="n">
-        <v>-130.01</v>
+        <v>-126.25</v>
       </c>
       <c r="L38" t="n">
-        <v>140.02</v>
+        <v>135.97</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>30</v>
       </c>
       <c r="J39" t="n">
-        <v>-104.2</v>
+        <v>-103.62</v>
       </c>
       <c r="K39" t="n">
-        <v>28.73</v>
+        <v>28.57</v>
       </c>
       <c r="L39" t="n">
-        <v>108.08</v>
+        <v>107.49</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>30</v>
       </c>
       <c r="J40" t="n">
-        <v>-58.61</v>
+        <v>-60.13</v>
       </c>
       <c r="K40" t="n">
-        <v>87.25</v>
+        <v>89.51000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>105.11</v>
+        <v>107.83</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-30.93</v>
+        <v>-30.7</v>
       </c>
       <c r="K41" t="n">
-        <v>180.4</v>
+        <v>179.05</v>
       </c>
       <c r="L41" t="n">
-        <v>183.03</v>
+        <v>181.66</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>30</v>
       </c>
       <c r="J42" t="n">
-        <v>144.09</v>
+        <v>146.23</v>
       </c>
       <c r="K42" t="n">
-        <v>23.1</v>
+        <v>23.45</v>
       </c>
       <c r="L42" t="n">
-        <v>145.93</v>
+        <v>148.1</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-177.03</v>
+        <v>-176.77</v>
       </c>
       <c r="K43" t="n">
-        <v>45.35</v>
+        <v>45.29</v>
       </c>
       <c r="L43" t="n">
-        <v>182.74</v>
+        <v>182.48</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-42.08</v>
+        <v>-41.41</v>
       </c>
       <c r="K44" t="n">
-        <v>44.5</v>
+        <v>43.79</v>
       </c>
       <c r="L44" t="n">
-        <v>61.24</v>
+        <v>60.26</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>30</v>
       </c>
       <c r="J45" t="n">
-        <v>-28.32</v>
+        <v>-29.41</v>
       </c>
       <c r="K45" t="n">
-        <v>-22.28</v>
+        <v>-23.14</v>
       </c>
       <c r="L45" t="n">
-        <v>36.04</v>
+        <v>37.42</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>15.85</v>
+        <v>16.24</v>
       </c>
       <c r="K46" t="n">
-        <v>-42.78</v>
+        <v>-43.84</v>
       </c>
       <c r="L46" t="n">
-        <v>45.62</v>
+        <v>46.76</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>-54.64</v>
+        <v>-54.3</v>
       </c>
       <c r="K47" t="n">
-        <v>-34.38</v>
+        <v>-34.17</v>
       </c>
       <c r="L47" t="n">
-        <v>64.56</v>
+        <v>64.15000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-16.25</v>
+        <v>-17.58</v>
       </c>
       <c r="K48" t="n">
-        <v>-32.42</v>
+        <v>-35.07</v>
       </c>
       <c r="L48" t="n">
-        <v>36.27</v>
+        <v>39.23</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>-52.31</v>
+        <v>-53.12</v>
       </c>
       <c r="K49" t="n">
-        <v>9.18</v>
+        <v>9.32</v>
       </c>
       <c r="L49" t="n">
-        <v>53.11</v>
+        <v>53.94</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>29</v>
       </c>
       <c r="J50" t="n">
-        <v>36.58</v>
+        <v>37.74</v>
       </c>
       <c r="K50" t="n">
-        <v>61.87</v>
+        <v>63.83</v>
       </c>
       <c r="L50" t="n">
-        <v>71.88</v>
+        <v>74.15000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>33.88</v>
+        <v>34.24</v>
       </c>
       <c r="K51" t="n">
-        <v>-83.45</v>
+        <v>-84.34</v>
       </c>
       <c r="L51" t="n">
-        <v>90.06999999999999</v>
+        <v>91.02</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>27</v>
       </c>
       <c r="J52" t="n">
-        <v>65.18000000000001</v>
+        <v>68.25</v>
       </c>
       <c r="K52" t="n">
-        <v>18.58</v>
+        <v>19.45</v>
       </c>
       <c r="L52" t="n">
-        <v>67.77</v>
+        <v>70.97</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>29</v>
       </c>
       <c r="J53" t="n">
-        <v>86.29000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="K53" t="n">
-        <v>-16.68</v>
+        <v>-17.3</v>
       </c>
       <c r="L53" t="n">
-        <v>87.89</v>
+        <v>91.15000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="K54" t="n">
-        <v>-150.5</v>
+        <v>-147.61</v>
       </c>
       <c r="L54" t="n">
-        <v>150.53</v>
+        <v>147.65</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>30</v>
       </c>
       <c r="J55" t="n">
-        <v>127.27</v>
+        <v>122.21</v>
       </c>
       <c r="K55" t="n">
-        <v>98.73999999999999</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>161.08</v>
+        <v>154.68</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>-40.02</v>
+        <v>-40.51</v>
       </c>
       <c r="K56" t="n">
-        <v>-167.13</v>
+        <v>-169.15</v>
       </c>
       <c r="L56" t="n">
-        <v>171.85</v>
+        <v>173.94</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-12.77</v>
+        <v>-13.83</v>
       </c>
       <c r="K57" t="n">
-        <v>-107.27</v>
+        <v>-116.18</v>
       </c>
       <c r="L57" t="n">
-        <v>108.03</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>30</v>
       </c>
       <c r="J58" t="n">
-        <v>28.55</v>
+        <v>28.57</v>
       </c>
       <c r="K58" t="n">
-        <v>168.1</v>
+        <v>168.22</v>
       </c>
       <c r="L58" t="n">
-        <v>170.51</v>
+        <v>170.63</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-33.45</v>
+        <v>-33.59</v>
       </c>
       <c r="K59" t="n">
-        <v>-39.56</v>
+        <v>-39.72</v>
       </c>
       <c r="L59" t="n">
-        <v>51.8</v>
+        <v>52.02</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>-47.13</v>
+        <v>-45.36</v>
       </c>
       <c r="K60" t="n">
-        <v>52.83</v>
+        <v>50.84</v>
       </c>
       <c r="L60" t="n">
-        <v>70.8</v>
+        <v>68.13</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>80</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>-30.87</v>
+        <v>-29.45</v>
       </c>
       <c r="L61" t="n">
-        <v>85.76000000000001</v>
+        <v>81.81</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>-35.52</v>
+        <v>-38.24</v>
       </c>
       <c r="K62" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="L62" t="n">
-        <v>35.54</v>
+        <v>38.26</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-52.89</v>
+        <v>-52.13</v>
       </c>
       <c r="K63" t="n">
-        <v>-65.34</v>
+        <v>-64.40000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>84.06</v>
+        <v>82.86</v>
       </c>
     </row>
     <row r="64">
@@ -2743,7 +2743,7 @@
         <v>-25.07</v>
       </c>
       <c r="K64" t="n">
-        <v>59.44</v>
+        <v>59.45</v>
       </c>
       <c r="L64" t="n">
         <v>64.52</v>
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>88.64</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>-50.46</v>
+        <v>-50.25</v>
       </c>
       <c r="L65" t="n">
-        <v>102</v>
+        <v>101.57</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>55.49</v>
+        <v>59.02</v>
       </c>
       <c r="K66" t="n">
-        <v>-27.93</v>
+        <v>-29.71</v>
       </c>
       <c r="L66" t="n">
-        <v>62.13</v>
+        <v>66.06999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>30</v>
       </c>
       <c r="J67" t="n">
-        <v>46.11</v>
+        <v>50.46</v>
       </c>
       <c r="K67" t="n">
-        <v>16.19</v>
+        <v>17.72</v>
       </c>
       <c r="L67" t="n">
-        <v>48.87</v>
+        <v>53.48</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-146.05</v>
+        <v>-142.2</v>
       </c>
       <c r="K68" t="n">
-        <v>-64.84</v>
+        <v>-63.14</v>
       </c>
       <c r="L68" t="n">
-        <v>159.8</v>
+        <v>155.59</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>-80.67</v>
+        <v>-80.40000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>74.58</v>
+        <v>74.33</v>
       </c>
       <c r="L69" t="n">
-        <v>109.87</v>
+        <v>109.49</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>30.98</v>
+        <v>32.4</v>
       </c>
       <c r="K70" t="n">
-        <v>-85.79000000000001</v>
+        <v>-89.72</v>
       </c>
       <c r="L70" t="n">
-        <v>91.20999999999999</v>
+        <v>95.39</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>-138.22</v>
+        <v>-139.49</v>
       </c>
       <c r="K71" t="n">
-        <v>-70.88</v>
+        <v>-71.53</v>
       </c>
       <c r="L71" t="n">
-        <v>155.33</v>
+        <v>156.76</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>11.77</v>
+        <v>12.16</v>
       </c>
       <c r="K72" t="n">
-        <v>-139.39</v>
+        <v>-144.06</v>
       </c>
       <c r="L72" t="n">
-        <v>139.89</v>
+        <v>144.57</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-34.03</v>
+        <v>-35.18</v>
       </c>
       <c r="K73" t="n">
-        <v>127.52</v>
+        <v>131.81</v>
       </c>
       <c r="L73" t="n">
-        <v>131.99</v>
+        <v>136.42</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>34.28</v>
+        <v>33.89</v>
       </c>
       <c r="K74" t="n">
-        <v>-37.46</v>
+        <v>-37.03</v>
       </c>
       <c r="L74" t="n">
-        <v>50.78</v>
+        <v>50.19</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>29</v>
       </c>
       <c r="J75" t="n">
-        <v>-27.64</v>
+        <v>-28.78</v>
       </c>
       <c r="K75" t="n">
-        <v>-12.86</v>
+        <v>-13.39</v>
       </c>
       <c r="L75" t="n">
-        <v>30.48</v>
+        <v>31.74</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>-49.8</v>
+        <v>-47.6</v>
       </c>
       <c r="K76" t="n">
-        <v>-41.07</v>
+        <v>-39.25</v>
       </c>
       <c r="L76" t="n">
-        <v>64.55</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>32.42</v>
+        <v>32.68</v>
       </c>
       <c r="K77" t="n">
-        <v>-55.34</v>
+        <v>-55.79</v>
       </c>
       <c r="L77" t="n">
-        <v>64.14</v>
+        <v>64.65000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>75.73</v>
+        <v>73.34</v>
       </c>
       <c r="K78" t="n">
-        <v>-44.02</v>
+        <v>-42.63</v>
       </c>
       <c r="L78" t="n">
-        <v>87.59</v>
+        <v>84.83</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-12.19</v>
+        <v>-12.58</v>
       </c>
       <c r="K79" t="n">
-        <v>-45.78</v>
+        <v>-47.26</v>
       </c>
       <c r="L79" t="n">
-        <v>47.38</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>49.88</v>
+        <v>53.66</v>
       </c>
       <c r="K80" t="n">
-        <v>-17.32</v>
+        <v>-18.63</v>
       </c>
       <c r="L80" t="n">
-        <v>52.8</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>7.91</v>
+        <v>8.08</v>
       </c>
       <c r="K81" t="n">
-        <v>-70.87</v>
+        <v>-72.41</v>
       </c>
       <c r="L81" t="n">
-        <v>71.31</v>
+        <v>72.86</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>10.02</v>
+        <v>10.71</v>
       </c>
       <c r="K82" t="n">
-        <v>-51.06</v>
+        <v>-54.59</v>
       </c>
       <c r="L82" t="n">
-        <v>52.03</v>
+        <v>55.64</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-75.34999999999999</v>
+        <v>-79.40000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>-28.15</v>
+        <v>-29.66</v>
       </c>
       <c r="L83" t="n">
-        <v>80.44</v>
+        <v>84.76000000000001</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>147.53</v>
+        <v>143.61</v>
       </c>
       <c r="K84" t="n">
-        <v>-70.59</v>
+        <v>-68.70999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>163.55</v>
+        <v>159.2</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>30</v>
       </c>
       <c r="J85" t="n">
-        <v>-26.56</v>
+        <v>-29.08</v>
       </c>
       <c r="K85" t="n">
-        <v>-58.95</v>
+        <v>-64.54000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>64.65000000000001</v>
+        <v>70.78</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-122.17</v>
+        <v>-127.78</v>
       </c>
       <c r="K86" t="n">
-        <v>-2.69</v>
+        <v>-2.81</v>
       </c>
       <c r="L86" t="n">
-        <v>122.2</v>
+        <v>127.81</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>17.79</v>
+        <v>18.3</v>
       </c>
       <c r="K87" t="n">
-        <v>119.84</v>
+        <v>123.28</v>
       </c>
       <c r="L87" t="n">
-        <v>121.15</v>
+        <v>124.63</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>-28.39</v>
+        <v>-28.06</v>
       </c>
       <c r="K88" t="n">
-        <v>176.63</v>
+        <v>174.59</v>
       </c>
       <c r="L88" t="n">
-        <v>178.9</v>
+        <v>176.83</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-09.xlsx
+++ b/output/2024-07-09.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-16.36</v>
+        <v>-16.05</v>
       </c>
       <c r="K14" t="n">
-        <v>-42.61</v>
+        <v>-41.78</v>
       </c>
       <c r="L14" t="n">
-        <v>45.64</v>
+        <v>44.76</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>22.75</v>
+        <v>24.28</v>
       </c>
       <c r="K15" t="n">
-        <v>-19.83</v>
+        <v>-21.16</v>
       </c>
       <c r="L15" t="n">
-        <v>30.18</v>
+        <v>32.21</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>17.31</v>
+        <v>18.15</v>
       </c>
       <c r="K16" t="n">
-        <v>-24.46</v>
+        <v>-25.64</v>
       </c>
       <c r="L16" t="n">
-        <v>29.97</v>
+        <v>31.41</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>31.56</v>
+        <v>33.49</v>
       </c>
       <c r="K17" t="n">
-        <v>-27.08</v>
+        <v>-28.73</v>
       </c>
       <c r="L17" t="n">
-        <v>41.58</v>
+        <v>44.13</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-24.04</v>
+        <v>-23.54</v>
       </c>
       <c r="K18" t="n">
-        <v>63.66</v>
+        <v>62.34</v>
       </c>
       <c r="L18" t="n">
-        <v>68.05</v>
+        <v>66.64</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>13.3</v>
+        <v>12.58</v>
       </c>
       <c r="K19" t="n">
-        <v>-92.40000000000001</v>
+        <v>-87.41</v>
       </c>
       <c r="L19" t="n">
-        <v>93.36</v>
+        <v>88.31</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-73.69</v>
+        <v>-74.65000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>20.19</v>
+        <v>20.45</v>
       </c>
       <c r="L20" t="n">
-        <v>76.40000000000001</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>66.04000000000001</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="L21" t="n">
-        <v>66.08</v>
+        <v>68.33</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>68.81999999999999</v>
+        <v>70.45</v>
       </c>
       <c r="K22" t="n">
-        <v>-26.73</v>
+        <v>-27.36</v>
       </c>
       <c r="L22" t="n">
-        <v>73.83</v>
+        <v>75.58</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>-8.74</v>
+        <v>-9.34</v>
       </c>
       <c r="K23" t="n">
-        <v>-78.17</v>
+        <v>-83.48</v>
       </c>
       <c r="L23" t="n">
-        <v>78.66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>32.88</v>
+        <v>34.23</v>
       </c>
       <c r="K24" t="n">
-        <v>-84.53</v>
+        <v>-88.01000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>90.7</v>
+        <v>94.44</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>101.31</v>
+        <v>104.06</v>
       </c>
       <c r="K25" t="n">
-        <v>3.14</v>
+        <v>3.23</v>
       </c>
       <c r="L25" t="n">
-        <v>101.36</v>
+        <v>104.11</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>-118.34</v>
+        <v>-119.4</v>
       </c>
       <c r="K26" t="n">
-        <v>-89.67</v>
+        <v>-90.48</v>
       </c>
       <c r="L26" t="n">
-        <v>148.48</v>
+        <v>149.81</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-88.11</v>
+        <v>-96.22</v>
       </c>
       <c r="K27" t="n">
-        <v>56.36</v>
+        <v>61.55</v>
       </c>
       <c r="L27" t="n">
-        <v>104.6</v>
+        <v>114.23</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>-66.63</v>
+        <v>-73.05</v>
       </c>
       <c r="K28" t="n">
-        <v>73.09</v>
+        <v>80.14</v>
       </c>
       <c r="L28" t="n">
-        <v>98.90000000000001</v>
+        <v>108.44</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>-15.99</v>
+        <v>-15.89</v>
       </c>
       <c r="K29" t="n">
-        <v>50.56</v>
+        <v>50.24</v>
       </c>
       <c r="L29" t="n">
-        <v>53.03</v>
+        <v>52.69</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-39.05</v>
+        <v>-39.78</v>
       </c>
       <c r="K30" t="n">
-        <v>24.93</v>
+        <v>25.39</v>
       </c>
       <c r="L30" t="n">
-        <v>46.33</v>
+        <v>47.19</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-26.16</v>
+        <v>-28.27</v>
       </c>
       <c r="K31" t="n">
-        <v>-12.38</v>
+        <v>-13.37</v>
       </c>
       <c r="L31" t="n">
-        <v>28.94</v>
+        <v>31.27</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>62.66</v>
+        <v>61.31</v>
       </c>
       <c r="K32" t="n">
-        <v>-35.03</v>
+        <v>-34.28</v>
       </c>
       <c r="L32" t="n">
-        <v>71.79000000000001</v>
+        <v>70.25</v>
       </c>
     </row>
     <row r="33">
@@ -1441,10 +1441,10 @@
         <v>-6.1</v>
       </c>
       <c r="K33" t="n">
-        <v>57.36</v>
+        <v>57.29</v>
       </c>
       <c r="L33" t="n">
-        <v>57.68</v>
+        <v>57.62</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>37.51</v>
+        <v>39.29</v>
       </c>
       <c r="K34" t="n">
-        <v>25.91</v>
+        <v>27.15</v>
       </c>
       <c r="L34" t="n">
-        <v>45.59</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>15.96</v>
+        <v>15.79</v>
       </c>
       <c r="K35" t="n">
-        <v>-101.79</v>
+        <v>-100.73</v>
       </c>
       <c r="L35" t="n">
-        <v>103.03</v>
+        <v>101.96</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>-18.89</v>
+        <v>-18.14</v>
       </c>
       <c r="K36" t="n">
-        <v>106.28</v>
+        <v>102.09</v>
       </c>
       <c r="L36" t="n">
-        <v>107.94</v>
+        <v>103.68</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>7.85</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>-72.48999999999999</v>
+        <v>-74.95999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>72.91</v>
+        <v>75.39</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>50.48</v>
+        <v>48.76</v>
       </c>
       <c r="K38" t="n">
-        <v>-126.25</v>
+        <v>-121.95</v>
       </c>
       <c r="L38" t="n">
-        <v>135.97</v>
+        <v>131.34</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>30</v>
       </c>
       <c r="J39" t="n">
-        <v>-103.62</v>
+        <v>-102.96</v>
       </c>
       <c r="K39" t="n">
-        <v>28.57</v>
+        <v>28.39</v>
       </c>
       <c r="L39" t="n">
-        <v>107.49</v>
+        <v>106.8</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>30</v>
       </c>
       <c r="J40" t="n">
-        <v>-60.13</v>
+        <v>-61.86</v>
       </c>
       <c r="K40" t="n">
-        <v>89.51000000000001</v>
+        <v>92.08</v>
       </c>
       <c r="L40" t="n">
-        <v>107.83</v>
+        <v>110.93</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-30.7</v>
+        <v>-30.43</v>
       </c>
       <c r="K41" t="n">
-        <v>179.05</v>
+        <v>177.51</v>
       </c>
       <c r="L41" t="n">
-        <v>181.66</v>
+        <v>180.1</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>30</v>
       </c>
       <c r="J42" t="n">
-        <v>146.23</v>
+        <v>148.68</v>
       </c>
       <c r="K42" t="n">
-        <v>23.45</v>
+        <v>23.84</v>
       </c>
       <c r="L42" t="n">
-        <v>148.1</v>
+        <v>150.58</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-176.77</v>
+        <v>-176.48</v>
       </c>
       <c r="K43" t="n">
-        <v>45.29</v>
+        <v>45.21</v>
       </c>
       <c r="L43" t="n">
-        <v>182.48</v>
+        <v>182.18</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-41.41</v>
+        <v>-40.64</v>
       </c>
       <c r="K44" t="n">
-        <v>43.79</v>
+        <v>42.97</v>
       </c>
       <c r="L44" t="n">
-        <v>60.26</v>
+        <v>59.15</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>30</v>
       </c>
       <c r="J45" t="n">
-        <v>-29.41</v>
+        <v>-30.64</v>
       </c>
       <c r="K45" t="n">
-        <v>-23.14</v>
+        <v>-24.11</v>
       </c>
       <c r="L45" t="n">
-        <v>37.42</v>
+        <v>38.99</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>16.24</v>
+        <v>16.69</v>
       </c>
       <c r="K46" t="n">
-        <v>-43.84</v>
+        <v>-45.06</v>
       </c>
       <c r="L46" t="n">
-        <v>46.76</v>
+        <v>48.05</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>-54.3</v>
+        <v>-53.91</v>
       </c>
       <c r="K47" t="n">
-        <v>-34.17</v>
+        <v>-33.92</v>
       </c>
       <c r="L47" t="n">
-        <v>64.15000000000001</v>
+        <v>63.69</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-17.58</v>
+        <v>-19.09</v>
       </c>
       <c r="K48" t="n">
-        <v>-35.07</v>
+        <v>-38.1</v>
       </c>
       <c r="L48" t="n">
-        <v>39.23</v>
+        <v>42.62</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>-53.12</v>
+        <v>-54.06</v>
       </c>
       <c r="K49" t="n">
-        <v>9.32</v>
+        <v>9.48</v>
       </c>
       <c r="L49" t="n">
-        <v>53.94</v>
+        <v>54.88</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>29</v>
       </c>
       <c r="J50" t="n">
-        <v>37.74</v>
+        <v>39.06</v>
       </c>
       <c r="K50" t="n">
-        <v>63.83</v>
+        <v>66.06</v>
       </c>
       <c r="L50" t="n">
-        <v>74.15000000000001</v>
+        <v>76.75</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>34.24</v>
+        <v>34.65</v>
       </c>
       <c r="K51" t="n">
-        <v>-84.34</v>
+        <v>-85.34999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>91.02</v>
+        <v>92.12</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>27</v>
       </c>
       <c r="J52" t="n">
-        <v>68.25</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>19.45</v>
+        <v>20.45</v>
       </c>
       <c r="L52" t="n">
-        <v>70.97</v>
+        <v>74.61</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>29</v>
       </c>
       <c r="J53" t="n">
-        <v>89.5</v>
+        <v>93.16</v>
       </c>
       <c r="K53" t="n">
-        <v>-17.3</v>
+        <v>-18.01</v>
       </c>
       <c r="L53" t="n">
-        <v>91.15000000000001</v>
+        <v>94.89</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="K54" t="n">
-        <v>-147.61</v>
+        <v>-144.31</v>
       </c>
       <c r="L54" t="n">
-        <v>147.65</v>
+        <v>144.34</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>30</v>
       </c>
       <c r="J55" t="n">
-        <v>122.21</v>
+        <v>116.43</v>
       </c>
       <c r="K55" t="n">
-        <v>94.81999999999999</v>
+        <v>90.33</v>
       </c>
       <c r="L55" t="n">
-        <v>154.68</v>
+        <v>147.36</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>-40.51</v>
+        <v>-40.94</v>
       </c>
       <c r="K56" t="n">
-        <v>-169.15</v>
+        <v>-170.95</v>
       </c>
       <c r="L56" t="n">
-        <v>173.94</v>
+        <v>175.79</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-13.83</v>
+        <v>-15.05</v>
       </c>
       <c r="K57" t="n">
-        <v>-116.18</v>
+        <v>-126.36</v>
       </c>
       <c r="L57" t="n">
-        <v>117</v>
+        <v>127.26</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>30</v>
       </c>
       <c r="J58" t="n">
-        <v>28.57</v>
+        <v>28.6</v>
       </c>
       <c r="K58" t="n">
-        <v>168.22</v>
+        <v>168.36</v>
       </c>
       <c r="L58" t="n">
-        <v>170.63</v>
+        <v>170.77</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-33.59</v>
+        <v>-33.75</v>
       </c>
       <c r="K59" t="n">
-        <v>-39.72</v>
+        <v>-39.91</v>
       </c>
       <c r="L59" t="n">
-        <v>52.02</v>
+        <v>52.26</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>-45.36</v>
+        <v>-43.33</v>
       </c>
       <c r="K60" t="n">
-        <v>50.84</v>
+        <v>48.57</v>
       </c>
       <c r="L60" t="n">
-        <v>68.13</v>
+        <v>65.09</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>76.31999999999999</v>
+        <v>72.12</v>
       </c>
       <c r="K61" t="n">
-        <v>-29.45</v>
+        <v>-27.83</v>
       </c>
       <c r="L61" t="n">
-        <v>81.81</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>-38.24</v>
+        <v>-41.34</v>
       </c>
       <c r="K62" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="L62" t="n">
-        <v>38.26</v>
+        <v>41.36</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-52.13</v>
+        <v>-51.26</v>
       </c>
       <c r="K63" t="n">
-        <v>-64.40000000000001</v>
+        <v>-63.33</v>
       </c>
       <c r="L63" t="n">
-        <v>82.86</v>
+        <v>81.48</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-25.07</v>
+        <v>-25.08</v>
       </c>
       <c r="K64" t="n">
-        <v>59.45</v>
+        <v>59.46</v>
       </c>
       <c r="L64" t="n">
-        <v>64.52</v>
+        <v>64.53</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>88.26000000000001</v>
+        <v>87.84</v>
       </c>
       <c r="K65" t="n">
-        <v>-50.25</v>
+        <v>-50.01</v>
       </c>
       <c r="L65" t="n">
-        <v>101.57</v>
+        <v>101.07</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>59.02</v>
+        <v>63.05</v>
       </c>
       <c r="K66" t="n">
-        <v>-29.71</v>
+        <v>-31.74</v>
       </c>
       <c r="L66" t="n">
-        <v>66.06999999999999</v>
+        <v>70.59</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>30</v>
       </c>
       <c r="J67" t="n">
-        <v>50.46</v>
+        <v>55.43</v>
       </c>
       <c r="K67" t="n">
-        <v>17.72</v>
+        <v>19.46</v>
       </c>
       <c r="L67" t="n">
-        <v>53.48</v>
+        <v>58.75</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-142.2</v>
+        <v>-137.81</v>
       </c>
       <c r="K68" t="n">
-        <v>-63.14</v>
+        <v>-61.19</v>
       </c>
       <c r="L68" t="n">
-        <v>155.59</v>
+        <v>150.78</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>-80.40000000000001</v>
+        <v>-80.08</v>
       </c>
       <c r="K69" t="n">
-        <v>74.33</v>
+        <v>74.03</v>
       </c>
       <c r="L69" t="n">
-        <v>109.49</v>
+        <v>109.06</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>32.4</v>
+        <v>34.02</v>
       </c>
       <c r="K70" t="n">
-        <v>-89.72</v>
+        <v>-94.20999999999999</v>
       </c>
       <c r="L70" t="n">
-        <v>95.39</v>
+        <v>100.16</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>-139.49</v>
+        <v>-140.95</v>
       </c>
       <c r="K71" t="n">
-        <v>-71.53</v>
+        <v>-72.28</v>
       </c>
       <c r="L71" t="n">
-        <v>156.76</v>
+        <v>158.41</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>12.16</v>
+        <v>12.62</v>
       </c>
       <c r="K72" t="n">
-        <v>-144.06</v>
+        <v>-149.4</v>
       </c>
       <c r="L72" t="n">
-        <v>144.57</v>
+        <v>149.93</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-35.18</v>
+        <v>-36.49</v>
       </c>
       <c r="K73" t="n">
-        <v>131.81</v>
+        <v>136.71</v>
       </c>
       <c r="L73" t="n">
-        <v>136.42</v>
+        <v>141.49</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>33.89</v>
+        <v>33.44</v>
       </c>
       <c r="K74" t="n">
-        <v>-37.03</v>
+        <v>-36.53</v>
       </c>
       <c r="L74" t="n">
-        <v>50.19</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>29</v>
       </c>
       <c r="J75" t="n">
-        <v>-28.78</v>
+        <v>-30.08</v>
       </c>
       <c r="K75" t="n">
-        <v>-13.39</v>
+        <v>-14</v>
       </c>
       <c r="L75" t="n">
-        <v>31.74</v>
+        <v>33.18</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>-47.6</v>
+        <v>-45.08</v>
       </c>
       <c r="K76" t="n">
-        <v>-39.25</v>
+        <v>-37.18</v>
       </c>
       <c r="L76" t="n">
-        <v>61.7</v>
+        <v>58.44</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>32.68</v>
+        <v>32.98</v>
       </c>
       <c r="K77" t="n">
-        <v>-55.79</v>
+        <v>-56.29</v>
       </c>
       <c r="L77" t="n">
-        <v>64.65000000000001</v>
+        <v>65.23999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>73.34</v>
+        <v>70.61</v>
       </c>
       <c r="K78" t="n">
-        <v>-42.63</v>
+        <v>-41.04</v>
       </c>
       <c r="L78" t="n">
-        <v>84.83</v>
+        <v>81.67</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-12.58</v>
+        <v>-13.03</v>
       </c>
       <c r="K79" t="n">
-        <v>-47.26</v>
+        <v>-48.94</v>
       </c>
       <c r="L79" t="n">
-        <v>48.9</v>
+        <v>50.65</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>53.66</v>
+        <v>57.98</v>
       </c>
       <c r="K80" t="n">
-        <v>-18.63</v>
+        <v>-20.13</v>
       </c>
       <c r="L80" t="n">
-        <v>56.8</v>
+        <v>61.38</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>8.08</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>-72.41</v>
+        <v>-74.17</v>
       </c>
       <c r="L81" t="n">
-        <v>72.86</v>
+        <v>74.63</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>10.71</v>
+        <v>11.51</v>
       </c>
       <c r="K82" t="n">
-        <v>-54.59</v>
+        <v>-58.64</v>
       </c>
       <c r="L82" t="n">
-        <v>55.64</v>
+        <v>59.75</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-79.40000000000001</v>
+        <v>-84.03</v>
       </c>
       <c r="K83" t="n">
-        <v>-29.66</v>
+        <v>-31.39</v>
       </c>
       <c r="L83" t="n">
-        <v>84.76000000000001</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>143.61</v>
+        <v>139.12</v>
       </c>
       <c r="K84" t="n">
-        <v>-68.70999999999999</v>
+        <v>-66.56</v>
       </c>
       <c r="L84" t="n">
-        <v>159.2</v>
+        <v>154.22</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>30</v>
       </c>
       <c r="J85" t="n">
-        <v>-29.08</v>
+        <v>-31.95</v>
       </c>
       <c r="K85" t="n">
-        <v>-64.54000000000001</v>
+        <v>-70.92</v>
       </c>
       <c r="L85" t="n">
-        <v>70.78</v>
+        <v>77.79000000000001</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-127.78</v>
+        <v>-134.2</v>
       </c>
       <c r="K86" t="n">
-        <v>-2.81</v>
+        <v>-2.96</v>
       </c>
       <c r="L86" t="n">
-        <v>127.81</v>
+        <v>134.23</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>18.3</v>
+        <v>18.89</v>
       </c>
       <c r="K87" t="n">
-        <v>123.28</v>
+        <v>127.21</v>
       </c>
       <c r="L87" t="n">
-        <v>124.63</v>
+        <v>128.61</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>-28.06</v>
+        <v>-27.69</v>
       </c>
       <c r="K88" t="n">
-        <v>174.59</v>
+        <v>172.26</v>
       </c>
       <c r="L88" t="n">
-        <v>176.83</v>
+        <v>174.47</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-09.xlsx
+++ b/output/2024-07-09.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="F14" t="n">
-        <v>8.5</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>253.5</v>
+        <v>262.6</v>
       </c>
       <c r="H14" t="n">
-        <v>50.6</v>
+        <v>53.3</v>
       </c>
       <c r="I14" t="n">
+        <v>18</v>
+      </c>
+      <c r="J14" t="n">
         <v>29</v>
       </c>
-      <c r="J14" t="n">
-        <v>-16.05</v>
-      </c>
       <c r="K14" t="n">
-        <v>-41.78</v>
+        <v>-42.43</v>
       </c>
       <c r="L14" t="n">
-        <v>44.76</v>
+        <v>51.39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:44:57</t>
+          <t>04:45:24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="F15" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="G15" t="n">
-        <v>259.5</v>
+        <v>269.8</v>
       </c>
       <c r="H15" t="n">
-        <v>49.7</v>
+        <v>51</v>
       </c>
       <c r="I15" t="n">
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>24.28</v>
+        <v>33.94</v>
       </c>
       <c r="K15" t="n">
-        <v>-21.16</v>
+        <v>-29.25</v>
       </c>
       <c r="L15" t="n">
-        <v>32.21</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:46:45</t>
+          <t>04:46:46</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="F16" t="n">
-        <v>8.970000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="G16" t="n">
-        <v>276.5</v>
+        <v>262.6</v>
       </c>
       <c r="H16" t="n">
-        <v>51.1</v>
+        <v>46.7</v>
       </c>
       <c r="I16" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>18.15</v>
+        <v>-21.4</v>
       </c>
       <c r="K16" t="n">
-        <v>-25.64</v>
+        <v>56.57</v>
       </c>
       <c r="L16" t="n">
-        <v>31.41</v>
+        <v>60.48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:52:10</t>
+          <t>04:51:03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="F17" t="n">
-        <v>9.32</v>
+        <v>5.76</v>
       </c>
       <c r="G17" t="n">
-        <v>271.9</v>
+        <v>262.1</v>
       </c>
       <c r="H17" t="n">
-        <v>43.4</v>
+        <v>46.3</v>
       </c>
       <c r="I17" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>33.49</v>
+        <v>13.52</v>
       </c>
       <c r="K17" t="n">
-        <v>-28.73</v>
+        <v>-101.65</v>
       </c>
       <c r="L17" t="n">
-        <v>44.13</v>
+        <v>102.54</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:53:05</t>
+          <t>04:52:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="F18" t="n">
-        <v>8.960000000000001</v>
+        <v>6.67</v>
       </c>
       <c r="G18" t="n">
-        <v>263.2</v>
+        <v>252.8</v>
       </c>
       <c r="H18" t="n">
-        <v>51</v>
+        <v>49.3</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>-23.54</v>
+        <v>-71.95</v>
       </c>
       <c r="K18" t="n">
-        <v>62.34</v>
+        <v>18.79</v>
       </c>
       <c r="L18" t="n">
-        <v>66.64</v>
+        <v>74.36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:55:20</t>
+          <t>04:53:47</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.17</v>
+        <v>1.12</v>
       </c>
       <c r="F19" t="n">
-        <v>8.94</v>
+        <v>1.42</v>
       </c>
       <c r="G19" t="n">
-        <v>262.4</v>
+        <v>265.6</v>
       </c>
       <c r="H19" t="n">
-        <v>51.7</v>
+        <v>56.5</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>12.58</v>
+        <v>46.07</v>
       </c>
       <c r="K19" t="n">
-        <v>-87.41</v>
+        <v>1.09</v>
       </c>
       <c r="L19" t="n">
-        <v>88.31</v>
+        <v>46.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:01:15</t>
+          <t>04:58:33</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="F20" t="n">
-        <v>8.48</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>268.6</v>
+        <v>266.2</v>
       </c>
       <c r="H20" t="n">
-        <v>47.3</v>
+        <v>49.9</v>
       </c>
       <c r="I20" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>-74.65000000000001</v>
+        <v>90.28</v>
       </c>
       <c r="K20" t="n">
-        <v>20.45</v>
+        <v>-39.24</v>
       </c>
       <c r="L20" t="n">
-        <v>77.40000000000001</v>
+        <v>98.43000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:03:07</t>
+          <t>05:00:17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.14</v>
+        <v>2.45</v>
       </c>
       <c r="F21" t="n">
-        <v>9.109999999999999</v>
+        <v>10.58</v>
       </c>
       <c r="G21" t="n">
-        <v>283</v>
+        <v>271.4</v>
       </c>
       <c r="H21" t="n">
-        <v>47.7</v>
+        <v>44.8</v>
       </c>
       <c r="I21" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>68.29000000000001</v>
+        <v>-22.97</v>
       </c>
       <c r="K21" t="n">
-        <v>2.32</v>
+        <v>-94.58</v>
       </c>
       <c r="L21" t="n">
-        <v>68.33</v>
+        <v>97.33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:05:17</t>
+          <t>05:01:49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="F22" t="n">
-        <v>9.140000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>269.6</v>
+        <v>258.8</v>
       </c>
       <c r="H22" t="n">
-        <v>50.6</v>
+        <v>44.2</v>
       </c>
       <c r="I22" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>70.45</v>
+        <v>30.43</v>
       </c>
       <c r="K22" t="n">
-        <v>-27.36</v>
+        <v>-96.92</v>
       </c>
       <c r="L22" t="n">
-        <v>75.58</v>
+        <v>101.58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:10:30</t>
+          <t>05:07:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
       <c r="F23" t="n">
-        <v>9.4</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>259.6</v>
+        <v>264.6</v>
       </c>
       <c r="H23" t="n">
-        <v>50.6</v>
+        <v>47.8</v>
       </c>
       <c r="I23" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-9.34</v>
+        <v>127.31</v>
       </c>
       <c r="K23" t="n">
-        <v>-83.48</v>
+        <v>1.75</v>
       </c>
       <c r="L23" t="n">
-        <v>84</v>
+        <v>127.32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:12:12</t>
+          <t>05:09:16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="F24" t="n">
-        <v>8.77</v>
+        <v>8.75</v>
       </c>
       <c r="G24" t="n">
-        <v>258.3</v>
+        <v>272.1</v>
       </c>
       <c r="H24" t="n">
-        <v>50.8</v>
+        <v>50.3</v>
       </c>
       <c r="I24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>34.23</v>
+        <v>-121.69</v>
       </c>
       <c r="K24" t="n">
-        <v>-88.01000000000001</v>
+        <v>-79.93000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>94.44</v>
+        <v>145.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:14:13</t>
+          <t>05:11:26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.58</v>
+        <v>2.02</v>
       </c>
       <c r="F25" t="n">
-        <v>9.07</v>
+        <v>4.05</v>
       </c>
       <c r="G25" t="n">
-        <v>265.5</v>
+        <v>256.6</v>
       </c>
       <c r="H25" t="n">
-        <v>45.8</v>
+        <v>50.1</v>
       </c>
       <c r="I25" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>104.06</v>
+        <v>-88.34999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>3.23</v>
+        <v>30.23</v>
       </c>
       <c r="L25" t="n">
-        <v>104.11</v>
+        <v>93.38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:18:20</t>
+          <t>05:15:17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="F26" t="n">
-        <v>9.44</v>
+        <v>8.01</v>
       </c>
       <c r="G26" t="n">
-        <v>270.5</v>
+        <v>265.4</v>
       </c>
       <c r="H26" t="n">
-        <v>48.9</v>
+        <v>42.6</v>
       </c>
       <c r="I26" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-119.4</v>
+        <v>-146.45</v>
       </c>
       <c r="K26" t="n">
-        <v>-90.48</v>
+        <v>85.55</v>
       </c>
       <c r="L26" t="n">
-        <v>149.81</v>
+        <v>169.61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:20:13</t>
+          <t>05:17:45</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.04</v>
+        <v>2.59</v>
       </c>
       <c r="F27" t="n">
-        <v>8.66</v>
+        <v>10.58</v>
       </c>
       <c r="G27" t="n">
-        <v>270.1</v>
+        <v>251</v>
       </c>
       <c r="H27" t="n">
-        <v>51.4</v>
+        <v>54.3</v>
       </c>
       <c r="I27" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-96.22</v>
+        <v>-126.82</v>
       </c>
       <c r="K27" t="n">
-        <v>61.55</v>
+        <v>193.79</v>
       </c>
       <c r="L27" t="n">
-        <v>114.23</v>
+        <v>231.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:21:19</t>
+          <t>05:19:26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="F28" t="n">
-        <v>9.109999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="G28" t="n">
-        <v>255</v>
+        <v>273.6</v>
       </c>
       <c r="H28" t="n">
-        <v>50.8</v>
+        <v>45.4</v>
       </c>
       <c r="I28" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-73.05</v>
+        <v>-208.59</v>
       </c>
       <c r="K28" t="n">
-        <v>80.14</v>
+        <v>98.42</v>
       </c>
       <c r="L28" t="n">
-        <v>108.44</v>
+        <v>230.64</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:30:14</t>
+          <t>05:29:42</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.62</v>
+        <v>1.88</v>
       </c>
       <c r="F29" t="n">
-        <v>8.380000000000001</v>
+        <v>7.38</v>
       </c>
       <c r="G29" t="n">
-        <v>278.4</v>
+        <v>279.6</v>
       </c>
       <c r="H29" t="n">
-        <v>38.7</v>
+        <v>46.7</v>
       </c>
       <c r="I29" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>-15.89</v>
+        <v>-39.92</v>
       </c>
       <c r="K29" t="n">
-        <v>50.24</v>
+        <v>-17.81</v>
       </c>
       <c r="L29" t="n">
-        <v>52.69</v>
+        <v>43.71</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:31:37</t>
+          <t>05:30:56</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="F30" t="n">
-        <v>9.51</v>
+        <v>9.67</v>
       </c>
       <c r="G30" t="n">
-        <v>260.6</v>
+        <v>253</v>
       </c>
       <c r="H30" t="n">
-        <v>47.3</v>
+        <v>49.7</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-39.78</v>
+        <v>61.95</v>
       </c>
       <c r="K30" t="n">
-        <v>25.39</v>
+        <v>-34.99</v>
       </c>
       <c r="L30" t="n">
-        <v>47.19</v>
+        <v>71.15000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:33:50</t>
+          <t>05:31:44</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="F31" t="n">
-        <v>9.81</v>
+        <v>3.5</v>
       </c>
       <c r="G31" t="n">
-        <v>263.4</v>
+        <v>280.3</v>
       </c>
       <c r="H31" t="n">
-        <v>46.1</v>
+        <v>46.8</v>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-28.27</v>
+        <v>-4.66</v>
       </c>
       <c r="K31" t="n">
-        <v>-13.37</v>
+        <v>43.78</v>
       </c>
       <c r="L31" t="n">
-        <v>31.27</v>
+        <v>44.02</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:38:22</t>
+          <t>05:37:16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="F32" t="n">
-        <v>8.48</v>
+        <v>10.46</v>
       </c>
       <c r="G32" t="n">
-        <v>269.3</v>
+        <v>257.2</v>
       </c>
       <c r="H32" t="n">
-        <v>50.4</v>
+        <v>46.5</v>
       </c>
       <c r="I32" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>61.31</v>
+        <v>60.09</v>
       </c>
       <c r="K32" t="n">
-        <v>-34.28</v>
+        <v>42.53</v>
       </c>
       <c r="L32" t="n">
-        <v>70.25</v>
+        <v>73.62</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:39:28</t>
+          <t>05:38:04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.83</v>
+        <v>2.47</v>
       </c>
       <c r="F33" t="n">
-        <v>9.85</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
-        <v>263.6</v>
+        <v>271.5</v>
       </c>
       <c r="H33" t="n">
-        <v>54.2</v>
+        <v>60.2</v>
       </c>
       <c r="I33" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-6.1</v>
+        <v>12.08</v>
       </c>
       <c r="K33" t="n">
-        <v>57.29</v>
+        <v>-79.59</v>
       </c>
       <c r="L33" t="n">
-        <v>57.62</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:41:56</t>
+          <t>05:40:06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="F34" t="n">
-        <v>8.699999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="G34" t="n">
-        <v>262.9</v>
+        <v>257.5</v>
       </c>
       <c r="H34" t="n">
-        <v>53.1</v>
+        <v>45.6</v>
       </c>
       <c r="I34" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>39.29</v>
+        <v>-17.1</v>
       </c>
       <c r="K34" t="n">
-        <v>27.15</v>
+        <v>96.17</v>
       </c>
       <c r="L34" t="n">
-        <v>47.76</v>
+        <v>97.68000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:46:31</t>
+          <t>05:45:01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.49</v>
+        <v>2.12</v>
       </c>
       <c r="F35" t="n">
-        <v>9.41</v>
+        <v>7.97</v>
       </c>
       <c r="G35" t="n">
-        <v>290.2</v>
+        <v>270.5</v>
       </c>
       <c r="H35" t="n">
-        <v>39.3</v>
+        <v>43.6</v>
       </c>
       <c r="I35" t="n">
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>15.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>-100.73</v>
+        <v>-90.98</v>
       </c>
       <c r="L35" t="n">
-        <v>101.96</v>
+        <v>90.98</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:47:48</t>
+          <t>05:47:06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="F36" t="n">
-        <v>8.710000000000001</v>
+        <v>7.42</v>
       </c>
       <c r="G36" t="n">
-        <v>261.2</v>
+        <v>260.1</v>
       </c>
       <c r="H36" t="n">
-        <v>51.3</v>
+        <v>49.9</v>
       </c>
       <c r="I36" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-18.14</v>
+        <v>45.08</v>
       </c>
       <c r="K36" t="n">
-        <v>102.09</v>
+        <v>-122.11</v>
       </c>
       <c r="L36" t="n">
-        <v>103.68</v>
+        <v>130.17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:50:21</t>
+          <t>05:48:51</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.13</v>
+        <v>1.66</v>
       </c>
       <c r="F37" t="n">
-        <v>9.359999999999999</v>
+        <v>10.13</v>
       </c>
       <c r="G37" t="n">
-        <v>257.1</v>
+        <v>267.4</v>
       </c>
       <c r="H37" t="n">
-        <v>49.8</v>
+        <v>55.2</v>
       </c>
       <c r="I37" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>8.119999999999999</v>
+        <v>-121.69</v>
       </c>
       <c r="K37" t="n">
-        <v>-74.95999999999999</v>
+        <v>31.11</v>
       </c>
       <c r="L37" t="n">
-        <v>75.39</v>
+        <v>125.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:53:45</t>
+          <t>05:52:44</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.04</v>
+        <v>3.06</v>
       </c>
       <c r="F38" t="n">
-        <v>8.84</v>
+        <v>10.58</v>
       </c>
       <c r="G38" t="n">
-        <v>269.8</v>
+        <v>254.6</v>
       </c>
       <c r="H38" t="n">
-        <v>48.2</v>
+        <v>54</v>
       </c>
       <c r="I38" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>48.76</v>
+        <v>-115.29</v>
       </c>
       <c r="K38" t="n">
-        <v>-121.95</v>
+        <v>105.41</v>
       </c>
       <c r="L38" t="n">
-        <v>131.34</v>
+        <v>156.21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:56:05</t>
+          <t>05:53:32</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.68</v>
+        <v>2.45</v>
       </c>
       <c r="F39" t="n">
-        <v>9.199999999999999</v>
+        <v>10.58</v>
       </c>
       <c r="G39" t="n">
-        <v>280.3</v>
+        <v>261.7</v>
       </c>
       <c r="H39" t="n">
-        <v>52.3</v>
+        <v>45.8</v>
       </c>
       <c r="I39" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-102.96</v>
+        <v>-45.46</v>
       </c>
       <c r="K39" t="n">
-        <v>28.39</v>
+        <v>167.43</v>
       </c>
       <c r="L39" t="n">
-        <v>106.8</v>
+        <v>173.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:58:19</t>
+          <t>05:55:19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.07</v>
+        <v>2.4</v>
       </c>
       <c r="F40" t="n">
-        <v>8.56</v>
+        <v>10.58</v>
       </c>
       <c r="G40" t="n">
-        <v>277.9</v>
+        <v>262.4</v>
       </c>
       <c r="H40" t="n">
-        <v>48.2</v>
+        <v>40.5</v>
       </c>
       <c r="I40" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J40" t="n">
-        <v>-61.86</v>
+        <v>149.27</v>
       </c>
       <c r="K40" t="n">
-        <v>92.08</v>
+        <v>28.69</v>
       </c>
       <c r="L40" t="n">
-        <v>110.93</v>
+        <v>152.01</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:03:53</t>
+          <t>05:58:21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="F41" t="n">
-        <v>8.92</v>
+        <v>8.98</v>
       </c>
       <c r="G41" t="n">
-        <v>261.6</v>
+        <v>263.7</v>
       </c>
       <c r="H41" t="n">
-        <v>52.2</v>
+        <v>50.3</v>
       </c>
       <c r="I41" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-30.43</v>
+        <v>-220.08</v>
       </c>
       <c r="K41" t="n">
-        <v>177.51</v>
+        <v>39.84</v>
       </c>
       <c r="L41" t="n">
-        <v>180.1</v>
+        <v>223.66</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:05:35</t>
+          <t>06:00:15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1804,31 +1804,31 @@
         <v>2.42</v>
       </c>
       <c r="F42" t="n">
-        <v>8.949999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="G42" t="n">
-        <v>250.9</v>
+        <v>273.8</v>
       </c>
       <c r="H42" t="n">
-        <v>51.1</v>
+        <v>48.4</v>
       </c>
       <c r="I42" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>148.68</v>
+        <v>-187.55</v>
       </c>
       <c r="K42" t="n">
-        <v>23.84</v>
+        <v>153.57</v>
       </c>
       <c r="L42" t="n">
-        <v>150.58</v>
+        <v>242.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:07:42</t>
+          <t>06:01:28</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="F43" t="n">
-        <v>9.02</v>
+        <v>10.58</v>
       </c>
       <c r="G43" t="n">
-        <v>270.6</v>
+        <v>261.5</v>
       </c>
       <c r="H43" t="n">
-        <v>48.1</v>
+        <v>53.2</v>
       </c>
       <c r="I43" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-176.48</v>
+        <v>-181.99</v>
       </c>
       <c r="K43" t="n">
-        <v>45.21</v>
+        <v>-101.63</v>
       </c>
       <c r="L43" t="n">
-        <v>182.18</v>
+        <v>208.44</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:18:03</t>
+          <t>06:11:14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="F44" t="n">
-        <v>9.52</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>266.7</v>
+        <v>255.1</v>
       </c>
       <c r="H44" t="n">
-        <v>46.5</v>
+        <v>44.3</v>
       </c>
       <c r="I44" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>-40.64</v>
+        <v>20.41</v>
       </c>
       <c r="K44" t="n">
-        <v>42.97</v>
+        <v>-57.88</v>
       </c>
       <c r="L44" t="n">
-        <v>59.15</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:19:30</t>
+          <t>06:12:38</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="F45" t="n">
-        <v>8.91</v>
+        <v>10.58</v>
       </c>
       <c r="G45" t="n">
-        <v>276.2</v>
+        <v>252.5</v>
       </c>
       <c r="H45" t="n">
-        <v>57.4</v>
+        <v>59.3</v>
       </c>
       <c r="I45" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>-30.64</v>
+        <v>-66.41</v>
       </c>
       <c r="K45" t="n">
-        <v>-24.11</v>
+        <v>-42.8</v>
       </c>
       <c r="L45" t="n">
-        <v>38.99</v>
+        <v>79.01000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:20:18</t>
+          <t>06:13:44</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="F46" t="n">
-        <v>8.59</v>
+        <v>8.82</v>
       </c>
       <c r="G46" t="n">
-        <v>258.5</v>
+        <v>260.6</v>
       </c>
       <c r="H46" t="n">
-        <v>48.4</v>
+        <v>53.3</v>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>16.69</v>
+        <v>-21.91</v>
       </c>
       <c r="K46" t="n">
-        <v>-45.06</v>
+        <v>-44.56</v>
       </c>
       <c r="L46" t="n">
-        <v>48.05</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:24:13</t>
+          <t>06:19:29</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.39</v>
+        <v>2.07</v>
       </c>
       <c r="F47" t="n">
-        <v>8.460000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="G47" t="n">
-        <v>288.5</v>
+        <v>259.9</v>
       </c>
       <c r="H47" t="n">
-        <v>37.6</v>
+        <v>44.4</v>
       </c>
       <c r="I47" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-53.91</v>
+        <v>-78.05</v>
       </c>
       <c r="K47" t="n">
-        <v>-33.92</v>
+        <v>13.03</v>
       </c>
       <c r="L47" t="n">
-        <v>63.69</v>
+        <v>79.13</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:25:12</t>
+          <t>06:21:51</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.34</v>
+        <v>2.68</v>
       </c>
       <c r="F48" t="n">
-        <v>8.859999999999999</v>
+        <v>7.58</v>
       </c>
       <c r="G48" t="n">
-        <v>276.5</v>
+        <v>265.9</v>
       </c>
       <c r="H48" t="n">
-        <v>48.3</v>
+        <v>50.3</v>
       </c>
       <c r="I48" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>-19.09</v>
+        <v>37.84</v>
       </c>
       <c r="K48" t="n">
-        <v>-38.1</v>
+        <v>63.57</v>
       </c>
       <c r="L48" t="n">
-        <v>42.62</v>
+        <v>73.98</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:27:06</t>
+          <t>06:23:01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="F49" t="n">
-        <v>8.83</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>258.8</v>
+        <v>274</v>
       </c>
       <c r="H49" t="n">
-        <v>51.1</v>
+        <v>53.5</v>
       </c>
       <c r="I49" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-54.06</v>
+        <v>32.52</v>
       </c>
       <c r="K49" t="n">
-        <v>9.48</v>
+        <v>-80.45</v>
       </c>
       <c r="L49" t="n">
-        <v>54.88</v>
+        <v>86.78</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:31:15</t>
+          <t>06:27:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="F50" t="n">
-        <v>9.130000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>270.4</v>
+        <v>259.6</v>
       </c>
       <c r="H50" t="n">
-        <v>43.8</v>
+        <v>47.7</v>
       </c>
       <c r="I50" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>39.06</v>
+        <v>96.37</v>
       </c>
       <c r="K50" t="n">
-        <v>66.06</v>
+        <v>27.99</v>
       </c>
       <c r="L50" t="n">
-        <v>76.75</v>
+        <v>100.35</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:32:30</t>
+          <t>06:28:14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="F51" t="n">
-        <v>9.529999999999999</v>
+        <v>3.74</v>
       </c>
       <c r="G51" t="n">
-        <v>276.9</v>
+        <v>260.2</v>
       </c>
       <c r="H51" t="n">
-        <v>57</v>
+        <v>45.7</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>34.65</v>
+        <v>80.18000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>-85.34999999999999</v>
+        <v>-18.05</v>
       </c>
       <c r="L51" t="n">
-        <v>92.12</v>
+        <v>82.19</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:33:56</t>
+          <t>06:29:11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="F52" t="n">
-        <v>8.81</v>
+        <v>10.2</v>
       </c>
       <c r="G52" t="n">
-        <v>265.4</v>
+        <v>276</v>
       </c>
       <c r="H52" t="n">
-        <v>46.4</v>
+        <v>48.5</v>
       </c>
       <c r="I52" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>71.76000000000001</v>
+        <v>-2.59</v>
       </c>
       <c r="K52" t="n">
-        <v>20.45</v>
+        <v>-139.52</v>
       </c>
       <c r="L52" t="n">
-        <v>74.61</v>
+        <v>139.55</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:37:42</t>
+          <t>06:34:50</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.26</v>
+        <v>2.01</v>
       </c>
       <c r="F53" t="n">
-        <v>8.84</v>
+        <v>2.96</v>
       </c>
       <c r="G53" t="n">
-        <v>261.4</v>
+        <v>261.3</v>
       </c>
       <c r="H53" t="n">
-        <v>43</v>
+        <v>50.7</v>
       </c>
       <c r="I53" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>93.16</v>
+        <v>127.21</v>
       </c>
       <c r="K53" t="n">
-        <v>-18.01</v>
+        <v>103.93</v>
       </c>
       <c r="L53" t="n">
-        <v>94.89</v>
+        <v>164.27</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:40:09</t>
+          <t>06:37:16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.7</v>
+        <v>3.29</v>
       </c>
       <c r="F54" t="n">
-        <v>9.640000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="G54" t="n">
-        <v>266.9</v>
+        <v>266.7</v>
       </c>
       <c r="H54" t="n">
-        <v>48.2</v>
+        <v>46</v>
       </c>
       <c r="I54" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>2.96</v>
+        <v>-70.72</v>
       </c>
       <c r="K54" t="n">
-        <v>-144.31</v>
+        <v>-172.4</v>
       </c>
       <c r="L54" t="n">
-        <v>144.34</v>
+        <v>186.34</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:40:56</t>
+          <t>06:39:40</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="F55" t="n">
-        <v>8.9</v>
+        <v>5.61</v>
       </c>
       <c r="G55" t="n">
-        <v>271.3</v>
+        <v>272.8</v>
       </c>
       <c r="H55" t="n">
-        <v>54.1</v>
+        <v>42.2</v>
       </c>
       <c r="I55" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>116.43</v>
+        <v>-44.38</v>
       </c>
       <c r="K55" t="n">
-        <v>90.33</v>
+        <v>-97.61</v>
       </c>
       <c r="L55" t="n">
-        <v>147.36</v>
+        <v>107.22</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:45:00</t>
+          <t>06:44:59</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="F56" t="n">
-        <v>9.17</v>
+        <v>10.58</v>
       </c>
       <c r="G56" t="n">
-        <v>261.9</v>
+        <v>278.7</v>
       </c>
       <c r="H56" t="n">
-        <v>49.2</v>
+        <v>50.9</v>
       </c>
       <c r="I56" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-40.94</v>
+        <v>-9.6</v>
       </c>
       <c r="K56" t="n">
-        <v>-170.95</v>
+        <v>246.08</v>
       </c>
       <c r="L56" t="n">
-        <v>175.79</v>
+        <v>246.27</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:46:44</t>
+          <t>06:47:15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.89</v>
+        <v>2.56</v>
       </c>
       <c r="F57" t="n">
-        <v>9.48</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>254.3</v>
+        <v>278.1</v>
       </c>
       <c r="H57" t="n">
-        <v>49.7</v>
+        <v>53.3</v>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-15.05</v>
+        <v>-195.9</v>
       </c>
       <c r="K57" t="n">
-        <v>-126.36</v>
+        <v>-147.55</v>
       </c>
       <c r="L57" t="n">
-        <v>127.26</v>
+        <v>245.25</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:49:10</t>
+          <t>06:48:31</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="F58" t="n">
-        <v>9.77</v>
+        <v>10.58</v>
       </c>
       <c r="G58" t="n">
-        <v>271.8</v>
+        <v>262.9</v>
       </c>
       <c r="H58" t="n">
-        <v>56.5</v>
+        <v>50.9</v>
       </c>
       <c r="I58" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>28.6</v>
+        <v>-256.93</v>
       </c>
       <c r="K58" t="n">
-        <v>168.36</v>
+        <v>224.58</v>
       </c>
       <c r="L58" t="n">
-        <v>170.77</v>
+        <v>341.25</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:57:32</t>
+          <t>07:00:39</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.58</v>
+        <v>2.41</v>
       </c>
       <c r="F59" t="n">
-        <v>9.74</v>
+        <v>10.58</v>
       </c>
       <c r="G59" t="n">
-        <v>276.4</v>
+        <v>259.6</v>
       </c>
       <c r="H59" t="n">
-        <v>48.1</v>
+        <v>47</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-33.75</v>
+        <v>84.91</v>
       </c>
       <c r="K59" t="n">
-        <v>-39.91</v>
+        <v>-33.07</v>
       </c>
       <c r="L59" t="n">
-        <v>52.26</v>
+        <v>91.12</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:58:58</t>
+          <t>07:02:22</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.56</v>
+        <v>1.95</v>
       </c>
       <c r="F60" t="n">
-        <v>8.98</v>
+        <v>3.88</v>
       </c>
       <c r="G60" t="n">
-        <v>271.7</v>
+        <v>275.3</v>
       </c>
       <c r="H60" t="n">
-        <v>52</v>
+        <v>44.8</v>
       </c>
       <c r="I60" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-43.33</v>
+        <v>-36.39</v>
       </c>
       <c r="K60" t="n">
-        <v>48.57</v>
+        <v>1.82</v>
       </c>
       <c r="L60" t="n">
-        <v>65.09</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:01:24</t>
+          <t>07:04:13</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.41</v>
+        <v>3.2</v>
       </c>
       <c r="F61" t="n">
-        <v>8.81</v>
+        <v>10.58</v>
       </c>
       <c r="G61" t="n">
-        <v>263.9</v>
+        <v>275.7</v>
       </c>
       <c r="H61" t="n">
-        <v>52.6</v>
+        <v>45.8</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>72.12</v>
+        <v>-52.22</v>
       </c>
       <c r="K61" t="n">
-        <v>-27.83</v>
+        <v>-63.87</v>
       </c>
       <c r="L61" t="n">
-        <v>77.3</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:07:39</t>
+          <t>07:08:38</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.96</v>
+        <v>2.29</v>
       </c>
       <c r="F62" t="n">
-        <v>9.6</v>
+        <v>6.73</v>
       </c>
       <c r="G62" t="n">
-        <v>259.4</v>
+        <v>268</v>
       </c>
       <c r="H62" t="n">
-        <v>42.1</v>
+        <v>48.1</v>
       </c>
       <c r="I62" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-41.34</v>
+        <v>-32.15</v>
       </c>
       <c r="K62" t="n">
-        <v>1.4</v>
+        <v>71.94</v>
       </c>
       <c r="L62" t="n">
-        <v>41.36</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:09:16</t>
+          <t>07:10:03</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.21</v>
+        <v>2.47</v>
       </c>
       <c r="F63" t="n">
-        <v>9.619999999999999</v>
+        <v>10.58</v>
       </c>
       <c r="G63" t="n">
-        <v>261.5</v>
+        <v>277.9</v>
       </c>
       <c r="H63" t="n">
-        <v>46.3</v>
+        <v>55</v>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>-51.26</v>
+        <v>83.7</v>
       </c>
       <c r="K63" t="n">
-        <v>-63.33</v>
+        <v>-47.85</v>
       </c>
       <c r="L63" t="n">
-        <v>81.48</v>
+        <v>96.41</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:11:32</t>
+          <t>07:11:08</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.29</v>
+        <v>2.59</v>
       </c>
       <c r="F64" t="n">
-        <v>9.24</v>
+        <v>10.58</v>
       </c>
       <c r="G64" t="n">
-        <v>266</v>
+        <v>271.8</v>
       </c>
       <c r="H64" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>-25.08</v>
+        <v>60.41</v>
       </c>
       <c r="K64" t="n">
-        <v>59.46</v>
+        <v>-28.69</v>
       </c>
       <c r="L64" t="n">
-        <v>64.53</v>
+        <v>66.87</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:15:36</t>
+          <t>07:15:40</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="F65" t="n">
-        <v>9.73</v>
+        <v>10.58</v>
       </c>
       <c r="G65" t="n">
-        <v>280</v>
+        <v>282.9</v>
       </c>
       <c r="H65" t="n">
-        <v>52.3</v>
+        <v>49.3</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>87.84</v>
+        <v>56.22</v>
       </c>
       <c r="K65" t="n">
-        <v>-50.01</v>
+        <v>39.19</v>
       </c>
       <c r="L65" t="n">
-        <v>101.07</v>
+        <v>68.53</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:17:46</t>
+          <t>07:17:24</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="F66" t="n">
-        <v>9.42</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G66" t="n">
-        <v>259.6</v>
+        <v>282.3</v>
       </c>
       <c r="H66" t="n">
-        <v>56.4</v>
+        <v>46.4</v>
       </c>
       <c r="I66" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>63.05</v>
+        <v>-133.96</v>
       </c>
       <c r="K66" t="n">
-        <v>-31.74</v>
+        <v>-54.29</v>
       </c>
       <c r="L66" t="n">
-        <v>70.59</v>
+        <v>144.55</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:19:14</t>
+          <t>07:19:17</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.49</v>
+        <v>1.99</v>
       </c>
       <c r="F67" t="n">
-        <v>9.98</v>
+        <v>7.16</v>
       </c>
       <c r="G67" t="n">
-        <v>268.5</v>
+        <v>272.3</v>
       </c>
       <c r="H67" t="n">
-        <v>49.5</v>
+        <v>53.4</v>
       </c>
       <c r="I67" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>55.43</v>
+        <v>-92.34</v>
       </c>
       <c r="K67" t="n">
-        <v>19.46</v>
+        <v>80.91</v>
       </c>
       <c r="L67" t="n">
-        <v>58.75</v>
+        <v>122.77</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:23:58</t>
+          <t>07:23:52</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.42</v>
+        <v>2.77</v>
       </c>
       <c r="F68" t="n">
-        <v>9.949999999999999</v>
+        <v>10.58</v>
       </c>
       <c r="G68" t="n">
-        <v>262.8</v>
+        <v>275.7</v>
       </c>
       <c r="H68" t="n">
-        <v>49</v>
+        <v>43.6</v>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-137.81</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>-61.19</v>
+        <v>-139.66</v>
       </c>
       <c r="L68" t="n">
-        <v>150.78</v>
+        <v>139.94</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:25:09</t>
+          <t>07:25:33</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="F69" t="n">
-        <v>9.449999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="G69" t="n">
-        <v>276.7</v>
+        <v>275.3</v>
       </c>
       <c r="H69" t="n">
-        <v>48.4</v>
+        <v>49.8</v>
       </c>
       <c r="I69" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-80.08</v>
+        <v>-152.11</v>
       </c>
       <c r="K69" t="n">
-        <v>74.03</v>
+        <v>-65.84999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>109.06</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:26:46</t>
+          <t>07:27:38</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.78</v>
+        <v>3.13</v>
       </c>
       <c r="F70" t="n">
-        <v>9.619999999999999</v>
+        <v>10.58</v>
       </c>
       <c r="G70" t="n">
-        <v>257.2</v>
+        <v>268.3</v>
       </c>
       <c r="H70" t="n">
-        <v>50.4</v>
+        <v>52</v>
       </c>
       <c r="I70" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>34.02</v>
+        <v>-21.1</v>
       </c>
       <c r="K70" t="n">
-        <v>-94.20999999999999</v>
+        <v>-158.99</v>
       </c>
       <c r="L70" t="n">
-        <v>100.16</v>
+        <v>160.39</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:30:23</t>
+          <t>07:32:25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.32</v>
+        <v>2.86</v>
       </c>
       <c r="F71" t="n">
-        <v>9.6</v>
+        <v>10.58</v>
       </c>
       <c r="G71" t="n">
-        <v>269.5</v>
+        <v>272.6</v>
       </c>
       <c r="H71" t="n">
-        <v>51.3</v>
+        <v>48.7</v>
       </c>
       <c r="I71" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-140.95</v>
+        <v>-104.49</v>
       </c>
       <c r="K71" t="n">
-        <v>-72.28</v>
+        <v>176.93</v>
       </c>
       <c r="L71" t="n">
-        <v>158.41</v>
+        <v>205.49</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:31:48</t>
+          <t>07:33:54</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.14</v>
+        <v>2.18</v>
       </c>
       <c r="F72" t="n">
-        <v>9.25</v>
+        <v>10.58</v>
       </c>
       <c r="G72" t="n">
-        <v>274</v>
+        <v>263.1</v>
       </c>
       <c r="H72" t="n">
-        <v>56.5</v>
+        <v>50</v>
       </c>
       <c r="I72" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>12.62</v>
+        <v>134.47</v>
       </c>
       <c r="K72" t="n">
-        <v>-149.4</v>
+        <v>-221.24</v>
       </c>
       <c r="L72" t="n">
-        <v>149.93</v>
+        <v>258.9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:34:17</t>
+          <t>07:34:58</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.86</v>
+        <v>2.1</v>
       </c>
       <c r="F73" t="n">
-        <v>9.470000000000001</v>
+        <v>7.48</v>
       </c>
       <c r="G73" t="n">
-        <v>267.2</v>
+        <v>258.5</v>
       </c>
       <c r="H73" t="n">
-        <v>45.2</v>
+        <v>54.1</v>
       </c>
       <c r="I73" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-36.49</v>
+        <v>-186.57</v>
       </c>
       <c r="K73" t="n">
-        <v>136.71</v>
+        <v>-72.34</v>
       </c>
       <c r="L73" t="n">
-        <v>141.49</v>
+        <v>200.1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:42:28</t>
+          <t>07:43:32</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="F74" t="n">
-        <v>8.99</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>270</v>
+        <v>262.4</v>
       </c>
       <c r="H74" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
       <c r="I74" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>33.44</v>
+        <v>-70.29000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-36.53</v>
+        <v>-57.81</v>
       </c>
       <c r="L74" t="n">
-        <v>49.53</v>
+        <v>91.01000000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:44:27</t>
+          <t>07:45:52</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.12</v>
+        <v>2.91</v>
       </c>
       <c r="F75" t="n">
-        <v>8.76</v>
+        <v>10.58</v>
       </c>
       <c r="G75" t="n">
-        <v>278.1</v>
+        <v>269.7</v>
       </c>
       <c r="H75" t="n">
-        <v>42.9</v>
+        <v>51</v>
       </c>
       <c r="I75" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-30.08</v>
+        <v>35.78</v>
       </c>
       <c r="K75" t="n">
-        <v>-14</v>
+        <v>-61.32</v>
       </c>
       <c r="L75" t="n">
-        <v>33.18</v>
+        <v>71</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:46:09</t>
+          <t>07:47:07</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.14</v>
+        <v>2.64</v>
       </c>
       <c r="F76" t="n">
-        <v>8.960000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="G76" t="n">
-        <v>275.2</v>
+        <v>269.9</v>
       </c>
       <c r="H76" t="n">
-        <v>49.1</v>
+        <v>55.8</v>
       </c>
       <c r="I76" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>-45.08</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>-37.18</v>
+        <v>-46.06</v>
       </c>
       <c r="L76" t="n">
-        <v>58.44</v>
+        <v>91.15000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:52:03</t>
+          <t>07:52:43</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.92</v>
+        <v>2.51</v>
       </c>
       <c r="F77" t="n">
-        <v>9.32</v>
+        <v>9.25</v>
       </c>
       <c r="G77" t="n">
-        <v>271.9</v>
+        <v>271.4</v>
       </c>
       <c r="H77" t="n">
-        <v>50.4</v>
+        <v>49.7</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>32.98</v>
+        <v>-22.15</v>
       </c>
       <c r="K77" t="n">
-        <v>-56.29</v>
+        <v>-71.83</v>
       </c>
       <c r="L77" t="n">
-        <v>65.23999999999999</v>
+        <v>75.17</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:53:17</t>
+          <t>07:55:02</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="F78" t="n">
-        <v>9.33</v>
+        <v>10.58</v>
       </c>
       <c r="G78" t="n">
-        <v>281.4</v>
+        <v>250.3</v>
       </c>
       <c r="H78" t="n">
-        <v>54.4</v>
+        <v>47.7</v>
       </c>
       <c r="I78" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>70.61</v>
+        <v>62.45</v>
       </c>
       <c r="K78" t="n">
-        <v>-41.04</v>
+        <v>-23.91</v>
       </c>
       <c r="L78" t="n">
-        <v>81.67</v>
+        <v>66.87</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:54:47</t>
+          <t>07:56:33</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.51</v>
+        <v>2.29</v>
       </c>
       <c r="F79" t="n">
-        <v>9.41</v>
+        <v>10.58</v>
       </c>
       <c r="G79" t="n">
-        <v>269.3</v>
+        <v>269.9</v>
       </c>
       <c r="H79" t="n">
-        <v>51.8</v>
+        <v>41.7</v>
       </c>
       <c r="I79" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>-13.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>-48.94</v>
+        <v>-79.98999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>50.65</v>
+        <v>80.47</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:57:54</t>
+          <t>08:00:41</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.36</v>
+        <v>2.13</v>
       </c>
       <c r="F80" t="n">
-        <v>8.35</v>
+        <v>10.58</v>
       </c>
       <c r="G80" t="n">
-        <v>265.2</v>
+        <v>253.9</v>
       </c>
       <c r="H80" t="n">
-        <v>56.1</v>
+        <v>48.4</v>
       </c>
       <c r="I80" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>57.98</v>
+        <v>3.17</v>
       </c>
       <c r="K80" t="n">
-        <v>-20.13</v>
+        <v>-102.01</v>
       </c>
       <c r="L80" t="n">
-        <v>61.38</v>
+        <v>102.06</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:00:01</t>
+          <t>08:02:04</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="F81" t="n">
-        <v>9.33</v>
+        <v>10.58</v>
       </c>
       <c r="G81" t="n">
-        <v>253.4</v>
+        <v>269.3</v>
       </c>
       <c r="H81" t="n">
-        <v>48.9</v>
+        <v>50.6</v>
       </c>
       <c r="I81" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>8.279999999999999</v>
+        <v>-104.14</v>
       </c>
       <c r="K81" t="n">
-        <v>-74.17</v>
+        <v>-36.07</v>
       </c>
       <c r="L81" t="n">
-        <v>74.63</v>
+        <v>110.21</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:02:14</t>
+          <t>08:04:21</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.13</v>
+        <v>2.77</v>
       </c>
       <c r="F82" t="n">
-        <v>8.529999999999999</v>
+        <v>8.49</v>
       </c>
       <c r="G82" t="n">
-        <v>266.7</v>
+        <v>274</v>
       </c>
       <c r="H82" t="n">
-        <v>54.8</v>
+        <v>47.9</v>
       </c>
       <c r="I82" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>11.51</v>
+        <v>121.73</v>
       </c>
       <c r="K82" t="n">
-        <v>-58.64</v>
+        <v>-59.2</v>
       </c>
       <c r="L82" t="n">
-        <v>59.75</v>
+        <v>135.36</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:06:48</t>
+          <t>08:08:26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.13</v>
+        <v>2.81</v>
       </c>
       <c r="F83" t="n">
-        <v>9.300000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="G83" t="n">
-        <v>271.1</v>
+        <v>271.7</v>
       </c>
       <c r="H83" t="n">
-        <v>49.7</v>
+        <v>43.6</v>
       </c>
       <c r="I83" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-84.03</v>
+        <v>-102.93</v>
       </c>
       <c r="K83" t="n">
-        <v>-31.39</v>
+        <v>-78.15000000000001</v>
       </c>
       <c r="L83" t="n">
-        <v>89.7</v>
+        <v>129.24</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:09:21</t>
+          <t>08:10:32</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.78</v>
+        <v>1.97</v>
       </c>
       <c r="F84" t="n">
-        <v>9.539999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G84" t="n">
-        <v>265.6</v>
+        <v>264.7</v>
       </c>
       <c r="H84" t="n">
-        <v>43.8</v>
+        <v>45</v>
       </c>
       <c r="I84" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>139.12</v>
+        <v>-134.96</v>
       </c>
       <c r="K84" t="n">
-        <v>-66.56</v>
+        <v>-2.88</v>
       </c>
       <c r="L84" t="n">
-        <v>154.22</v>
+        <v>134.99</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:11:03</t>
+          <t>08:12:29</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.81</v>
+        <v>1.92</v>
       </c>
       <c r="F85" t="n">
-        <v>9.42</v>
+        <v>7.97</v>
       </c>
       <c r="G85" t="n">
-        <v>257.2</v>
+        <v>275.5</v>
       </c>
       <c r="H85" t="n">
-        <v>51.9</v>
+        <v>38.9</v>
       </c>
       <c r="I85" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-31.95</v>
+        <v>1.69</v>
       </c>
       <c r="K85" t="n">
-        <v>-70.92</v>
+        <v>130.6</v>
       </c>
       <c r="L85" t="n">
-        <v>77.79000000000001</v>
+        <v>130.61</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:14:43</t>
+          <t>08:16:37</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="F86" t="n">
-        <v>9.07</v>
+        <v>10.57</v>
       </c>
       <c r="G86" t="n">
-        <v>259.9</v>
+        <v>270.7</v>
       </c>
       <c r="H86" t="n">
-        <v>49.5</v>
+        <v>47</v>
       </c>
       <c r="I86" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-134.2</v>
+        <v>-87.29000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>-2.96</v>
+        <v>257.15</v>
       </c>
       <c r="L86" t="n">
-        <v>134.23</v>
+        <v>271.56</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:15:54</t>
+          <t>08:18:33</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.93</v>
+        <v>2.56</v>
       </c>
       <c r="F87" t="n">
-        <v>9.609999999999999</v>
+        <v>10.58</v>
       </c>
       <c r="G87" t="n">
-        <v>247.6</v>
+        <v>260.9</v>
       </c>
       <c r="H87" t="n">
-        <v>44.3</v>
+        <v>55.4</v>
       </c>
       <c r="I87" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>18.89</v>
+        <v>-152.28</v>
       </c>
       <c r="K87" t="n">
-        <v>127.21</v>
+        <v>-94.54000000000001</v>
       </c>
       <c r="L87" t="n">
-        <v>128.61</v>
+        <v>179.25</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:17:52</t>
+          <t>08:20:44</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="F88" t="n">
-        <v>9.369999999999999</v>
+        <v>10.58</v>
       </c>
       <c r="G88" t="n">
-        <v>264</v>
+        <v>281.7</v>
       </c>
       <c r="H88" t="n">
-        <v>47.7</v>
+        <v>44.1</v>
       </c>
       <c r="I88" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-27.69</v>
+        <v>258.34</v>
       </c>
       <c r="K88" t="n">
-        <v>172.26</v>
+        <v>-128.87</v>
       </c>
       <c r="L88" t="n">
-        <v>174.47</v>
+        <v>288.7</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-09.xlsx
+++ b/output/2024-07-09.xlsx
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>29</v>
+        <v>32.1</v>
       </c>
       <c r="K14" t="n">
-        <v>-42.43</v>
+        <v>-46.97</v>
       </c>
       <c r="L14" t="n">
-        <v>51.39</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="15">
@@ -766,13 +766,13 @@
         <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>13.52</v>
+        <v>14.52</v>
       </c>
       <c r="K17" t="n">
-        <v>-101.65</v>
+        <v>-109.18</v>
       </c>
       <c r="L17" t="n">
-        <v>102.54</v>
+        <v>110.14</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>19</v>
       </c>
       <c r="J18" t="n">
-        <v>-71.95</v>
+        <v>-78.48999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>18.79</v>
+        <v>20.5</v>
       </c>
       <c r="L18" t="n">
-        <v>74.36</v>
+        <v>81.13</v>
       </c>
     </row>
     <row r="19">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-22.97</v>
+        <v>-24.67</v>
       </c>
       <c r="K21" t="n">
-        <v>-94.58</v>
+        <v>-101.58</v>
       </c>
       <c r="L21" t="n">
-        <v>97.33</v>
+        <v>104.53</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>30.43</v>
+        <v>32.68</v>
       </c>
       <c r="K22" t="n">
-        <v>-96.92</v>
+        <v>-104.09</v>
       </c>
       <c r="L22" t="n">
-        <v>101.58</v>
+        <v>109.1</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>127.31</v>
+        <v>132.2</v>
       </c>
       <c r="K23" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="L23" t="n">
-        <v>127.32</v>
+        <v>132.22</v>
       </c>
     </row>
     <row r="24">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>-88.34999999999999</v>
+        <v>-91.75</v>
       </c>
       <c r="K25" t="n">
-        <v>30.23</v>
+        <v>31.39</v>
       </c>
       <c r="L25" t="n">
-        <v>93.38</v>
+        <v>96.97</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-146.45</v>
+        <v>-152.08</v>
       </c>
       <c r="K26" t="n">
-        <v>85.55</v>
+        <v>88.84</v>
       </c>
       <c r="L26" t="n">
-        <v>169.61</v>
+        <v>176.13</v>
       </c>
     </row>
     <row r="27">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-208.59</v>
+        <v>-227.56</v>
       </c>
       <c r="K28" t="n">
-        <v>98.42</v>
+        <v>107.36</v>
       </c>
       <c r="L28" t="n">
-        <v>230.64</v>
+        <v>251.61</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>-39.92</v>
+        <v>-44.19</v>
       </c>
       <c r="K29" t="n">
-        <v>-17.81</v>
+        <v>-19.72</v>
       </c>
       <c r="L29" t="n">
-        <v>43.71</v>
+        <v>48.39</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>61.95</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-34.99</v>
+        <v>-36.97</v>
       </c>
       <c r="L30" t="n">
-        <v>71.15000000000001</v>
+        <v>75.18000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.66</v>
+        <v>-4.75</v>
       </c>
       <c r="K31" t="n">
-        <v>43.78</v>
+        <v>44.63</v>
       </c>
       <c r="L31" t="n">
-        <v>44.02</v>
+        <v>44.89</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>60.09</v>
+        <v>65.56</v>
       </c>
       <c r="K32" t="n">
-        <v>42.53</v>
+        <v>46.39</v>
       </c>
       <c r="L32" t="n">
-        <v>73.62</v>
+        <v>80.31</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>12.08</v>
+        <v>12.97</v>
       </c>
       <c r="K33" t="n">
-        <v>-79.59</v>
+        <v>-85.48</v>
       </c>
       <c r="L33" t="n">
-        <v>80.5</v>
+        <v>86.45999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-17.1</v>
+        <v>-17.44</v>
       </c>
       <c r="K34" t="n">
-        <v>96.17</v>
+        <v>98.06</v>
       </c>
       <c r="L34" t="n">
-        <v>97.68000000000001</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>45.08</v>
+        <v>46.82</v>
       </c>
       <c r="K36" t="n">
-        <v>-122.11</v>
+        <v>-126.8</v>
       </c>
       <c r="L36" t="n">
-        <v>130.17</v>
+        <v>135.17</v>
       </c>
     </row>
     <row r="37">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-115.29</v>
+        <v>-123.83</v>
       </c>
       <c r="K38" t="n">
-        <v>105.41</v>
+        <v>113.21</v>
       </c>
       <c r="L38" t="n">
-        <v>156.21</v>
+        <v>167.78</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-45.46</v>
+        <v>-48.83</v>
       </c>
       <c r="K39" t="n">
-        <v>167.43</v>
+        <v>179.84</v>
       </c>
       <c r="L39" t="n">
-        <v>173.5</v>
+        <v>186.35</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>18</v>
       </c>
       <c r="J40" t="n">
-        <v>149.27</v>
+        <v>165.27</v>
       </c>
       <c r="K40" t="n">
-        <v>28.69</v>
+        <v>31.76</v>
       </c>
       <c r="L40" t="n">
-        <v>152.01</v>
+        <v>168.29</v>
       </c>
     </row>
     <row r="41">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-187.55</v>
+        <v>-191.23</v>
       </c>
       <c r="K42" t="n">
-        <v>153.57</v>
+        <v>156.58</v>
       </c>
       <c r="L42" t="n">
-        <v>242.4</v>
+        <v>247.16</v>
       </c>
     </row>
     <row r="43">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>20.41</v>
+        <v>21.2</v>
       </c>
       <c r="K44" t="n">
-        <v>-57.88</v>
+        <v>-60.1</v>
       </c>
       <c r="L44" t="n">
-        <v>61.37</v>
+        <v>63.73</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>-66.41</v>
+        <v>-73.53</v>
       </c>
       <c r="K45" t="n">
-        <v>-42.8</v>
+        <v>-47.39</v>
       </c>
       <c r="L45" t="n">
-        <v>79.01000000000001</v>
+        <v>87.48</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-21.91</v>
+        <v>-23.15</v>
       </c>
       <c r="K46" t="n">
-        <v>-44.56</v>
+        <v>-47.08</v>
       </c>
       <c r="L46" t="n">
-        <v>49.65</v>
+        <v>52.46</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-78.05</v>
+        <v>-79.58</v>
       </c>
       <c r="K47" t="n">
-        <v>13.03</v>
+        <v>13.28</v>
       </c>
       <c r="L47" t="n">
-        <v>79.13</v>
+        <v>80.68000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>20</v>
       </c>
       <c r="J48" t="n">
-        <v>37.84</v>
+        <v>40.65</v>
       </c>
       <c r="K48" t="n">
-        <v>63.57</v>
+        <v>68.28</v>
       </c>
       <c r="L48" t="n">
-        <v>73.98</v>
+        <v>79.45999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>32.52</v>
+        <v>34.93</v>
       </c>
       <c r="K49" t="n">
-        <v>-80.45</v>
+        <v>-86.41</v>
       </c>
       <c r="L49" t="n">
-        <v>86.78</v>
+        <v>93.20999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>96.37</v>
+        <v>105.13</v>
       </c>
       <c r="K50" t="n">
-        <v>27.99</v>
+        <v>30.54</v>
       </c>
       <c r="L50" t="n">
-        <v>100.35</v>
+        <v>109.47</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>80.18000000000001</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>-18.05</v>
+        <v>-18.75</v>
       </c>
       <c r="L51" t="n">
-        <v>82.19</v>
+        <v>85.34999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-2.59</v>
+        <v>-2.69</v>
       </c>
       <c r="K52" t="n">
-        <v>-139.52</v>
+        <v>-144.89</v>
       </c>
       <c r="L52" t="n">
-        <v>139.55</v>
+        <v>144.92</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>127.21</v>
+        <v>136.63</v>
       </c>
       <c r="K53" t="n">
-        <v>103.93</v>
+        <v>111.63</v>
       </c>
       <c r="L53" t="n">
-        <v>164.27</v>
+        <v>176.44</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>-70.72</v>
+        <v>-78.3</v>
       </c>
       <c r="K54" t="n">
-        <v>-172.4</v>
+        <v>-190.88</v>
       </c>
       <c r="L54" t="n">
-        <v>186.34</v>
+        <v>206.32</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>-44.38</v>
+        <v>-48.41</v>
       </c>
       <c r="K55" t="n">
-        <v>-97.61</v>
+        <v>-106.48</v>
       </c>
       <c r="L55" t="n">
-        <v>107.22</v>
+        <v>116.97</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.6</v>
+        <v>-10.14</v>
       </c>
       <c r="K56" t="n">
-        <v>246.08</v>
+        <v>260.01</v>
       </c>
       <c r="L56" t="n">
-        <v>246.27</v>
+        <v>260.21</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-195.9</v>
+        <v>-203.43</v>
       </c>
       <c r="K57" t="n">
-        <v>-147.55</v>
+        <v>-153.23</v>
       </c>
       <c r="L57" t="n">
-        <v>245.25</v>
+        <v>254.68</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>-256.93</v>
+        <v>-275.97</v>
       </c>
       <c r="K58" t="n">
-        <v>224.58</v>
+        <v>241.22</v>
       </c>
       <c r="L58" t="n">
-        <v>341.25</v>
+        <v>366.53</v>
       </c>
     </row>
     <row r="59">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-36.39</v>
+        <v>-37.79</v>
       </c>
       <c r="K60" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="L60" t="n">
-        <v>36.43</v>
+        <v>37.84</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-52.22</v>
+        <v>-54.23</v>
       </c>
       <c r="K61" t="n">
-        <v>-63.87</v>
+        <v>-66.31999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>82.5</v>
+        <v>85.67</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-32.15</v>
+        <v>-33.97</v>
       </c>
       <c r="K62" t="n">
-        <v>71.94</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>78.8</v>
+        <v>83.26000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>83.7</v>
+        <v>91.31</v>
       </c>
       <c r="K63" t="n">
-        <v>-47.85</v>
+        <v>-52.2</v>
       </c>
       <c r="L63" t="n">
-        <v>96.41</v>
+        <v>105.17</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>60.41</v>
+        <v>61.59</v>
       </c>
       <c r="K64" t="n">
-        <v>-28.69</v>
+        <v>-29.25</v>
       </c>
       <c r="L64" t="n">
-        <v>66.87</v>
+        <v>68.18000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>56.22</v>
+        <v>57.32</v>
       </c>
       <c r="K65" t="n">
-        <v>39.19</v>
+        <v>39.96</v>
       </c>
       <c r="L65" t="n">
-        <v>68.53</v>
+        <v>69.87</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-133.96</v>
+        <v>-139.12</v>
       </c>
       <c r="K66" t="n">
-        <v>-54.29</v>
+        <v>-56.38</v>
       </c>
       <c r="L66" t="n">
-        <v>144.55</v>
+        <v>150.11</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-92.34</v>
+        <v>-100.73</v>
       </c>
       <c r="K67" t="n">
-        <v>80.91</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>122.77</v>
+        <v>133.93</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>8.789999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="K68" t="n">
-        <v>-139.66</v>
+        <v>-150.01</v>
       </c>
       <c r="L68" t="n">
-        <v>139.94</v>
+        <v>150.31</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-152.11</v>
+        <v>-168.4</v>
       </c>
       <c r="K69" t="n">
-        <v>-65.84999999999999</v>
+        <v>-72.91</v>
       </c>
       <c r="L69" t="n">
-        <v>165.75</v>
+        <v>183.51</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-21.1</v>
+        <v>-23.02</v>
       </c>
       <c r="K70" t="n">
-        <v>-158.99</v>
+        <v>-173.45</v>
       </c>
       <c r="L70" t="n">
-        <v>160.39</v>
+        <v>174.97</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-104.49</v>
+        <v>-106.54</v>
       </c>
       <c r="K71" t="n">
-        <v>176.93</v>
+        <v>180.4</v>
       </c>
       <c r="L71" t="n">
-        <v>205.49</v>
+        <v>209.52</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>134.47</v>
+        <v>144.43</v>
       </c>
       <c r="K72" t="n">
-        <v>-221.24</v>
+        <v>-237.63</v>
       </c>
       <c r="L72" t="n">
-        <v>258.9</v>
+        <v>278.08</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-186.57</v>
+        <v>-190.23</v>
       </c>
       <c r="K73" t="n">
-        <v>-72.34</v>
+        <v>-73.76000000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>200.1</v>
+        <v>204.03</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-70.29000000000001</v>
+        <v>-77.83</v>
       </c>
       <c r="K74" t="n">
-        <v>-57.81</v>
+        <v>-64.01000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>91.01000000000001</v>
+        <v>100.76</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>35.78</v>
+        <v>37.8</v>
       </c>
       <c r="K75" t="n">
-        <v>-61.32</v>
+        <v>-64.79000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>71</v>
+        <v>75.02</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>78.65000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="K76" t="n">
-        <v>-46.06</v>
+        <v>-50.25</v>
       </c>
       <c r="L76" t="n">
-        <v>91.15000000000001</v>
+        <v>99.43000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>-22.15</v>
+        <v>-23.79</v>
       </c>
       <c r="K77" t="n">
-        <v>-71.83</v>
+        <v>-77.15000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>75.17</v>
+        <v>80.73999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>62.45</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>-23.91</v>
+        <v>-25.26</v>
       </c>
       <c r="L78" t="n">
-        <v>66.87</v>
+        <v>70.66</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>8.800000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>-79.98999999999999</v>
+        <v>-85.91</v>
       </c>
       <c r="L79" t="n">
-        <v>80.47</v>
+        <v>86.43000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>3.17</v>
+        <v>3.46</v>
       </c>
       <c r="K80" t="n">
-        <v>-102.01</v>
+        <v>-111.29</v>
       </c>
       <c r="L80" t="n">
-        <v>102.06</v>
+        <v>111.34</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>-104.14</v>
+        <v>-115.3</v>
       </c>
       <c r="K81" t="n">
-        <v>-36.07</v>
+        <v>-39.94</v>
       </c>
       <c r="L81" t="n">
-        <v>110.21</v>
+        <v>122.02</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>121.73</v>
+        <v>128.62</v>
       </c>
       <c r="K82" t="n">
-        <v>-59.2</v>
+        <v>-62.55</v>
       </c>
       <c r="L82" t="n">
-        <v>135.36</v>
+        <v>143.02</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-102.93</v>
+        <v>-110.55</v>
       </c>
       <c r="K83" t="n">
-        <v>-78.15000000000001</v>
+        <v>-83.94</v>
       </c>
       <c r="L83" t="n">
-        <v>129.24</v>
+        <v>138.81</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>-134.96</v>
+        <v>-144.96</v>
       </c>
       <c r="K84" t="n">
-        <v>-2.88</v>
+        <v>-3.09</v>
       </c>
       <c r="L84" t="n">
-        <v>134.99</v>
+        <v>144.99</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="K85" t="n">
-        <v>130.6</v>
+        <v>135.62</v>
       </c>
       <c r="L85" t="n">
-        <v>130.61</v>
+        <v>135.63</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-87.29000000000001</v>
+        <v>-96.65000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>257.15</v>
+        <v>284.7</v>
       </c>
       <c r="L86" t="n">
-        <v>271.56</v>
+        <v>300.66</v>
       </c>
     </row>
     <row r="87">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>258.34</v>
+        <v>268.28</v>
       </c>
       <c r="K88" t="n">
-        <v>-128.87</v>
+        <v>-133.83</v>
       </c>
       <c r="L88" t="n">
-        <v>288.7</v>
+        <v>299.8</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-09.xlsx
+++ b/output/2024-07-09.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="F14" t="n">
-        <v>8.369999999999999</v>
+        <v>5.58</v>
       </c>
       <c r="G14" t="n">
-        <v>262.6</v>
+        <v>271.8</v>
       </c>
       <c r="H14" t="n">
-        <v>53.3</v>
+        <v>36</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>32.1</v>
+        <v>-3.71</v>
       </c>
       <c r="K14" t="n">
-        <v>-46.97</v>
+        <v>37.25</v>
       </c>
       <c r="L14" t="n">
-        <v>56.9</v>
+        <v>37.44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:45:24</t>
+          <t>04:45:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="F15" t="n">
-        <v>8.4</v>
+        <v>5.63</v>
       </c>
       <c r="G15" t="n">
-        <v>269.8</v>
+        <v>271.5</v>
       </c>
       <c r="H15" t="n">
-        <v>51</v>
+        <v>65.7</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J15" t="n">
-        <v>33.94</v>
+        <v>-12.29</v>
       </c>
       <c r="K15" t="n">
-        <v>-29.25</v>
+        <v>-25.48</v>
       </c>
       <c r="L15" t="n">
-        <v>44.8</v>
+        <v>28.29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:46:46</t>
+          <t>04:47:08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -712,31 +712,31 @@
         <v>1.86</v>
       </c>
       <c r="F16" t="n">
-        <v>8.27</v>
+        <v>5.82</v>
       </c>
       <c r="G16" t="n">
-        <v>262.6</v>
+        <v>260.4</v>
       </c>
       <c r="H16" t="n">
-        <v>46.7</v>
+        <v>32.9</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-21.4</v>
+        <v>-35.04</v>
       </c>
       <c r="K16" t="n">
-        <v>56.57</v>
+        <v>21.4</v>
       </c>
       <c r="L16" t="n">
-        <v>60.48</v>
+        <v>41.06</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:51:03</t>
+          <t>04:52:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="F17" t="n">
-        <v>5.76</v>
+        <v>5.01</v>
       </c>
       <c r="G17" t="n">
-        <v>262.1</v>
+        <v>267.6</v>
       </c>
       <c r="H17" t="n">
-        <v>46.3</v>
+        <v>28.6</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>14.52</v>
+        <v>32.75</v>
       </c>
       <c r="K17" t="n">
-        <v>-109.18</v>
+        <v>33.62</v>
       </c>
       <c r="L17" t="n">
-        <v>110.14</v>
+        <v>46.94</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:52:30</t>
+          <t>04:54:20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.02</v>
+        <v>1.31</v>
       </c>
       <c r="F18" t="n">
-        <v>6.67</v>
+        <v>4.23</v>
       </c>
       <c r="G18" t="n">
-        <v>252.8</v>
+        <v>282.4</v>
       </c>
       <c r="H18" t="n">
-        <v>49.3</v>
+        <v>76.8</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-78.48999999999999</v>
+        <v>34.7</v>
       </c>
       <c r="K18" t="n">
-        <v>20.5</v>
+        <v>18.6</v>
       </c>
       <c r="L18" t="n">
-        <v>81.13</v>
+        <v>39.37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:53:47</t>
+          <t>04:56:24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.12</v>
+        <v>2.07</v>
       </c>
       <c r="F19" t="n">
-        <v>1.42</v>
+        <v>7.71</v>
       </c>
       <c r="G19" t="n">
-        <v>265.6</v>
+        <v>252.8</v>
       </c>
       <c r="H19" t="n">
-        <v>56.5</v>
+        <v>41.7</v>
       </c>
       <c r="I19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>46.07</v>
+        <v>-37.97</v>
       </c>
       <c r="K19" t="n">
-        <v>1.09</v>
+        <v>14.42</v>
       </c>
       <c r="L19" t="n">
-        <v>46.08</v>
+        <v>40.62</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:58:33</t>
+          <t>05:01:07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.02</v>
+        <v>1.69</v>
       </c>
       <c r="F20" t="n">
-        <v>8.640000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="G20" t="n">
-        <v>266.2</v>
+        <v>259.2</v>
       </c>
       <c r="H20" t="n">
-        <v>49.9</v>
+        <v>60.1</v>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J20" t="n">
-        <v>90.28</v>
+        <v>-9.83</v>
       </c>
       <c r="K20" t="n">
-        <v>-39.24</v>
+        <v>-36.18</v>
       </c>
       <c r="L20" t="n">
-        <v>98.43000000000001</v>
+        <v>37.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:00:17</t>
+          <t>05:02:16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="F21" t="n">
-        <v>10.58</v>
+        <v>4.68</v>
       </c>
       <c r="G21" t="n">
-        <v>271.4</v>
+        <v>270</v>
       </c>
       <c r="H21" t="n">
-        <v>44.8</v>
+        <v>59.3</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>-24.67</v>
+        <v>45.77</v>
       </c>
       <c r="K21" t="n">
-        <v>-101.58</v>
+        <v>62.62</v>
       </c>
       <c r="L21" t="n">
-        <v>104.53</v>
+        <v>77.56999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:01:49</t>
+          <t>05:04:03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="F22" t="n">
-        <v>8.880000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="G22" t="n">
-        <v>258.8</v>
+        <v>272.8</v>
       </c>
       <c r="H22" t="n">
-        <v>44.2</v>
+        <v>62.9</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J22" t="n">
-        <v>32.68</v>
+        <v>-60.34</v>
       </c>
       <c r="K22" t="n">
-        <v>-104.09</v>
+        <v>32.96</v>
       </c>
       <c r="L22" t="n">
-        <v>109.1</v>
+        <v>68.76000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:07:04</t>
+          <t>05:08:18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.57</v>
+        <v>2.16</v>
       </c>
       <c r="F23" t="n">
-        <v>8.109999999999999</v>
+        <v>10.58</v>
       </c>
       <c r="G23" t="n">
-        <v>264.6</v>
+        <v>270.8</v>
       </c>
       <c r="H23" t="n">
-        <v>47.8</v>
+        <v>60</v>
       </c>
       <c r="I23" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>132.2</v>
+        <v>-80.68000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>1.82</v>
+        <v>-74.90000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>132.22</v>
+        <v>110.09</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:09:16</t>
+          <t>05:11:07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.3</v>
+        <v>1.58</v>
       </c>
       <c r="F24" t="n">
-        <v>8.75</v>
+        <v>2.33</v>
       </c>
       <c r="G24" t="n">
-        <v>272.1</v>
+        <v>258.1</v>
       </c>
       <c r="H24" t="n">
-        <v>50.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-121.69</v>
+        <v>-77.41</v>
       </c>
       <c r="K24" t="n">
-        <v>-79.93000000000001</v>
+        <v>75.22</v>
       </c>
       <c r="L24" t="n">
-        <v>145.6</v>
+        <v>107.93</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:11:26</t>
+          <t>05:12:59</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="F25" t="n">
-        <v>4.05</v>
+        <v>6.82</v>
       </c>
       <c r="G25" t="n">
-        <v>256.6</v>
+        <v>274.4</v>
       </c>
       <c r="H25" t="n">
-        <v>50.1</v>
+        <v>67.7</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-91.75</v>
+        <v>-39.59</v>
       </c>
       <c r="K25" t="n">
-        <v>31.39</v>
+        <v>103.28</v>
       </c>
       <c r="L25" t="n">
-        <v>96.97</v>
+        <v>110.61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:15:17</t>
+          <t>05:18:29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="F26" t="n">
-        <v>8.01</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>265.4</v>
+        <v>258.6</v>
       </c>
       <c r="H26" t="n">
-        <v>42.6</v>
+        <v>28.5</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-152.08</v>
+        <v>118</v>
       </c>
       <c r="K26" t="n">
-        <v>88.84</v>
+        <v>-82.36</v>
       </c>
       <c r="L26" t="n">
-        <v>176.13</v>
+        <v>143.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:17:45</t>
+          <t>05:20:03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.59</v>
+        <v>2.21</v>
       </c>
       <c r="F27" t="n">
-        <v>10.58</v>
+        <v>10.4</v>
       </c>
       <c r="G27" t="n">
-        <v>251</v>
+        <v>258.6</v>
       </c>
       <c r="H27" t="n">
-        <v>54.3</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J27" t="n">
-        <v>-126.82</v>
+        <v>-41.41</v>
       </c>
       <c r="K27" t="n">
-        <v>193.79</v>
+        <v>-120.09</v>
       </c>
       <c r="L27" t="n">
-        <v>231.6</v>
+        <v>127.03</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:19:26</t>
+          <t>05:21:20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.44</v>
+        <v>2.71</v>
       </c>
       <c r="F28" t="n">
-        <v>8.33</v>
+        <v>10.58</v>
       </c>
       <c r="G28" t="n">
-        <v>273.6</v>
+        <v>286.2</v>
       </c>
       <c r="H28" t="n">
-        <v>45.4</v>
+        <v>87.8</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J28" t="n">
-        <v>-227.56</v>
+        <v>-168.83</v>
       </c>
       <c r="K28" t="n">
-        <v>107.36</v>
+        <v>55.55</v>
       </c>
       <c r="L28" t="n">
-        <v>251.61</v>
+        <v>177.73</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:29:42</t>
+          <t>05:31:38</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.88</v>
+        <v>2.19</v>
       </c>
       <c r="F29" t="n">
-        <v>7.38</v>
+        <v>7.2</v>
       </c>
       <c r="G29" t="n">
-        <v>279.6</v>
+        <v>261.8</v>
       </c>
       <c r="H29" t="n">
-        <v>46.7</v>
+        <v>56.9</v>
       </c>
       <c r="I29" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-44.19</v>
+        <v>-35.16</v>
       </c>
       <c r="K29" t="n">
-        <v>-19.72</v>
+        <v>2.87</v>
       </c>
       <c r="L29" t="n">
-        <v>48.39</v>
+        <v>35.27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:30:56</t>
+          <t>05:33:01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="F30" t="n">
-        <v>9.67</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="H30" t="n">
-        <v>49.7</v>
+        <v>23.8</v>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>65.45999999999999</v>
+        <v>-26.9</v>
       </c>
       <c r="K30" t="n">
-        <v>-36.97</v>
+        <v>-13.14</v>
       </c>
       <c r="L30" t="n">
-        <v>75.18000000000001</v>
+        <v>29.94</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:31:44</t>
+          <t>05:34:26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.82</v>
+        <v>2.22</v>
       </c>
       <c r="F31" t="n">
-        <v>3.5</v>
+        <v>4.97</v>
       </c>
       <c r="G31" t="n">
-        <v>280.3</v>
+        <v>274.8</v>
       </c>
       <c r="H31" t="n">
-        <v>46.8</v>
+        <v>34.6</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.75</v>
+        <v>-23.8</v>
       </c>
       <c r="K31" t="n">
-        <v>44.63</v>
+        <v>-34.49</v>
       </c>
       <c r="L31" t="n">
-        <v>44.89</v>
+        <v>41.91</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:37:16</t>
+          <t>05:39:20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="F32" t="n">
-        <v>10.46</v>
+        <v>4.53</v>
       </c>
       <c r="G32" t="n">
-        <v>257.2</v>
+        <v>272.4</v>
       </c>
       <c r="H32" t="n">
-        <v>46.5</v>
+        <v>52.3</v>
       </c>
       <c r="I32" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>65.56</v>
+        <v>-16.48</v>
       </c>
       <c r="K32" t="n">
-        <v>46.39</v>
+        <v>-53.3</v>
       </c>
       <c r="L32" t="n">
-        <v>80.31</v>
+        <v>55.79</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:38:04</t>
+          <t>05:41:08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>9.92</v>
       </c>
       <c r="G33" t="n">
-        <v>271.5</v>
+        <v>281</v>
       </c>
       <c r="H33" t="n">
-        <v>60.2</v>
+        <v>46.8</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>12.97</v>
+        <v>35.04</v>
       </c>
       <c r="K33" t="n">
-        <v>-85.48</v>
+        <v>36.45</v>
       </c>
       <c r="L33" t="n">
-        <v>86.45999999999999</v>
+        <v>50.56</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:40:06</t>
+          <t>05:42:38</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="F34" t="n">
-        <v>8.94</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>257.5</v>
+        <v>273</v>
       </c>
       <c r="H34" t="n">
-        <v>45.6</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>-17.44</v>
+        <v>-18.99</v>
       </c>
       <c r="K34" t="n">
-        <v>98.06</v>
+        <v>45.14</v>
       </c>
       <c r="L34" t="n">
-        <v>99.59999999999999</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:45:01</t>
+          <t>05:46:54</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.12</v>
+        <v>2.74</v>
       </c>
       <c r="F35" t="n">
-        <v>7.97</v>
+        <v>7.91</v>
       </c>
       <c r="G35" t="n">
-        <v>270.5</v>
+        <v>269.8</v>
       </c>
       <c r="H35" t="n">
-        <v>43.6</v>
+        <v>42.8</v>
       </c>
       <c r="I35" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9399999999999999</v>
+        <v>-58.61</v>
       </c>
       <c r="K35" t="n">
-        <v>-90.98</v>
+        <v>14.38</v>
       </c>
       <c r="L35" t="n">
-        <v>90.98</v>
+        <v>60.35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:47:06</t>
+          <t>05:48:55</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.02</v>
+        <v>2.37</v>
       </c>
       <c r="F36" t="n">
-        <v>7.42</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>260.1</v>
+        <v>263.1</v>
       </c>
       <c r="H36" t="n">
-        <v>49.9</v>
+        <v>41.8</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J36" t="n">
-        <v>46.82</v>
+        <v>-65.58</v>
       </c>
       <c r="K36" t="n">
-        <v>-126.8</v>
+        <v>9.56</v>
       </c>
       <c r="L36" t="n">
-        <v>135.17</v>
+        <v>66.27</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:48:51</t>
+          <t>05:51:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.66</v>
+        <v>2.18</v>
       </c>
       <c r="F37" t="n">
-        <v>10.13</v>
+        <v>7.95</v>
       </c>
       <c r="G37" t="n">
-        <v>267.4</v>
+        <v>267.9</v>
       </c>
       <c r="H37" t="n">
-        <v>55.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J37" t="n">
-        <v>-121.69</v>
+        <v>44.7</v>
       </c>
       <c r="K37" t="n">
-        <v>31.11</v>
+        <v>74.55</v>
       </c>
       <c r="L37" t="n">
-        <v>125.6</v>
+        <v>86.93000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:52:44</t>
+          <t>05:55:19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.06</v>
+        <v>2.12</v>
       </c>
       <c r="F38" t="n">
-        <v>10.58</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>254.6</v>
+        <v>273.4</v>
       </c>
       <c r="H38" t="n">
-        <v>54</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J38" t="n">
-        <v>-123.83</v>
+        <v>-115.16</v>
       </c>
       <c r="K38" t="n">
-        <v>113.21</v>
+        <v>44.9</v>
       </c>
       <c r="L38" t="n">
-        <v>167.78</v>
+        <v>123.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:53:32</t>
+          <t>05:56:16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="F39" t="n">
-        <v>10.58</v>
+        <v>10.56</v>
       </c>
       <c r="G39" t="n">
-        <v>261.7</v>
+        <v>272.9</v>
       </c>
       <c r="H39" t="n">
-        <v>45.8</v>
+        <v>96.2</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-48.83</v>
+        <v>37.06</v>
       </c>
       <c r="K39" t="n">
-        <v>179.84</v>
+        <v>136.15</v>
       </c>
       <c r="L39" t="n">
-        <v>186.35</v>
+        <v>141.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:55:19</t>
+          <t>05:57:22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="F40" t="n">
         <v>10.58</v>
       </c>
       <c r="G40" t="n">
-        <v>262.4</v>
+        <v>265.4</v>
       </c>
       <c r="H40" t="n">
-        <v>40.5</v>
+        <v>61.5</v>
       </c>
       <c r="I40" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>165.27</v>
+        <v>60.17</v>
       </c>
       <c r="K40" t="n">
-        <v>31.76</v>
+        <v>-143.72</v>
       </c>
       <c r="L40" t="n">
-        <v>168.29</v>
+        <v>155.81</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:58:21</t>
+          <t>06:02:44</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="F41" t="n">
-        <v>8.98</v>
+        <v>10.58</v>
       </c>
       <c r="G41" t="n">
-        <v>263.7</v>
+        <v>279.3</v>
       </c>
       <c r="H41" t="n">
-        <v>50.3</v>
+        <v>49.1</v>
       </c>
       <c r="I41" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J41" t="n">
-        <v>-220.08</v>
+        <v>45.31</v>
       </c>
       <c r="K41" t="n">
-        <v>39.84</v>
+        <v>-156.88</v>
       </c>
       <c r="L41" t="n">
-        <v>223.66</v>
+        <v>163.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:00:15</t>
+          <t>06:04:22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="F42" t="n">
-        <v>8.06</v>
+        <v>9.83</v>
       </c>
       <c r="G42" t="n">
-        <v>273.8</v>
+        <v>273.2</v>
       </c>
       <c r="H42" t="n">
-        <v>48.4</v>
+        <v>52.3</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J42" t="n">
-        <v>-191.23</v>
+        <v>-124.13</v>
       </c>
       <c r="K42" t="n">
-        <v>156.58</v>
+        <v>209.56</v>
       </c>
       <c r="L42" t="n">
-        <v>247.16</v>
+        <v>243.56</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:01:28</t>
+          <t>06:06:11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.33</v>
+        <v>2.17</v>
       </c>
       <c r="F43" t="n">
         <v>10.58</v>
       </c>
       <c r="G43" t="n">
-        <v>261.5</v>
+        <v>280.1</v>
       </c>
       <c r="H43" t="n">
-        <v>53.2</v>
+        <v>63.9</v>
       </c>
       <c r="I43" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J43" t="n">
-        <v>-181.99</v>
+        <v>-143.13</v>
       </c>
       <c r="K43" t="n">
-        <v>-101.63</v>
+        <v>-165.26</v>
       </c>
       <c r="L43" t="n">
-        <v>208.44</v>
+        <v>218.62</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:11:14</t>
+          <t>06:17:58</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.54</v>
+        <v>2.35</v>
       </c>
       <c r="F44" t="n">
-        <v>9.720000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="G44" t="n">
-        <v>255.1</v>
+        <v>260.3</v>
       </c>
       <c r="H44" t="n">
-        <v>44.3</v>
+        <v>36.7</v>
       </c>
       <c r="I44" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J44" t="n">
-        <v>21.2</v>
+        <v>-28.57</v>
       </c>
       <c r="K44" t="n">
-        <v>-60.1</v>
+        <v>-9.77</v>
       </c>
       <c r="L44" t="n">
-        <v>63.73</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:12:38</t>
+          <t>06:19:28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="F45" t="n">
         <v>10.58</v>
       </c>
       <c r="G45" t="n">
-        <v>252.5</v>
+        <v>266.6</v>
       </c>
       <c r="H45" t="n">
-        <v>59.3</v>
+        <v>43.2</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J45" t="n">
-        <v>-73.53</v>
+        <v>-4.19</v>
       </c>
       <c r="K45" t="n">
-        <v>-47.39</v>
+        <v>22.43</v>
       </c>
       <c r="L45" t="n">
-        <v>87.48</v>
+        <v>22.82</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:13:44</t>
+          <t>06:20:46</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.32</v>
+        <v>1.96</v>
       </c>
       <c r="F46" t="n">
-        <v>8.82</v>
+        <v>6.22</v>
       </c>
       <c r="G46" t="n">
-        <v>260.6</v>
+        <v>264.6</v>
       </c>
       <c r="H46" t="n">
-        <v>53.3</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-23.15</v>
+        <v>-28.93</v>
       </c>
       <c r="K46" t="n">
-        <v>-47.08</v>
+        <v>-2.08</v>
       </c>
       <c r="L46" t="n">
-        <v>52.46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:19:29</t>
+          <t>06:25:33</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.07</v>
+        <v>2.32</v>
       </c>
       <c r="F47" t="n">
-        <v>9.32</v>
+        <v>6.35</v>
       </c>
       <c r="G47" t="n">
-        <v>259.9</v>
+        <v>265.3</v>
       </c>
       <c r="H47" t="n">
-        <v>44.4</v>
+        <v>24.1</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>-79.58</v>
+        <v>-40.57</v>
       </c>
       <c r="K47" t="n">
-        <v>13.28</v>
+        <v>-22.22</v>
       </c>
       <c r="L47" t="n">
-        <v>80.68000000000001</v>
+        <v>46.25</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:21:51</t>
+          <t>06:28:07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="F48" t="n">
-        <v>7.58</v>
+        <v>10.4</v>
       </c>
       <c r="G48" t="n">
-        <v>265.9</v>
+        <v>263</v>
       </c>
       <c r="H48" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>40.65</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>68.28</v>
+        <v>6.33</v>
       </c>
       <c r="L48" t="n">
-        <v>79.45999999999999</v>
+        <v>68.39</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:23:01</t>
+          <t>06:29:33</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="F49" t="n">
-        <v>9.609999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="G49" t="n">
-        <v>274</v>
+        <v>264.6</v>
       </c>
       <c r="H49" t="n">
-        <v>53.5</v>
+        <v>14.8</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>34.93</v>
+        <v>43.61</v>
       </c>
       <c r="K49" t="n">
-        <v>-86.41</v>
+        <v>-48.6</v>
       </c>
       <c r="L49" t="n">
-        <v>93.20999999999999</v>
+        <v>65.29000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:27:27</t>
+          <t>06:34:51</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.59</v>
+        <v>2.26</v>
       </c>
       <c r="F50" t="n">
-        <v>8.779999999999999</v>
+        <v>7.76</v>
       </c>
       <c r="G50" t="n">
-        <v>259.6</v>
+        <v>255.2</v>
       </c>
       <c r="H50" t="n">
-        <v>47.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>105.13</v>
+        <v>6.26</v>
       </c>
       <c r="K50" t="n">
-        <v>30.54</v>
+        <v>-109.79</v>
       </c>
       <c r="L50" t="n">
-        <v>109.47</v>
+        <v>109.97</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:28:14</t>
+          <t>06:37:06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="F51" t="n">
-        <v>3.74</v>
+        <v>6.88</v>
       </c>
       <c r="G51" t="n">
-        <v>260.2</v>
+        <v>274.1</v>
       </c>
       <c r="H51" t="n">
-        <v>45.7</v>
+        <v>55.1</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>83.26000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>-18.75</v>
+        <v>7.84</v>
       </c>
       <c r="L51" t="n">
-        <v>85.34999999999999</v>
+        <v>82.28</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:29:11</t>
+          <t>06:39:34</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.68</v>
+        <v>2.15</v>
       </c>
       <c r="F52" t="n">
-        <v>10.2</v>
+        <v>9.06</v>
       </c>
       <c r="G52" t="n">
-        <v>276</v>
+        <v>261.8</v>
       </c>
       <c r="H52" t="n">
-        <v>48.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>-2.69</v>
+        <v>-79.51000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-144.89</v>
+        <v>33.9</v>
       </c>
       <c r="L52" t="n">
-        <v>144.92</v>
+        <v>86.44</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:34:50</t>
+          <t>06:45:29</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="F53" t="n">
-        <v>2.96</v>
+        <v>7.93</v>
       </c>
       <c r="G53" t="n">
-        <v>261.3</v>
+        <v>258.3</v>
       </c>
       <c r="H53" t="n">
-        <v>50.7</v>
+        <v>41.6</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J53" t="n">
-        <v>136.63</v>
+        <v>54.31</v>
       </c>
       <c r="K53" t="n">
-        <v>111.63</v>
+        <v>-114.39</v>
       </c>
       <c r="L53" t="n">
-        <v>176.44</v>
+        <v>126.63</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:37:16</t>
+          <t>06:46:13</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.29</v>
+        <v>2.07</v>
       </c>
       <c r="F54" t="n">
-        <v>10.58</v>
+        <v>9.69</v>
       </c>
       <c r="G54" t="n">
-        <v>266.7</v>
+        <v>277.4</v>
       </c>
       <c r="H54" t="n">
-        <v>46</v>
+        <v>56.2</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-78.3</v>
+        <v>113.88</v>
       </c>
       <c r="K54" t="n">
-        <v>-190.88</v>
+        <v>-76.23</v>
       </c>
       <c r="L54" t="n">
-        <v>206.32</v>
+        <v>137.04</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:39:40</t>
+          <t>06:47:51</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.88</v>
+        <v>2.47</v>
       </c>
       <c r="F55" t="n">
-        <v>5.61</v>
+        <v>8.16</v>
       </c>
       <c r="G55" t="n">
-        <v>272.8</v>
+        <v>267.5</v>
       </c>
       <c r="H55" t="n">
-        <v>42.2</v>
+        <v>53.8</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>-48.41</v>
+        <v>131.37</v>
       </c>
       <c r="K55" t="n">
-        <v>-106.48</v>
+        <v>43.09</v>
       </c>
       <c r="L55" t="n">
-        <v>116.97</v>
+        <v>138.26</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:44:59</t>
+          <t>06:52:47</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.8</v>
+        <v>2.09</v>
       </c>
       <c r="F56" t="n">
-        <v>10.58</v>
+        <v>5.36</v>
       </c>
       <c r="G56" t="n">
-        <v>278.7</v>
+        <v>256.6</v>
       </c>
       <c r="H56" t="n">
-        <v>50.9</v>
+        <v>55.9</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.14</v>
+        <v>-157.72</v>
       </c>
       <c r="K56" t="n">
-        <v>260.01</v>
+        <v>3.72</v>
       </c>
       <c r="L56" t="n">
-        <v>260.21</v>
+        <v>157.77</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:47:15</t>
+          <t>06:55:04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="F57" t="n">
-        <v>9.369999999999999</v>
+        <v>7.26</v>
       </c>
       <c r="G57" t="n">
-        <v>278.1</v>
+        <v>267.9</v>
       </c>
       <c r="H57" t="n">
-        <v>53.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-203.43</v>
+        <v>-73.05</v>
       </c>
       <c r="K57" t="n">
-        <v>-153.23</v>
+        <v>-135.95</v>
       </c>
       <c r="L57" t="n">
-        <v>254.68</v>
+        <v>154.33</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:48:31</t>
+          <t>06:57:23</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.54</v>
+        <v>2.71</v>
       </c>
       <c r="F58" t="n">
-        <v>10.58</v>
+        <v>7.95</v>
       </c>
       <c r="G58" t="n">
-        <v>262.9</v>
+        <v>278.5</v>
       </c>
       <c r="H58" t="n">
-        <v>50.9</v>
+        <v>22.4</v>
       </c>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-275.97</v>
+        <v>-290</v>
       </c>
       <c r="K58" t="n">
-        <v>241.22</v>
+        <v>-28.72</v>
       </c>
       <c r="L58" t="n">
-        <v>366.53</v>
+        <v>291.42</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:00:39</t>
+          <t>07:07:42</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="F59" t="n">
-        <v>10.58</v>
+        <v>10.12</v>
       </c>
       <c r="G59" t="n">
-        <v>259.6</v>
+        <v>268.5</v>
       </c>
       <c r="H59" t="n">
-        <v>47</v>
+        <v>43.1</v>
       </c>
       <c r="I59" t="n">
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>84.91</v>
+        <v>-12.7</v>
       </c>
       <c r="K59" t="n">
-        <v>-33.07</v>
+        <v>40.67</v>
       </c>
       <c r="L59" t="n">
-        <v>91.12</v>
+        <v>42.61</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:02:22</t>
+          <t>07:10:30</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.95</v>
+        <v>2.68</v>
       </c>
       <c r="F60" t="n">
-        <v>3.88</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>275.3</v>
+        <v>277.7</v>
       </c>
       <c r="H60" t="n">
-        <v>44.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-37.79</v>
+        <v>-35.33</v>
       </c>
       <c r="K60" t="n">
-        <v>1.89</v>
+        <v>-6.51</v>
       </c>
       <c r="L60" t="n">
-        <v>37.84</v>
+        <v>35.93</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:04:13</t>
+          <t>07:12:44</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="F61" t="n">
-        <v>10.58</v>
+        <v>8.08</v>
       </c>
       <c r="G61" t="n">
-        <v>275.7</v>
+        <v>258.8</v>
       </c>
       <c r="H61" t="n">
-        <v>45.8</v>
+        <v>60.7</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>-54.23</v>
+        <v>37.12</v>
       </c>
       <c r="K61" t="n">
-        <v>-66.31999999999999</v>
+        <v>4.06</v>
       </c>
       <c r="L61" t="n">
-        <v>85.67</v>
+        <v>37.34</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:08:38</t>
+          <t>07:18:22</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.29</v>
+        <v>2.09</v>
       </c>
       <c r="F62" t="n">
-        <v>6.73</v>
+        <v>10.58</v>
       </c>
       <c r="G62" t="n">
-        <v>268</v>
+        <v>253.3</v>
       </c>
       <c r="H62" t="n">
-        <v>48.1</v>
+        <v>52</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-33.97</v>
+        <v>-15.32</v>
       </c>
       <c r="K62" t="n">
-        <v>76.01000000000001</v>
+        <v>-39.01</v>
       </c>
       <c r="L62" t="n">
-        <v>83.26000000000001</v>
+        <v>41.91</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:10:03</t>
+          <t>07:20:27</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="F63" t="n">
-        <v>10.58</v>
+        <v>10.27</v>
       </c>
       <c r="G63" t="n">
-        <v>277.9</v>
+        <v>268.4</v>
       </c>
       <c r="H63" t="n">
-        <v>55</v>
+        <v>57.3</v>
       </c>
       <c r="I63" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>91.31</v>
+        <v>30.6</v>
       </c>
       <c r="K63" t="n">
-        <v>-52.2</v>
+        <v>-48.3</v>
       </c>
       <c r="L63" t="n">
-        <v>105.17</v>
+        <v>57.17</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:11:08</t>
+          <t>07:21:09</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="F64" t="n">
-        <v>10.58</v>
+        <v>4.72</v>
       </c>
       <c r="G64" t="n">
-        <v>271.8</v>
+        <v>256.5</v>
       </c>
       <c r="H64" t="n">
-        <v>44.8</v>
+        <v>34.3</v>
       </c>
       <c r="I64" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>61.59</v>
+        <v>52.84</v>
       </c>
       <c r="K64" t="n">
-        <v>-29.25</v>
+        <v>-26.25</v>
       </c>
       <c r="L64" t="n">
-        <v>68.18000000000001</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:15:40</t>
+          <t>07:26:49</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.49</v>
+        <v>2.58</v>
       </c>
       <c r="F65" t="n">
-        <v>10.58</v>
+        <v>9.58</v>
       </c>
       <c r="G65" t="n">
-        <v>282.9</v>
+        <v>267.2</v>
       </c>
       <c r="H65" t="n">
-        <v>49.3</v>
+        <v>40.7</v>
       </c>
       <c r="I65" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>57.32</v>
+        <v>-82.78</v>
       </c>
       <c r="K65" t="n">
-        <v>39.96</v>
+        <v>-43.59</v>
       </c>
       <c r="L65" t="n">
-        <v>69.87</v>
+        <v>93.56</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:17:24</t>
+          <t>07:28:03</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="F66" t="n">
-        <v>9.859999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="G66" t="n">
-        <v>282.3</v>
+        <v>271.9</v>
       </c>
       <c r="H66" t="n">
-        <v>46.4</v>
+        <v>61.7</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J66" t="n">
-        <v>-139.12</v>
+        <v>-32.72</v>
       </c>
       <c r="K66" t="n">
-        <v>-56.38</v>
+        <v>67.38</v>
       </c>
       <c r="L66" t="n">
-        <v>150.11</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:19:17</t>
+          <t>07:29:59</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.99</v>
+        <v>2.72</v>
       </c>
       <c r="F67" t="n">
-        <v>7.16</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G67" t="n">
-        <v>272.3</v>
+        <v>275.5</v>
       </c>
       <c r="H67" t="n">
-        <v>53.4</v>
+        <v>44.5</v>
       </c>
       <c r="I67" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J67" t="n">
-        <v>-100.73</v>
+        <v>77.37</v>
       </c>
       <c r="K67" t="n">
-        <v>88.26000000000001</v>
+        <v>6.59</v>
       </c>
       <c r="L67" t="n">
-        <v>133.93</v>
+        <v>77.65000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:23:52</t>
+          <t>07:33:56</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="F68" t="n">
         <v>10.58</v>
       </c>
       <c r="G68" t="n">
-        <v>275.7</v>
+        <v>269</v>
       </c>
       <c r="H68" t="n">
-        <v>43.6</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>9.44</v>
+        <v>-148.61</v>
       </c>
       <c r="K68" t="n">
-        <v>-150.01</v>
+        <v>-36.66</v>
       </c>
       <c r="L68" t="n">
-        <v>150.31</v>
+        <v>153.07</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:25:33</t>
+          <t>07:35:46</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="F69" t="n">
-        <v>8.52</v>
+        <v>10.58</v>
       </c>
       <c r="G69" t="n">
-        <v>275.3</v>
+        <v>273.3</v>
       </c>
       <c r="H69" t="n">
-        <v>49.8</v>
+        <v>62.1</v>
       </c>
       <c r="I69" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-168.4</v>
+        <v>-102.96</v>
       </c>
       <c r="K69" t="n">
-        <v>-72.91</v>
+        <v>-120.68</v>
       </c>
       <c r="L69" t="n">
-        <v>183.51</v>
+        <v>158.63</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:27:38</t>
+          <t>07:38:11</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.13</v>
+        <v>2.16</v>
       </c>
       <c r="F70" t="n">
-        <v>10.58</v>
+        <v>10.03</v>
       </c>
       <c r="G70" t="n">
-        <v>268.3</v>
+        <v>269.9</v>
       </c>
       <c r="H70" t="n">
-        <v>52</v>
+        <v>31.3</v>
       </c>
       <c r="I70" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-23.02</v>
+        <v>-114.71</v>
       </c>
       <c r="K70" t="n">
-        <v>-173.45</v>
+        <v>-31.35</v>
       </c>
       <c r="L70" t="n">
-        <v>174.97</v>
+        <v>118.92</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:32:25</t>
+          <t>07:41:22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="F71" t="n">
         <v>10.58</v>
       </c>
       <c r="G71" t="n">
-        <v>272.6</v>
+        <v>267.1</v>
       </c>
       <c r="H71" t="n">
-        <v>48.7</v>
+        <v>33.9</v>
       </c>
       <c r="I71" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-106.54</v>
+        <v>125.73</v>
       </c>
       <c r="K71" t="n">
-        <v>180.4</v>
+        <v>-117.26</v>
       </c>
       <c r="L71" t="n">
-        <v>209.52</v>
+        <v>171.92</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:33:54</t>
+          <t>07:42:42</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="F72" t="n">
         <v>10.58</v>
       </c>
       <c r="G72" t="n">
-        <v>263.1</v>
+        <v>249.4</v>
       </c>
       <c r="H72" t="n">
-        <v>50</v>
+        <v>31.4</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>144.43</v>
+        <v>-52.38</v>
       </c>
       <c r="K72" t="n">
-        <v>-237.63</v>
+        <v>-145.02</v>
       </c>
       <c r="L72" t="n">
-        <v>278.08</v>
+        <v>154.19</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:34:58</t>
+          <t>07:43:26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.1</v>
+        <v>2.51</v>
       </c>
       <c r="F73" t="n">
-        <v>7.48</v>
+        <v>7.14</v>
       </c>
       <c r="G73" t="n">
-        <v>258.5</v>
+        <v>276.4</v>
       </c>
       <c r="H73" t="n">
-        <v>54.1</v>
+        <v>67.8</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-190.23</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="K73" t="n">
-        <v>-73.76000000000001</v>
+        <v>99.23</v>
       </c>
       <c r="L73" t="n">
-        <v>204.03</v>
+        <v>121.75</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:43:32</t>
+          <t>07:55:10</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="F74" t="n">
-        <v>8.949999999999999</v>
+        <v>10.58</v>
       </c>
       <c r="G74" t="n">
-        <v>262.4</v>
+        <v>274.5</v>
       </c>
       <c r="H74" t="n">
-        <v>52.6</v>
+        <v>54.6</v>
       </c>
       <c r="I74" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J74" t="n">
-        <v>-77.83</v>
+        <v>40.16</v>
       </c>
       <c r="K74" t="n">
-        <v>-64.01000000000001</v>
+        <v>-3.87</v>
       </c>
       <c r="L74" t="n">
-        <v>100.76</v>
+        <v>40.35</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:45:52</t>
+          <t>07:56:25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="F75" t="n">
         <v>10.58</v>
       </c>
       <c r="G75" t="n">
-        <v>269.7</v>
+        <v>274.6</v>
       </c>
       <c r="H75" t="n">
-        <v>51</v>
+        <v>26.2</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J75" t="n">
-        <v>37.8</v>
+        <v>-28.28</v>
       </c>
       <c r="K75" t="n">
-        <v>-64.79000000000001</v>
+        <v>-30.46</v>
       </c>
       <c r="L75" t="n">
-        <v>75.02</v>
+        <v>41.56</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:47:07</t>
+          <t>07:57:24</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="F76" t="n">
-        <v>10.58</v>
+        <v>7.94</v>
       </c>
       <c r="G76" t="n">
-        <v>269.9</v>
+        <v>260.1</v>
       </c>
       <c r="H76" t="n">
-        <v>55.8</v>
+        <v>53.1</v>
       </c>
       <c r="I76" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J76" t="n">
-        <v>85.8</v>
+        <v>21.6</v>
       </c>
       <c r="K76" t="n">
-        <v>-50.25</v>
+        <v>-22.99</v>
       </c>
       <c r="L76" t="n">
-        <v>99.43000000000001</v>
+        <v>31.54</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:52:43</t>
+          <t>08:03:19</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="F77" t="n">
-        <v>9.25</v>
+        <v>10.51</v>
       </c>
       <c r="G77" t="n">
-        <v>271.4</v>
+        <v>259.5</v>
       </c>
       <c r="H77" t="n">
-        <v>49.7</v>
+        <v>67.8</v>
       </c>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J77" t="n">
-        <v>-23.79</v>
+        <v>7.63</v>
       </c>
       <c r="K77" t="n">
-        <v>-77.15000000000001</v>
+        <v>-37.38</v>
       </c>
       <c r="L77" t="n">
-        <v>80.73999999999999</v>
+        <v>38.15</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:55:02</t>
+          <t>08:04:15</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="F78" t="n">
-        <v>10.58</v>
+        <v>7.35</v>
       </c>
       <c r="G78" t="n">
-        <v>250.3</v>
+        <v>256.9</v>
       </c>
       <c r="H78" t="n">
-        <v>47.7</v>
+        <v>54.8</v>
       </c>
       <c r="I78" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>65.98999999999999</v>
+        <v>17.19</v>
       </c>
       <c r="K78" t="n">
-        <v>-25.26</v>
+        <v>102.44</v>
       </c>
       <c r="L78" t="n">
-        <v>70.66</v>
+        <v>103.87</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:56:33</t>
+          <t>08:06:23</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.29</v>
+        <v>2.64</v>
       </c>
       <c r="F79" t="n">
         <v>10.58</v>
       </c>
       <c r="G79" t="n">
-        <v>269.9</v>
+        <v>271.1</v>
       </c>
       <c r="H79" t="n">
-        <v>41.7</v>
+        <v>39.3</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J79" t="n">
-        <v>9.449999999999999</v>
+        <v>48.83</v>
       </c>
       <c r="K79" t="n">
-        <v>-85.91</v>
+        <v>-28.03</v>
       </c>
       <c r="L79" t="n">
-        <v>86.43000000000001</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:00:41</t>
+          <t>08:11:43</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.13</v>
+        <v>2.52</v>
       </c>
       <c r="F80" t="n">
         <v>10.58</v>
       </c>
       <c r="G80" t="n">
-        <v>253.9</v>
+        <v>278.1</v>
       </c>
       <c r="H80" t="n">
-        <v>48.4</v>
+        <v>17.4</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>3.46</v>
+        <v>71.61</v>
       </c>
       <c r="K80" t="n">
-        <v>-111.29</v>
+        <v>-38.79</v>
       </c>
       <c r="L80" t="n">
-        <v>111.34</v>
+        <v>81.44</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:02:04</t>
+          <t>08:13:18</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="F81" t="n">
         <v>10.58</v>
       </c>
       <c r="G81" t="n">
-        <v>269.3</v>
+        <v>260.9</v>
       </c>
       <c r="H81" t="n">
-        <v>50.6</v>
+        <v>45.4</v>
       </c>
       <c r="I81" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>-115.3</v>
+        <v>-85.05</v>
       </c>
       <c r="K81" t="n">
-        <v>-39.94</v>
+        <v>22.49</v>
       </c>
       <c r="L81" t="n">
-        <v>122.02</v>
+        <v>87.97</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:04:21</t>
+          <t>08:14:49</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.77</v>
+        <v>2.05</v>
       </c>
       <c r="F82" t="n">
-        <v>8.49</v>
+        <v>8.16</v>
       </c>
       <c r="G82" t="n">
-        <v>274</v>
+        <v>266.5</v>
       </c>
       <c r="H82" t="n">
-        <v>47.9</v>
+        <v>28.3</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J82" t="n">
-        <v>128.62</v>
+        <v>56.91</v>
       </c>
       <c r="K82" t="n">
-        <v>-62.55</v>
+        <v>54.19</v>
       </c>
       <c r="L82" t="n">
-        <v>143.02</v>
+        <v>78.59</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:08:26</t>
+          <t>08:20:17</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.81</v>
+        <v>2.26</v>
       </c>
       <c r="F83" t="n">
-        <v>10.58</v>
+        <v>6.56</v>
       </c>
       <c r="G83" t="n">
-        <v>271.7</v>
+        <v>276.3</v>
       </c>
       <c r="H83" t="n">
-        <v>43.6</v>
+        <v>50.2</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J83" t="n">
-        <v>-110.55</v>
+        <v>-87.11</v>
       </c>
       <c r="K83" t="n">
-        <v>-83.94</v>
+        <v>-60.22</v>
       </c>
       <c r="L83" t="n">
-        <v>138.81</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:10:32</t>
+          <t>08:22:46</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.97</v>
+        <v>2.33</v>
       </c>
       <c r="F84" t="n">
-        <v>8.630000000000001</v>
+        <v>7.84</v>
       </c>
       <c r="G84" t="n">
-        <v>264.7</v>
+        <v>258.5</v>
       </c>
       <c r="H84" t="n">
-        <v>45</v>
+        <v>60.4</v>
       </c>
       <c r="I84" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J84" t="n">
-        <v>-144.96</v>
+        <v>25.21</v>
       </c>
       <c r="K84" t="n">
-        <v>-3.09</v>
+        <v>-111.82</v>
       </c>
       <c r="L84" t="n">
-        <v>144.99</v>
+        <v>114.62</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:12:29</t>
+          <t>08:24:43</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="F85" t="n">
-        <v>7.97</v>
+        <v>10.58</v>
       </c>
       <c r="G85" t="n">
-        <v>275.5</v>
+        <v>259.4</v>
       </c>
       <c r="H85" t="n">
-        <v>38.9</v>
+        <v>37.1</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J85" t="n">
-        <v>1.76</v>
+        <v>-109.35</v>
       </c>
       <c r="K85" t="n">
-        <v>135.62</v>
+        <v>91.16</v>
       </c>
       <c r="L85" t="n">
-        <v>135.63</v>
+        <v>142.36</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:16:37</t>
+          <t>08:28:31</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="F86" t="n">
-        <v>10.57</v>
+        <v>10.58</v>
       </c>
       <c r="G86" t="n">
-        <v>270.7</v>
+        <v>261.8</v>
       </c>
       <c r="H86" t="n">
-        <v>47</v>
+        <v>33.9</v>
       </c>
       <c r="I86" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>-96.65000000000001</v>
+        <v>-163.99</v>
       </c>
       <c r="K86" t="n">
-        <v>284.7</v>
+        <v>-22.32</v>
       </c>
       <c r="L86" t="n">
-        <v>300.66</v>
+        <v>165.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:18:33</t>
+          <t>08:29:18</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.56</v>
+        <v>2.85</v>
       </c>
       <c r="F87" t="n">
-        <v>10.58</v>
+        <v>10.05</v>
       </c>
       <c r="G87" t="n">
-        <v>260.9</v>
+        <v>278.4</v>
       </c>
       <c r="H87" t="n">
-        <v>55.4</v>
+        <v>68.3</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-152.28</v>
+        <v>-47.71</v>
       </c>
       <c r="K87" t="n">
-        <v>-94.54000000000001</v>
+        <v>-112.7</v>
       </c>
       <c r="L87" t="n">
-        <v>179.25</v>
+        <v>122.38</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:20:44</t>
+          <t>08:31:38</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.67</v>
+        <v>2.89</v>
       </c>
       <c r="F88" t="n">
         <v>10.58</v>
       </c>
       <c r="G88" t="n">
-        <v>281.7</v>
+        <v>271.6</v>
       </c>
       <c r="H88" t="n">
-        <v>44.1</v>
+        <v>29.1</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>268.28</v>
+        <v>-131.1</v>
       </c>
       <c r="K88" t="n">
-        <v>-133.83</v>
+        <v>-4.9</v>
       </c>
       <c r="L88" t="n">
-        <v>299.8</v>
+        <v>131.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-09.xlsx
+++ b/output/2024-07-09.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="F14" t="n">
-        <v>5.58</v>
+        <v>6.54</v>
       </c>
       <c r="G14" t="n">
-        <v>271.8</v>
+        <v>275</v>
       </c>
       <c r="H14" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.71</v>
+        <v>11.01</v>
       </c>
       <c r="K14" t="n">
-        <v>37.25</v>
+        <v>40.25</v>
       </c>
       <c r="L14" t="n">
-        <v>37.44</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:45:28</t>
+          <t>04:44:19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="F15" t="n">
-        <v>5.63</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>271.5</v>
+        <v>272.6</v>
       </c>
       <c r="H15" t="n">
-        <v>65.7</v>
+        <v>34.3</v>
       </c>
       <c r="I15" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-12.29</v>
+        <v>13.64</v>
       </c>
       <c r="K15" t="n">
-        <v>-25.48</v>
+        <v>21.75</v>
       </c>
       <c r="L15" t="n">
-        <v>28.29</v>
+        <v>25.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:47:08</t>
+          <t>04:45:59</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.86</v>
+        <v>2.72</v>
       </c>
       <c r="F16" t="n">
-        <v>5.82</v>
+        <v>10.27</v>
       </c>
       <c r="G16" t="n">
-        <v>260.4</v>
+        <v>266.4</v>
       </c>
       <c r="H16" t="n">
-        <v>32.9</v>
+        <v>60.7</v>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-35.04</v>
+        <v>-38.51</v>
       </c>
       <c r="K16" t="n">
-        <v>21.4</v>
+        <v>-3.23</v>
       </c>
       <c r="L16" t="n">
-        <v>41.06</v>
+        <v>38.65</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:52:33</t>
+          <t>04:50:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="F17" t="n">
-        <v>5.01</v>
+        <v>9.91</v>
       </c>
       <c r="G17" t="n">
-        <v>267.6</v>
+        <v>262.2</v>
       </c>
       <c r="H17" t="n">
-        <v>28.6</v>
+        <v>37.8</v>
       </c>
       <c r="I17" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>32.75</v>
+        <v>-63.47</v>
       </c>
       <c r="K17" t="n">
-        <v>33.62</v>
+        <v>-24.02</v>
       </c>
       <c r="L17" t="n">
-        <v>46.94</v>
+        <v>67.86</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:54:20</t>
+          <t>04:53:09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.31</v>
+        <v>1.88</v>
       </c>
       <c r="F18" t="n">
-        <v>4.23</v>
+        <v>10.58</v>
       </c>
       <c r="G18" t="n">
-        <v>282.4</v>
+        <v>257.1</v>
       </c>
       <c r="H18" t="n">
-        <v>76.8</v>
+        <v>29.6</v>
       </c>
       <c r="I18" t="n">
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>34.7</v>
+        <v>22.85</v>
       </c>
       <c r="K18" t="n">
-        <v>18.6</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>39.37</v>
+        <v>84.55</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:56:24</t>
+          <t>04:54:49</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.07</v>
+        <v>1.84</v>
       </c>
       <c r="F19" t="n">
-        <v>7.71</v>
+        <v>10.58</v>
       </c>
       <c r="G19" t="n">
-        <v>252.8</v>
+        <v>262.6</v>
       </c>
       <c r="H19" t="n">
-        <v>41.7</v>
+        <v>65.7</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-37.97</v>
+        <v>-41.49</v>
       </c>
       <c r="K19" t="n">
-        <v>14.42</v>
+        <v>33.38</v>
       </c>
       <c r="L19" t="n">
-        <v>40.62</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:01:07</t>
+          <t>04:59:06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="F20" t="n">
-        <v>8.6</v>
+        <v>5.05</v>
       </c>
       <c r="G20" t="n">
-        <v>259.2</v>
+        <v>267.2</v>
       </c>
       <c r="H20" t="n">
-        <v>60.1</v>
+        <v>41.5</v>
       </c>
       <c r="I20" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.83</v>
+        <v>-75.45</v>
       </c>
       <c r="K20" t="n">
-        <v>-36.18</v>
+        <v>-10.34</v>
       </c>
       <c r="L20" t="n">
-        <v>37.49</v>
+        <v>76.15000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:02:16</t>
+          <t>05:00:55</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="F21" t="n">
-        <v>4.68</v>
+        <v>7.88</v>
       </c>
       <c r="G21" t="n">
-        <v>270</v>
+        <v>271.2</v>
       </c>
       <c r="H21" t="n">
-        <v>59.3</v>
+        <v>48.2</v>
       </c>
       <c r="I21" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>45.77</v>
+        <v>5.61</v>
       </c>
       <c r="K21" t="n">
-        <v>62.62</v>
+        <v>111.29</v>
       </c>
       <c r="L21" t="n">
-        <v>77.56999999999999</v>
+        <v>111.43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:04:03</t>
+          <t>05:02:15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="F22" t="n">
-        <v>10.58</v>
+        <v>4.41</v>
       </c>
       <c r="G22" t="n">
-        <v>272.8</v>
+        <v>265</v>
       </c>
       <c r="H22" t="n">
-        <v>62.9</v>
+        <v>51.9</v>
       </c>
       <c r="I22" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>-60.34</v>
+        <v>-56.66</v>
       </c>
       <c r="K22" t="n">
-        <v>32.96</v>
+        <v>75.27</v>
       </c>
       <c r="L22" t="n">
-        <v>68.76000000000001</v>
+        <v>94.20999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:08:18</t>
+          <t>05:07:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.16</v>
+        <v>1.74</v>
       </c>
       <c r="F23" t="n">
-        <v>10.58</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>270.8</v>
+        <v>266</v>
       </c>
       <c r="H23" t="n">
-        <v>60</v>
+        <v>60.3</v>
       </c>
       <c r="I23" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-80.68000000000001</v>
+        <v>-124.91</v>
       </c>
       <c r="K23" t="n">
-        <v>-74.90000000000001</v>
+        <v>-31.08</v>
       </c>
       <c r="L23" t="n">
-        <v>110.09</v>
+        <v>128.72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:11:07</t>
+          <t>05:08:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.58</v>
+        <v>2.04</v>
       </c>
       <c r="F24" t="n">
-        <v>2.33</v>
+        <v>3.46</v>
       </c>
       <c r="G24" t="n">
-        <v>258.1</v>
+        <v>271.5</v>
       </c>
       <c r="H24" t="n">
-        <v>84.59999999999999</v>
+        <v>50.9</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>-77.41</v>
+        <v>80.45</v>
       </c>
       <c r="K24" t="n">
-        <v>75.22</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>107.93</v>
+        <v>109.77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:12:59</t>
+          <t>05:10:43</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.22</v>
+        <v>1.55</v>
       </c>
       <c r="F25" t="n">
-        <v>6.82</v>
+        <v>6.4</v>
       </c>
       <c r="G25" t="n">
-        <v>274.4</v>
+        <v>260.8</v>
       </c>
       <c r="H25" t="n">
-        <v>67.7</v>
+        <v>47.3</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-39.59</v>
+        <v>61.68</v>
       </c>
       <c r="K25" t="n">
-        <v>103.28</v>
+        <v>100.13</v>
       </c>
       <c r="L25" t="n">
-        <v>110.61</v>
+        <v>117.61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:18:29</t>
+          <t>05:15:46</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="F26" t="n">
-        <v>8.890000000000001</v>
+        <v>5.64</v>
       </c>
       <c r="G26" t="n">
-        <v>258.6</v>
+        <v>274.3</v>
       </c>
       <c r="H26" t="n">
-        <v>28.5</v>
+        <v>56.7</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>118</v>
+        <v>-105</v>
       </c>
       <c r="K26" t="n">
-        <v>-82.36</v>
+        <v>67.19</v>
       </c>
       <c r="L26" t="n">
-        <v>143.9</v>
+        <v>124.66</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:20:03</t>
+          <t>05:16:39</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.21</v>
+        <v>1.92</v>
       </c>
       <c r="F27" t="n">
-        <v>10.4</v>
+        <v>8.33</v>
       </c>
       <c r="G27" t="n">
-        <v>258.6</v>
+        <v>262</v>
       </c>
       <c r="H27" t="n">
-        <v>82.90000000000001</v>
+        <v>66</v>
       </c>
       <c r="I27" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-41.41</v>
+        <v>-0.82</v>
       </c>
       <c r="K27" t="n">
-        <v>-120.09</v>
+        <v>-151.28</v>
       </c>
       <c r="L27" t="n">
-        <v>127.03</v>
+        <v>151.28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:21:20</t>
+          <t>05:19:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.71</v>
+        <v>2.36</v>
       </c>
       <c r="F28" t="n">
-        <v>10.58</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>286.2</v>
+        <v>258.8</v>
       </c>
       <c r="H28" t="n">
-        <v>87.8</v>
+        <v>78.7</v>
       </c>
       <c r="I28" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>-168.83</v>
+        <v>-94.45</v>
       </c>
       <c r="K28" t="n">
-        <v>55.55</v>
+        <v>160.95</v>
       </c>
       <c r="L28" t="n">
-        <v>177.73</v>
+        <v>186.61</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:31:38</t>
+          <t>05:27:57</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.19</v>
+        <v>1.89</v>
       </c>
       <c r="F29" t="n">
-        <v>7.2</v>
+        <v>7.93</v>
       </c>
       <c r="G29" t="n">
-        <v>261.8</v>
+        <v>265</v>
       </c>
       <c r="H29" t="n">
-        <v>56.9</v>
+        <v>80</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J29" t="n">
-        <v>-35.16</v>
+        <v>-24.77</v>
       </c>
       <c r="K29" t="n">
-        <v>2.87</v>
+        <v>-27.33</v>
       </c>
       <c r="L29" t="n">
-        <v>35.27</v>
+        <v>36.89</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:33:01</t>
+          <t>05:30:20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="F30" t="n">
-        <v>8.779999999999999</v>
+        <v>5.73</v>
       </c>
       <c r="G30" t="n">
-        <v>270</v>
+        <v>254.7</v>
       </c>
       <c r="H30" t="n">
-        <v>23.8</v>
+        <v>81.7</v>
       </c>
       <c r="I30" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-26.9</v>
+        <v>10.44</v>
       </c>
       <c r="K30" t="n">
-        <v>-13.14</v>
+        <v>-66.18000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>29.94</v>
+        <v>66.98999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:34:26</t>
+          <t>05:31:09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.22</v>
+        <v>1.64</v>
       </c>
       <c r="F31" t="n">
-        <v>4.97</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>274.8</v>
+        <v>265.9</v>
       </c>
       <c r="H31" t="n">
-        <v>34.6</v>
+        <v>41.4</v>
       </c>
       <c r="I31" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-23.8</v>
+        <v>24.08</v>
       </c>
       <c r="K31" t="n">
-        <v>-34.49</v>
+        <v>-27.29</v>
       </c>
       <c r="L31" t="n">
-        <v>41.91</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:39:20</t>
+          <t>05:36:13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="F32" t="n">
-        <v>4.53</v>
+        <v>7.27</v>
       </c>
       <c r="G32" t="n">
-        <v>272.4</v>
+        <v>264.4</v>
       </c>
       <c r="H32" t="n">
-        <v>52.3</v>
+        <v>13.4</v>
       </c>
       <c r="I32" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-16.48</v>
+        <v>-29.67</v>
       </c>
       <c r="K32" t="n">
-        <v>-53.3</v>
+        <v>-46.78</v>
       </c>
       <c r="L32" t="n">
-        <v>55.79</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:41:08</t>
+          <t>05:38:40</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="F33" t="n">
-        <v>9.92</v>
+        <v>10.32</v>
       </c>
       <c r="G33" t="n">
-        <v>281</v>
+        <v>268.1</v>
       </c>
       <c r="H33" t="n">
-        <v>46.8</v>
+        <v>28.4</v>
       </c>
       <c r="I33" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>35.04</v>
+        <v>-25.85</v>
       </c>
       <c r="K33" t="n">
-        <v>36.45</v>
+        <v>65.44</v>
       </c>
       <c r="L33" t="n">
-        <v>50.56</v>
+        <v>70.36</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:42:38</t>
+          <t>05:40:23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
       <c r="F34" t="n">
-        <v>8.970000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>273</v>
+        <v>258.4</v>
       </c>
       <c r="H34" t="n">
-        <v>66.09999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-18.99</v>
+        <v>-24.19</v>
       </c>
       <c r="K34" t="n">
-        <v>45.14</v>
+        <v>-31.85</v>
       </c>
       <c r="L34" t="n">
-        <v>48.98</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:46:54</t>
+          <t>05:45:45</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.74</v>
+        <v>2.37</v>
       </c>
       <c r="F35" t="n">
-        <v>7.91</v>
+        <v>6.59</v>
       </c>
       <c r="G35" t="n">
-        <v>269.8</v>
+        <v>258.2</v>
       </c>
       <c r="H35" t="n">
-        <v>42.8</v>
+        <v>25.7</v>
       </c>
       <c r="I35" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-58.61</v>
+        <v>47.7</v>
       </c>
       <c r="K35" t="n">
-        <v>14.38</v>
+        <v>-75.40000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>60.35</v>
+        <v>89.22</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:48:55</t>
+          <t>05:47:14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="F36" t="n">
-        <v>8.609999999999999</v>
+        <v>7.45</v>
       </c>
       <c r="G36" t="n">
-        <v>263.1</v>
+        <v>260.6</v>
       </c>
       <c r="H36" t="n">
-        <v>41.8</v>
+        <v>63.2</v>
       </c>
       <c r="I36" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>-65.58</v>
+        <v>17.7</v>
       </c>
       <c r="K36" t="n">
-        <v>9.56</v>
+        <v>-123.22</v>
       </c>
       <c r="L36" t="n">
-        <v>66.27</v>
+        <v>124.49</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:51:00</t>
+          <t>05:49:29</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.18</v>
+        <v>1.52</v>
       </c>
       <c r="F37" t="n">
-        <v>7.95</v>
+        <v>10</v>
       </c>
       <c r="G37" t="n">
-        <v>267.9</v>
+        <v>262.2</v>
       </c>
       <c r="H37" t="n">
-        <v>65.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="I37" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>44.7</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>74.55</v>
+        <v>-83.02</v>
       </c>
       <c r="L37" t="n">
-        <v>86.93000000000001</v>
+        <v>83.55</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:55:19</t>
+          <t>05:53:04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>9.300000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="G38" t="n">
-        <v>273.4</v>
+        <v>266.1</v>
       </c>
       <c r="H38" t="n">
-        <v>73.40000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="I38" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-115.16</v>
+        <v>103.47</v>
       </c>
       <c r="K38" t="n">
-        <v>44.9</v>
+        <v>-19.53</v>
       </c>
       <c r="L38" t="n">
-        <v>123.6</v>
+        <v>105.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:56:16</t>
+          <t>05:54:40</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="F39" t="n">
-        <v>10.56</v>
+        <v>6.4</v>
       </c>
       <c r="G39" t="n">
-        <v>272.9</v>
+        <v>261.1</v>
       </c>
       <c r="H39" t="n">
-        <v>96.2</v>
+        <v>45.1</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>37.06</v>
+        <v>-91.38</v>
       </c>
       <c r="K39" t="n">
-        <v>136.15</v>
+        <v>-41.3</v>
       </c>
       <c r="L39" t="n">
-        <v>141.1</v>
+        <v>100.28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:57:22</t>
+          <t>05:57:17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="F40" t="n">
         <v>10.58</v>
       </c>
       <c r="G40" t="n">
-        <v>265.4</v>
+        <v>258.6</v>
       </c>
       <c r="H40" t="n">
-        <v>61.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>60.17</v>
+        <v>-18.32</v>
       </c>
       <c r="K40" t="n">
-        <v>-143.72</v>
+        <v>-99.40000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>155.81</v>
+        <v>101.08</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:02:44</t>
+          <t>06:02:50</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.44</v>
+        <v>2.79</v>
       </c>
       <c r="F41" t="n">
         <v>10.58</v>
       </c>
       <c r="G41" t="n">
-        <v>279.3</v>
+        <v>269.9</v>
       </c>
       <c r="H41" t="n">
-        <v>49.1</v>
+        <v>96.8</v>
       </c>
       <c r="I41" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>45.31</v>
+        <v>-194.84</v>
       </c>
       <c r="K41" t="n">
-        <v>-156.88</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>163.3</v>
+        <v>195.02</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:04:22</t>
+          <t>06:04:41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="F42" t="n">
-        <v>9.83</v>
+        <v>6.16</v>
       </c>
       <c r="G42" t="n">
-        <v>273.2</v>
+        <v>261.8</v>
       </c>
       <c r="H42" t="n">
-        <v>52.3</v>
+        <v>56.9</v>
       </c>
       <c r="I42" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-124.13</v>
+        <v>-166.89</v>
       </c>
       <c r="K42" t="n">
-        <v>209.56</v>
+        <v>20.45</v>
       </c>
       <c r="L42" t="n">
-        <v>243.56</v>
+        <v>168.14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:06:11</t>
+          <t>06:07:23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="F43" t="n">
-        <v>10.58</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>280.1</v>
+        <v>274.1</v>
       </c>
       <c r="H43" t="n">
-        <v>63.9</v>
+        <v>56.4</v>
       </c>
       <c r="I43" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-143.13</v>
+        <v>123.42</v>
       </c>
       <c r="K43" t="n">
-        <v>-165.26</v>
+        <v>-49.52</v>
       </c>
       <c r="L43" t="n">
-        <v>218.62</v>
+        <v>132.98</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:17:58</t>
+          <t>06:19:30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.35</v>
+        <v>2.01</v>
       </c>
       <c r="F44" t="n">
-        <v>9.32</v>
+        <v>6.22</v>
       </c>
       <c r="G44" t="n">
-        <v>260.3</v>
+        <v>274.8</v>
       </c>
       <c r="H44" t="n">
-        <v>36.7</v>
+        <v>34.6</v>
       </c>
       <c r="I44" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-28.57</v>
+        <v>-15.81</v>
       </c>
       <c r="K44" t="n">
-        <v>-9.77</v>
+        <v>-34.89</v>
       </c>
       <c r="L44" t="n">
-        <v>30.2</v>
+        <v>38.31</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:19:28</t>
+          <t>06:20:22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="F45" t="n">
-        <v>10.58</v>
+        <v>5.06</v>
       </c>
       <c r="G45" t="n">
-        <v>266.6</v>
+        <v>279.9</v>
       </c>
       <c r="H45" t="n">
-        <v>43.2</v>
+        <v>62.4</v>
       </c>
       <c r="I45" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.19</v>
+        <v>-30.28</v>
       </c>
       <c r="K45" t="n">
-        <v>22.43</v>
+        <v>-19.78</v>
       </c>
       <c r="L45" t="n">
-        <v>22.82</v>
+        <v>36.17</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:20:46</t>
+          <t>06:22:38</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="F46" t="n">
-        <v>6.22</v>
+        <v>5.74</v>
       </c>
       <c r="G46" t="n">
-        <v>264.6</v>
+        <v>281</v>
       </c>
       <c r="H46" t="n">
-        <v>64.90000000000001</v>
+        <v>46.8</v>
       </c>
       <c r="I46" t="n">
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-28.93</v>
+        <v>21.74</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.08</v>
+        <v>15.95</v>
       </c>
       <c r="L46" t="n">
-        <v>29</v>
+        <v>26.96</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:25:33</t>
+          <t>06:25:47</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="F47" t="n">
-        <v>6.35</v>
+        <v>9.49</v>
       </c>
       <c r="G47" t="n">
-        <v>265.3</v>
+        <v>244.3</v>
       </c>
       <c r="H47" t="n">
-        <v>24.1</v>
+        <v>64</v>
       </c>
       <c r="I47" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>-40.57</v>
+        <v>40.64</v>
       </c>
       <c r="K47" t="n">
-        <v>-22.22</v>
+        <v>-32.03</v>
       </c>
       <c r="L47" t="n">
-        <v>46.25</v>
+        <v>51.74</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:28:07</t>
+          <t>06:26:50</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.46</v>
+        <v>1.84</v>
       </c>
       <c r="F48" t="n">
-        <v>10.4</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>263</v>
+        <v>269.8</v>
       </c>
       <c r="H48" t="n">
-        <v>50.2</v>
+        <v>42.8</v>
       </c>
       <c r="I48" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>68.09999999999999</v>
+        <v>-18.71</v>
       </c>
       <c r="K48" t="n">
-        <v>6.33</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>68.39</v>
+        <v>20.36</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:29:33</t>
+          <t>06:28:03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="F49" t="n">
-        <v>3.4</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>264.6</v>
+        <v>279.1</v>
       </c>
       <c r="H49" t="n">
-        <v>14.8</v>
+        <v>39.2</v>
       </c>
       <c r="I49" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>43.61</v>
+        <v>22.94</v>
       </c>
       <c r="K49" t="n">
-        <v>-48.6</v>
+        <v>37.75</v>
       </c>
       <c r="L49" t="n">
-        <v>65.29000000000001</v>
+        <v>44.17</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:34:51</t>
+          <t>06:33:26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="F50" t="n">
-        <v>7.76</v>
+        <v>10.58</v>
       </c>
       <c r="G50" t="n">
-        <v>255.2</v>
+        <v>267.9</v>
       </c>
       <c r="H50" t="n">
-        <v>76.59999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>6.26</v>
+        <v>55.66</v>
       </c>
       <c r="K50" t="n">
-        <v>-109.79</v>
+        <v>69.7</v>
       </c>
       <c r="L50" t="n">
-        <v>109.97</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:37:06</t>
+          <t>06:34:44</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="F51" t="n">
-        <v>6.88</v>
+        <v>9.81</v>
       </c>
       <c r="G51" t="n">
-        <v>274.1</v>
+        <v>266.8</v>
       </c>
       <c r="H51" t="n">
-        <v>55.1</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>81.90000000000001</v>
+        <v>-56.2</v>
       </c>
       <c r="K51" t="n">
-        <v>7.84</v>
+        <v>-67.19</v>
       </c>
       <c r="L51" t="n">
-        <v>82.28</v>
+        <v>87.59999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:39:34</t>
+          <t>06:37:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="F52" t="n">
-        <v>9.06</v>
+        <v>10.58</v>
       </c>
       <c r="G52" t="n">
-        <v>261.8</v>
+        <v>272.9</v>
       </c>
       <c r="H52" t="n">
-        <v>66.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="I52" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-79.51000000000001</v>
+        <v>43.17</v>
       </c>
       <c r="K52" t="n">
-        <v>33.9</v>
+        <v>93.58</v>
       </c>
       <c r="L52" t="n">
-        <v>86.44</v>
+        <v>103.06</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:45:29</t>
+          <t>06:43:04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
       <c r="F53" t="n">
-        <v>7.93</v>
+        <v>10.58</v>
       </c>
       <c r="G53" t="n">
-        <v>258.3</v>
+        <v>267.4</v>
       </c>
       <c r="H53" t="n">
-        <v>41.6</v>
+        <v>44.8</v>
       </c>
       <c r="I53" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>54.31</v>
+        <v>74.37</v>
       </c>
       <c r="K53" t="n">
-        <v>-114.39</v>
+        <v>-154.28</v>
       </c>
       <c r="L53" t="n">
-        <v>126.63</v>
+        <v>171.27</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:46:13</t>
+          <t>06:44:12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="F54" t="n">
-        <v>9.69</v>
+        <v>10.58</v>
       </c>
       <c r="G54" t="n">
-        <v>277.4</v>
+        <v>279.3</v>
       </c>
       <c r="H54" t="n">
-        <v>56.2</v>
+        <v>49.1</v>
       </c>
       <c r="I54" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>113.88</v>
+        <v>51.13</v>
       </c>
       <c r="K54" t="n">
-        <v>-76.23</v>
+        <v>-99.63</v>
       </c>
       <c r="L54" t="n">
-        <v>137.04</v>
+        <v>111.98</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:47:51</t>
+          <t>06:45:34</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.47</v>
+        <v>2.64</v>
       </c>
       <c r="F55" t="n">
-        <v>8.16</v>
+        <v>10.38</v>
       </c>
       <c r="G55" t="n">
-        <v>267.5</v>
+        <v>260.6</v>
       </c>
       <c r="H55" t="n">
-        <v>53.8</v>
+        <v>64.3</v>
       </c>
       <c r="I55" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="K55" t="n">
         <v>131.37</v>
       </c>
-      <c r="K55" t="n">
-        <v>43.09</v>
-      </c>
       <c r="L55" t="n">
-        <v>138.26</v>
+        <v>135.93</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:52:47</t>
+          <t>06:50:24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.09</v>
+        <v>2.37</v>
       </c>
       <c r="F56" t="n">
-        <v>5.36</v>
+        <v>10.58</v>
       </c>
       <c r="G56" t="n">
-        <v>256.6</v>
+        <v>280.1</v>
       </c>
       <c r="H56" t="n">
-        <v>55.9</v>
+        <v>63.9</v>
       </c>
       <c r="I56" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J56" t="n">
-        <v>-157.72</v>
+        <v>-124.03</v>
       </c>
       <c r="K56" t="n">
-        <v>3.72</v>
+        <v>-196.7</v>
       </c>
       <c r="L56" t="n">
-        <v>157.77</v>
+        <v>232.54</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:55:04</t>
+          <t>06:51:37</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="F57" t="n">
-        <v>7.26</v>
+        <v>9.77</v>
       </c>
       <c r="G57" t="n">
-        <v>267.9</v>
+        <v>264.9</v>
       </c>
       <c r="H57" t="n">
-        <v>66.90000000000001</v>
+        <v>32.1</v>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-73.05</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>-135.95</v>
+        <v>49.03</v>
       </c>
       <c r="L57" t="n">
-        <v>154.33</v>
+        <v>105.09</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:57:23</t>
+          <t>06:53:53</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.71</v>
+        <v>1.99</v>
       </c>
       <c r="F58" t="n">
-        <v>7.95</v>
+        <v>5.82</v>
       </c>
       <c r="G58" t="n">
-        <v>278.5</v>
+        <v>266.4</v>
       </c>
       <c r="H58" t="n">
-        <v>22.4</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-290</v>
+        <v>-233.02</v>
       </c>
       <c r="K58" t="n">
-        <v>-28.72</v>
+        <v>16.04</v>
       </c>
       <c r="L58" t="n">
-        <v>291.42</v>
+        <v>233.57</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:07:42</t>
+          <t>07:06:35</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.59</v>
+        <v>2.05</v>
       </c>
       <c r="F59" t="n">
-        <v>10.12</v>
+        <v>6.78</v>
       </c>
       <c r="G59" t="n">
-        <v>268.5</v>
+        <v>265.5</v>
       </c>
       <c r="H59" t="n">
-        <v>43.1</v>
+        <v>42.8</v>
       </c>
       <c r="I59" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-12.7</v>
+        <v>2.45</v>
       </c>
       <c r="K59" t="n">
-        <v>40.67</v>
+        <v>34.42</v>
       </c>
       <c r="L59" t="n">
-        <v>42.61</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:10:30</t>
+          <t>07:07:40</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="F60" t="n">
-        <v>8.140000000000001</v>
+        <v>9.84</v>
       </c>
       <c r="G60" t="n">
-        <v>277.7</v>
+        <v>265.3</v>
       </c>
       <c r="H60" t="n">
-        <v>65.09999999999999</v>
+        <v>24.1</v>
       </c>
       <c r="I60" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-35.33</v>
+        <v>-26.24</v>
       </c>
       <c r="K60" t="n">
-        <v>-6.51</v>
+        <v>-17.15</v>
       </c>
       <c r="L60" t="n">
-        <v>35.93</v>
+        <v>31.34</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:12:44</t>
+          <t>07:10:03</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="F61" t="n">
-        <v>8.08</v>
+        <v>10.58</v>
       </c>
       <c r="G61" t="n">
-        <v>258.8</v>
+        <v>269.1</v>
       </c>
       <c r="H61" t="n">
-        <v>60.7</v>
+        <v>39</v>
       </c>
       <c r="I61" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>37.12</v>
+        <v>-31.6</v>
       </c>
       <c r="K61" t="n">
-        <v>4.06</v>
+        <v>16.07</v>
       </c>
       <c r="L61" t="n">
-        <v>37.34</v>
+        <v>35.45</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:18:22</t>
+          <t>07:14:01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.09</v>
+        <v>2.5</v>
       </c>
       <c r="F62" t="n">
         <v>10.58</v>
       </c>
       <c r="G62" t="n">
-        <v>253.3</v>
+        <v>264.6</v>
       </c>
       <c r="H62" t="n">
-        <v>52</v>
+        <v>14.8</v>
       </c>
       <c r="I62" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-15.32</v>
+        <v>51.4</v>
       </c>
       <c r="K62" t="n">
-        <v>-39.01</v>
+        <v>-42.43</v>
       </c>
       <c r="L62" t="n">
-        <v>41.91</v>
+        <v>66.65000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:20:27</t>
+          <t>07:15:50</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="F63" t="n">
-        <v>10.27</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>268.4</v>
+        <v>264.6</v>
       </c>
       <c r="H63" t="n">
-        <v>57.3</v>
+        <v>19.5</v>
       </c>
       <c r="I63" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J63" t="n">
-        <v>30.6</v>
+        <v>16.29</v>
       </c>
       <c r="K63" t="n">
-        <v>-48.3</v>
+        <v>53.01</v>
       </c>
       <c r="L63" t="n">
-        <v>57.17</v>
+        <v>55.46</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:21:09</t>
+          <t>07:18:16</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="F64" t="n">
-        <v>4.72</v>
+        <v>10.58</v>
       </c>
       <c r="G64" t="n">
-        <v>256.5</v>
+        <v>274.1</v>
       </c>
       <c r="H64" t="n">
-        <v>34.3</v>
+        <v>55.1</v>
       </c>
       <c r="I64" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>52.84</v>
+        <v>60.39</v>
       </c>
       <c r="K64" t="n">
-        <v>-26.25</v>
+        <v>4.12</v>
       </c>
       <c r="L64" t="n">
-        <v>59</v>
+        <v>60.54</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:26:49</t>
+          <t>07:23:21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.58</v>
+        <v>2.22</v>
       </c>
       <c r="F65" t="n">
-        <v>9.58</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G65" t="n">
-        <v>267.2</v>
+        <v>268.3</v>
       </c>
       <c r="H65" t="n">
-        <v>40.7</v>
+        <v>36</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>-82.78</v>
+        <v>-61.71</v>
       </c>
       <c r="K65" t="n">
-        <v>-43.59</v>
+        <v>12.39</v>
       </c>
       <c r="L65" t="n">
-        <v>93.56</v>
+        <v>62.94</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:28:03</t>
+          <t>07:25:24</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="F66" t="n">
-        <v>8.77</v>
+        <v>5.64</v>
       </c>
       <c r="G66" t="n">
-        <v>271.9</v>
+        <v>258.3</v>
       </c>
       <c r="H66" t="n">
-        <v>61.7</v>
+        <v>41.6</v>
       </c>
       <c r="I66" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-32.72</v>
+        <v>49.57</v>
       </c>
       <c r="K66" t="n">
-        <v>67.38</v>
+        <v>-67.51000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>74.90000000000001</v>
+        <v>83.75</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:29:59</t>
+          <t>07:27:38</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.72</v>
+        <v>2.14</v>
       </c>
       <c r="F67" t="n">
-        <v>9.869999999999999</v>
+        <v>10.14</v>
       </c>
       <c r="G67" t="n">
-        <v>275.5</v>
+        <v>262.8</v>
       </c>
       <c r="H67" t="n">
-        <v>44.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>77.37</v>
+        <v>72.09</v>
       </c>
       <c r="K67" t="n">
-        <v>6.59</v>
+        <v>-47.99</v>
       </c>
       <c r="L67" t="n">
-        <v>77.65000000000001</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:33:56</t>
+          <t>07:32:30</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.99</v>
+        <v>2.32</v>
       </c>
       <c r="F68" t="n">
         <v>10.58</v>
       </c>
       <c r="G68" t="n">
-        <v>269</v>
+        <v>267.5</v>
       </c>
       <c r="H68" t="n">
-        <v>79.40000000000001</v>
+        <v>53.8</v>
       </c>
       <c r="I68" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>-148.61</v>
+        <v>142.58</v>
       </c>
       <c r="K68" t="n">
-        <v>-36.66</v>
+        <v>38.81</v>
       </c>
       <c r="L68" t="n">
-        <v>153.07</v>
+        <v>147.77</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:35:46</t>
+          <t>07:33:57</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.37</v>
+        <v>2.16</v>
       </c>
       <c r="F69" t="n">
-        <v>10.58</v>
+        <v>5.82</v>
       </c>
       <c r="G69" t="n">
-        <v>273.3</v>
+        <v>266.5</v>
       </c>
       <c r="H69" t="n">
-        <v>62.1</v>
+        <v>22.9</v>
       </c>
       <c r="I69" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-102.96</v>
+        <v>132.25</v>
       </c>
       <c r="K69" t="n">
-        <v>-120.68</v>
+        <v>-28.49</v>
       </c>
       <c r="L69" t="n">
-        <v>158.63</v>
+        <v>135.28</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:38:11</t>
+          <t>07:34:35</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="F70" t="n">
-        <v>10.03</v>
+        <v>10.14</v>
       </c>
       <c r="G70" t="n">
-        <v>269.9</v>
+        <v>268.5</v>
       </c>
       <c r="H70" t="n">
-        <v>31.3</v>
+        <v>51.2</v>
       </c>
       <c r="I70" t="n">
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-114.71</v>
+        <v>109.1</v>
       </c>
       <c r="K70" t="n">
-        <v>-31.35</v>
+        <v>-32.06</v>
       </c>
       <c r="L70" t="n">
-        <v>118.92</v>
+        <v>113.71</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:41:22</t>
+          <t>07:39:46</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.81</v>
+        <v>1.89</v>
       </c>
       <c r="F71" t="n">
-        <v>10.58</v>
+        <v>4.43</v>
       </c>
       <c r="G71" t="n">
-        <v>267.1</v>
+        <v>264.7</v>
       </c>
       <c r="H71" t="n">
-        <v>33.9</v>
+        <v>37.4</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>125.73</v>
+        <v>-109.89</v>
       </c>
       <c r="K71" t="n">
-        <v>-117.26</v>
+        <v>-149.15</v>
       </c>
       <c r="L71" t="n">
-        <v>171.92</v>
+        <v>185.26</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:42:42</t>
+          <t>07:42:01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.34</v>
+        <v>3.55</v>
       </c>
       <c r="F72" t="n">
         <v>10.58</v>
       </c>
       <c r="G72" t="n">
-        <v>249.4</v>
+        <v>263.1</v>
       </c>
       <c r="H72" t="n">
-        <v>31.4</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-52.38</v>
+        <v>263.37</v>
       </c>
       <c r="K72" t="n">
-        <v>-145.02</v>
+        <v>-105.1</v>
       </c>
       <c r="L72" t="n">
-        <v>154.19</v>
+        <v>283.56</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:43:26</t>
+          <t>07:44:23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.51</v>
+        <v>2.78</v>
       </c>
       <c r="F73" t="n">
-        <v>7.14</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>276.4</v>
+        <v>264.4</v>
       </c>
       <c r="H73" t="n">
-        <v>67.8</v>
+        <v>47</v>
       </c>
       <c r="I73" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>70.54000000000001</v>
+        <v>142.12</v>
       </c>
       <c r="K73" t="n">
-        <v>99.23</v>
+        <v>-9.5</v>
       </c>
       <c r="L73" t="n">
-        <v>121.75</v>
+        <v>142.44</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:55:10</t>
+          <t>07:51:42</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="F74" t="n">
         <v>10.58</v>
       </c>
       <c r="G74" t="n">
-        <v>274.5</v>
+        <v>259.2</v>
       </c>
       <c r="H74" t="n">
-        <v>54.6</v>
+        <v>48.7</v>
       </c>
       <c r="I74" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J74" t="n">
-        <v>40.16</v>
+        <v>14.24</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.87</v>
+        <v>-28</v>
       </c>
       <c r="L74" t="n">
-        <v>40.35</v>
+        <v>31.42</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:56:25</t>
+          <t>07:54:10</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.78</v>
+        <v>1.9</v>
       </c>
       <c r="F75" t="n">
-        <v>10.58</v>
+        <v>5.45</v>
       </c>
       <c r="G75" t="n">
-        <v>274.6</v>
+        <v>276.8</v>
       </c>
       <c r="H75" t="n">
-        <v>26.2</v>
+        <v>15.1</v>
       </c>
       <c r="I75" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-28.28</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>-30.46</v>
+        <v>36.35</v>
       </c>
       <c r="L75" t="n">
-        <v>41.56</v>
+        <v>37.42</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:57:24</t>
+          <t>07:55:50</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="F76" t="n">
-        <v>7.94</v>
+        <v>8.02</v>
       </c>
       <c r="G76" t="n">
-        <v>260.1</v>
+        <v>266.3</v>
       </c>
       <c r="H76" t="n">
-        <v>53.1</v>
+        <v>47.6</v>
       </c>
       <c r="I76" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>21.6</v>
+        <v>39.59</v>
       </c>
       <c r="K76" t="n">
-        <v>-22.99</v>
+        <v>-10.8</v>
       </c>
       <c r="L76" t="n">
-        <v>31.54</v>
+        <v>41.03</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:03:19</t>
+          <t>08:01:16</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="F77" t="n">
-        <v>10.51</v>
+        <v>8.93</v>
       </c>
       <c r="G77" t="n">
-        <v>259.5</v>
+        <v>271.2</v>
       </c>
       <c r="H77" t="n">
-        <v>67.8</v>
+        <v>86.8</v>
       </c>
       <c r="I77" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>7.63</v>
+        <v>-28.02</v>
       </c>
       <c r="K77" t="n">
-        <v>-37.38</v>
+        <v>-59.27</v>
       </c>
       <c r="L77" t="n">
-        <v>38.15</v>
+        <v>65.56</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:04:15</t>
+          <t>08:03:02</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="F78" t="n">
-        <v>7.35</v>
+        <v>7.57</v>
       </c>
       <c r="G78" t="n">
-        <v>256.9</v>
+        <v>259.3</v>
       </c>
       <c r="H78" t="n">
-        <v>54.8</v>
+        <v>58</v>
       </c>
       <c r="I78" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>17.19</v>
+        <v>-19.12</v>
       </c>
       <c r="K78" t="n">
-        <v>102.44</v>
+        <v>-51.16</v>
       </c>
       <c r="L78" t="n">
-        <v>103.87</v>
+        <v>54.62</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:06:23</t>
+          <t>08:05:06</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.64</v>
+        <v>2.36</v>
       </c>
       <c r="F79" t="n">
         <v>10.58</v>
       </c>
       <c r="G79" t="n">
-        <v>271.1</v>
+        <v>262.7</v>
       </c>
       <c r="H79" t="n">
-        <v>39.3</v>
+        <v>23.6</v>
       </c>
       <c r="I79" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>48.83</v>
+        <v>64.3</v>
       </c>
       <c r="K79" t="n">
-        <v>-28.03</v>
+        <v>-2.62</v>
       </c>
       <c r="L79" t="n">
-        <v>56.3</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:11:43</t>
+          <t>08:09:49</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.52</v>
+        <v>2.87</v>
       </c>
       <c r="F80" t="n">
         <v>10.58</v>
       </c>
       <c r="G80" t="n">
-        <v>278.1</v>
+        <v>251.5</v>
       </c>
       <c r="H80" t="n">
-        <v>17.4</v>
+        <v>63.8</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>71.61</v>
+        <v>69.86</v>
       </c>
       <c r="K80" t="n">
-        <v>-38.79</v>
+        <v>-29.62</v>
       </c>
       <c r="L80" t="n">
-        <v>81.44</v>
+        <v>75.88</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:13:18</t>
+          <t>08:10:58</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.27</v>
+        <v>2.69</v>
       </c>
       <c r="F81" t="n">
         <v>10.58</v>
       </c>
       <c r="G81" t="n">
-        <v>260.9</v>
+        <v>271.6</v>
       </c>
       <c r="H81" t="n">
-        <v>45.4</v>
+        <v>44.8</v>
       </c>
       <c r="I81" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-85.05</v>
+        <v>-106.57</v>
       </c>
       <c r="K81" t="n">
-        <v>22.49</v>
+        <v>4.51</v>
       </c>
       <c r="L81" t="n">
-        <v>87.97</v>
+        <v>106.67</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:14:49</t>
+          <t>08:12:46</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="F82" t="n">
-        <v>8.16</v>
+        <v>10.32</v>
       </c>
       <c r="G82" t="n">
-        <v>266.5</v>
+        <v>262.4</v>
       </c>
       <c r="H82" t="n">
-        <v>28.3</v>
+        <v>26.9</v>
       </c>
       <c r="I82" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>56.91</v>
+        <v>-36.96</v>
       </c>
       <c r="K82" t="n">
-        <v>54.19</v>
+        <v>-105.79</v>
       </c>
       <c r="L82" t="n">
-        <v>78.59</v>
+        <v>112.07</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:20:17</t>
+          <t>08:17:01</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="F83" t="n">
-        <v>6.56</v>
+        <v>10.43</v>
       </c>
       <c r="G83" t="n">
-        <v>276.3</v>
+        <v>260.8</v>
       </c>
       <c r="H83" t="n">
-        <v>50.2</v>
+        <v>56.1</v>
       </c>
       <c r="I83" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>-87.11</v>
+        <v>72.94</v>
       </c>
       <c r="K83" t="n">
-        <v>-60.22</v>
+        <v>41.12</v>
       </c>
       <c r="L83" t="n">
-        <v>105.9</v>
+        <v>83.73</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:22:46</t>
+          <t>08:19:49</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="F84" t="n">
-        <v>7.84</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G84" t="n">
-        <v>258.5</v>
+        <v>267.1</v>
       </c>
       <c r="H84" t="n">
-        <v>60.4</v>
+        <v>33.9</v>
       </c>
       <c r="I84" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>25.21</v>
+        <v>118.5</v>
       </c>
       <c r="K84" t="n">
-        <v>-111.82</v>
+        <v>-80.23999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>114.62</v>
+        <v>143.11</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:24:43</t>
+          <t>08:21:42</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F85" t="n">
         <v>10.58</v>
       </c>
       <c r="G85" t="n">
-        <v>259.4</v>
+        <v>260.5</v>
       </c>
       <c r="H85" t="n">
-        <v>37.1</v>
+        <v>5</v>
       </c>
       <c r="I85" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-109.35</v>
+        <v>60.63</v>
       </c>
       <c r="K85" t="n">
-        <v>91.16</v>
+        <v>-87.53</v>
       </c>
       <c r="L85" t="n">
-        <v>142.36</v>
+        <v>106.48</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:28:31</t>
+          <t>08:27:11</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="F86" t="n">
         <v>10.58</v>
       </c>
       <c r="G86" t="n">
-        <v>261.8</v>
+        <v>276.4</v>
       </c>
       <c r="H86" t="n">
-        <v>33.9</v>
+        <v>67.8</v>
       </c>
       <c r="I86" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-163.99</v>
+        <v>102.01</v>
       </c>
       <c r="K86" t="n">
-        <v>-22.32</v>
+        <v>102.53</v>
       </c>
       <c r="L86" t="n">
-        <v>165.5</v>
+        <v>144.64</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:29:18</t>
+          <t>08:28:46</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="F87" t="n">
-        <v>10.05</v>
+        <v>10.58</v>
       </c>
       <c r="G87" t="n">
-        <v>278.4</v>
+        <v>253.9</v>
       </c>
       <c r="H87" t="n">
-        <v>68.3</v>
+        <v>67.7</v>
       </c>
       <c r="I87" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-47.71</v>
+        <v>-29.34</v>
       </c>
       <c r="K87" t="n">
-        <v>-112.7</v>
+        <v>-124.37</v>
       </c>
       <c r="L87" t="n">
-        <v>122.38</v>
+        <v>127.78</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:31:38</t>
+          <t>08:30:02</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.89</v>
+        <v>2.28</v>
       </c>
       <c r="F88" t="n">
         <v>10.58</v>
       </c>
       <c r="G88" t="n">
-        <v>271.6</v>
+        <v>274.6</v>
       </c>
       <c r="H88" t="n">
-        <v>29.1</v>
+        <v>26.2</v>
       </c>
       <c r="I88" t="n">
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-131.1</v>
+        <v>-93.7</v>
       </c>
       <c r="K88" t="n">
-        <v>-4.9</v>
+        <v>-156.98</v>
       </c>
       <c r="L88" t="n">
-        <v>131.2</v>
+        <v>182.82</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-09.xlsx
+++ b/output/2024-07-09.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-16.05</v>
+        <v>-15.9</v>
       </c>
       <c r="K14" t="n">
-        <v>-41.78</v>
+        <v>-41.4</v>
       </c>
       <c r="L14" t="n">
-        <v>44.76</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>24.28</v>
+        <v>27.11</v>
       </c>
       <c r="K15" t="n">
-        <v>-21.16</v>
+        <v>-23.63</v>
       </c>
       <c r="L15" t="n">
-        <v>32.21</v>
+        <v>35.96</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>18.15</v>
+        <v>19.53</v>
       </c>
       <c r="K16" t="n">
-        <v>-25.64</v>
+        <v>-27.59</v>
       </c>
       <c r="L16" t="n">
-        <v>31.41</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>33.49</v>
+        <v>37.2</v>
       </c>
       <c r="K17" t="n">
-        <v>-28.73</v>
+        <v>-31.91</v>
       </c>
       <c r="L17" t="n">
-        <v>44.13</v>
+        <v>49.01</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-23.54</v>
+        <v>-23.88</v>
       </c>
       <c r="K18" t="n">
-        <v>62.34</v>
+        <v>63.24</v>
       </c>
       <c r="L18" t="n">
-        <v>66.64</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>12.58</v>
+        <v>12.32</v>
       </c>
       <c r="K19" t="n">
-        <v>-87.41</v>
+        <v>-85.61</v>
       </c>
       <c r="L19" t="n">
-        <v>88.31</v>
+        <v>86.48999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-74.65000000000001</v>
+        <v>-82.68000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>20.45</v>
+        <v>22.65</v>
       </c>
       <c r="L20" t="n">
-        <v>77.40000000000001</v>
+        <v>85.73</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>68.29000000000001</v>
+        <v>76.23</v>
       </c>
       <c r="K21" t="n">
-        <v>2.32</v>
+        <v>2.59</v>
       </c>
       <c r="L21" t="n">
-        <v>68.33</v>
+        <v>76.27</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>70.45</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-27.36</v>
+        <v>-30.87</v>
       </c>
       <c r="L22" t="n">
-        <v>75.58</v>
+        <v>85.27</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>-9.34</v>
+        <v>-11.35</v>
       </c>
       <c r="K23" t="n">
-        <v>-83.48</v>
+        <v>-101.5</v>
       </c>
       <c r="L23" t="n">
-        <v>84</v>
+        <v>102.14</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>34.23</v>
+        <v>40.25</v>
       </c>
       <c r="K24" t="n">
-        <v>-88.01000000000001</v>
+        <v>-103.48</v>
       </c>
       <c r="L24" t="n">
-        <v>94.44</v>
+        <v>111.03</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>104.06</v>
+        <v>121.44</v>
       </c>
       <c r="K25" t="n">
-        <v>3.23</v>
+        <v>3.77</v>
       </c>
       <c r="L25" t="n">
-        <v>104.11</v>
+        <v>121.5</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="J26" t="n">
-        <v>-119.4</v>
+        <v>-141.42</v>
       </c>
       <c r="K26" t="n">
-        <v>-90.48</v>
+        <v>-107.17</v>
       </c>
       <c r="L26" t="n">
-        <v>149.81</v>
+        <v>177.44</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-96.22</v>
+        <v>-125.28</v>
       </c>
       <c r="K27" t="n">
-        <v>61.55</v>
+        <v>80.14</v>
       </c>
       <c r="L27" t="n">
-        <v>114.23</v>
+        <v>148.72</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>-73.05</v>
+        <v>-94.83</v>
       </c>
       <c r="K28" t="n">
-        <v>80.14</v>
+        <v>104.02</v>
       </c>
       <c r="L28" t="n">
-        <v>108.44</v>
+        <v>140.76</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>-15.89</v>
+        <v>-16.05</v>
       </c>
       <c r="K29" t="n">
-        <v>50.24</v>
+        <v>50.76</v>
       </c>
       <c r="L29" t="n">
-        <v>52.69</v>
+        <v>53.23</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-39.78</v>
+        <v>-41.74</v>
       </c>
       <c r="K30" t="n">
-        <v>25.39</v>
+        <v>26.65</v>
       </c>
       <c r="L30" t="n">
-        <v>47.19</v>
+        <v>49.52</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-28.27</v>
+        <v>-31.6</v>
       </c>
       <c r="K31" t="n">
-        <v>-13.37</v>
+        <v>-14.95</v>
       </c>
       <c r="L31" t="n">
-        <v>31.27</v>
+        <v>34.96</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>61.31</v>
+        <v>62.72</v>
       </c>
       <c r="K32" t="n">
-        <v>-34.28</v>
+        <v>-35.07</v>
       </c>
       <c r="L32" t="n">
-        <v>70.25</v>
+        <v>71.86</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-6.1</v>
+        <v>-6.31</v>
       </c>
       <c r="K33" t="n">
-        <v>57.29</v>
+        <v>59.33</v>
       </c>
       <c r="L33" t="n">
-        <v>57.62</v>
+        <v>59.66</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>39.29</v>
+        <v>43.46</v>
       </c>
       <c r="K34" t="n">
-        <v>27.15</v>
+        <v>30.02</v>
       </c>
       <c r="L34" t="n">
-        <v>47.76</v>
+        <v>52.82</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>15.79</v>
+        <v>17.12</v>
       </c>
       <c r="K35" t="n">
-        <v>-100.73</v>
+        <v>-109.17</v>
       </c>
       <c r="L35" t="n">
-        <v>101.96</v>
+        <v>110.51</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>-18.14</v>
+        <v>-18.7</v>
       </c>
       <c r="K36" t="n">
-        <v>102.09</v>
+        <v>105.21</v>
       </c>
       <c r="L36" t="n">
-        <v>103.68</v>
+        <v>106.85</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>8.119999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>-74.95999999999999</v>
+        <v>-85.68000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>75.39</v>
+        <v>86.18000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>48.76</v>
+        <v>51.53</v>
       </c>
       <c r="K38" t="n">
-        <v>-121.95</v>
+        <v>-128.87</v>
       </c>
       <c r="L38" t="n">
-        <v>131.34</v>
+        <v>138.79</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>30</v>
       </c>
       <c r="J39" t="n">
-        <v>-102.96</v>
+        <v>-115.94</v>
       </c>
       <c r="K39" t="n">
-        <v>28.39</v>
+        <v>31.97</v>
       </c>
       <c r="L39" t="n">
-        <v>106.8</v>
+        <v>120.27</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>30</v>
       </c>
       <c r="J40" t="n">
-        <v>-61.86</v>
+        <v>-73.36</v>
       </c>
       <c r="K40" t="n">
-        <v>92.08</v>
+        <v>109.2</v>
       </c>
       <c r="L40" t="n">
-        <v>110.93</v>
+        <v>131.56</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-30.43</v>
+        <v>-35.67</v>
       </c>
       <c r="K41" t="n">
-        <v>177.51</v>
+        <v>208.09</v>
       </c>
       <c r="L41" t="n">
-        <v>180.1</v>
+        <v>211.13</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>30</v>
       </c>
       <c r="J42" t="n">
-        <v>148.68</v>
+        <v>178.55</v>
       </c>
       <c r="K42" t="n">
-        <v>23.84</v>
+        <v>28.63</v>
       </c>
       <c r="L42" t="n">
-        <v>150.58</v>
+        <v>180.83</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-176.48</v>
+        <v>-209.27</v>
       </c>
       <c r="K43" t="n">
-        <v>45.21</v>
+        <v>53.61</v>
       </c>
       <c r="L43" t="n">
-        <v>182.18</v>
+        <v>216.03</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-40.64</v>
+        <v>-40.73</v>
       </c>
       <c r="K44" t="n">
-        <v>42.97</v>
+        <v>43.08</v>
       </c>
       <c r="L44" t="n">
-        <v>59.15</v>
+        <v>59.29</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>30</v>
       </c>
       <c r="J45" t="n">
-        <v>-30.64</v>
+        <v>-32.91</v>
       </c>
       <c r="K45" t="n">
-        <v>-24.11</v>
+        <v>-25.89</v>
       </c>
       <c r="L45" t="n">
-        <v>38.99</v>
+        <v>41.87</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>16.69</v>
+        <v>17.85</v>
       </c>
       <c r="K46" t="n">
-        <v>-45.06</v>
+        <v>-48.19</v>
       </c>
       <c r="L46" t="n">
-        <v>48.05</v>
+        <v>51.39</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>-53.91</v>
+        <v>-55.28</v>
       </c>
       <c r="K47" t="n">
-        <v>-33.92</v>
+        <v>-34.78</v>
       </c>
       <c r="L47" t="n">
-        <v>63.69</v>
+        <v>65.31</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-19.09</v>
+        <v>-21.93</v>
       </c>
       <c r="K48" t="n">
-        <v>-38.1</v>
+        <v>-43.77</v>
       </c>
       <c r="L48" t="n">
-        <v>42.62</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>-54.06</v>
+        <v>-57.67</v>
       </c>
       <c r="K49" t="n">
-        <v>9.48</v>
+        <v>10.12</v>
       </c>
       <c r="L49" t="n">
-        <v>54.88</v>
+        <v>58.55</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>29</v>
       </c>
       <c r="J50" t="n">
-        <v>39.06</v>
+        <v>44.63</v>
       </c>
       <c r="K50" t="n">
-        <v>66.06</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>76.75</v>
+        <v>87.69</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>34.65</v>
+        <v>39.31</v>
       </c>
       <c r="K51" t="n">
-        <v>-85.34999999999999</v>
+        <v>-96.81999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>92.12</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>27</v>
       </c>
       <c r="J52" t="n">
-        <v>71.76000000000001</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>20.45</v>
+        <v>23.94</v>
       </c>
       <c r="L52" t="n">
-        <v>74.61</v>
+        <v>87.34</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>29</v>
       </c>
       <c r="J53" t="n">
-        <v>93.16</v>
+        <v>108.5</v>
       </c>
       <c r="K53" t="n">
-        <v>-18.01</v>
+        <v>-20.97</v>
       </c>
       <c r="L53" t="n">
-        <v>94.89</v>
+        <v>110.51</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>2.96</v>
+        <v>3.27</v>
       </c>
       <c r="K54" t="n">
-        <v>-144.31</v>
+        <v>-159.5</v>
       </c>
       <c r="L54" t="n">
-        <v>144.34</v>
+        <v>159.53</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>30</v>
       </c>
       <c r="J55" t="n">
-        <v>116.43</v>
+        <v>121.88</v>
       </c>
       <c r="K55" t="n">
-        <v>90.33</v>
+        <v>94.56</v>
       </c>
       <c r="L55" t="n">
-        <v>147.36</v>
+        <v>154.26</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>-40.94</v>
+        <v>-49.7</v>
       </c>
       <c r="K56" t="n">
-        <v>-170.95</v>
+        <v>-207.53</v>
       </c>
       <c r="L56" t="n">
-        <v>175.79</v>
+        <v>213.4</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-15.05</v>
+        <v>-19.54</v>
       </c>
       <c r="K57" t="n">
-        <v>-126.36</v>
+        <v>-164.12</v>
       </c>
       <c r="L57" t="n">
-        <v>127.26</v>
+        <v>165.28</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>30</v>
       </c>
       <c r="J58" t="n">
-        <v>28.6</v>
+        <v>34.12</v>
       </c>
       <c r="K58" t="n">
-        <v>168.36</v>
+        <v>200.87</v>
       </c>
       <c r="L58" t="n">
-        <v>170.77</v>
+        <v>203.74</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-33.75</v>
+        <v>-35.06</v>
       </c>
       <c r="K59" t="n">
-        <v>-39.91</v>
+        <v>-41.47</v>
       </c>
       <c r="L59" t="n">
-        <v>52.26</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>-43.33</v>
+        <v>-41.9</v>
       </c>
       <c r="K60" t="n">
-        <v>48.57</v>
+        <v>46.96</v>
       </c>
       <c r="L60" t="n">
-        <v>65.09</v>
+        <v>62.93</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>72.12</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>-27.83</v>
+        <v>-26.67</v>
       </c>
       <c r="L61" t="n">
-        <v>77.3</v>
+        <v>74.06999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>-41.34</v>
+        <v>-46.47</v>
       </c>
       <c r="K62" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="L62" t="n">
-        <v>41.36</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-51.26</v>
+        <v>-53.92</v>
       </c>
       <c r="K63" t="n">
-        <v>-63.33</v>
+        <v>-66.62</v>
       </c>
       <c r="L63" t="n">
-        <v>81.48</v>
+        <v>85.70999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-25.08</v>
+        <v>-26.3</v>
       </c>
       <c r="K64" t="n">
-        <v>59.46</v>
+        <v>62.37</v>
       </c>
       <c r="L64" t="n">
-        <v>64.53</v>
+        <v>67.69</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>87.84</v>
+        <v>97.41</v>
       </c>
       <c r="K65" t="n">
-        <v>-50.01</v>
+        <v>-55.46</v>
       </c>
       <c r="L65" t="n">
-        <v>101.07</v>
+        <v>112.09</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>63.05</v>
+        <v>76.02</v>
       </c>
       <c r="K66" t="n">
-        <v>-31.74</v>
+        <v>-38.27</v>
       </c>
       <c r="L66" t="n">
-        <v>70.59</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>30</v>
       </c>
       <c r="J67" t="n">
-        <v>55.43</v>
+        <v>67.63</v>
       </c>
       <c r="K67" t="n">
-        <v>19.46</v>
+        <v>23.75</v>
       </c>
       <c r="L67" t="n">
-        <v>58.75</v>
+        <v>71.68000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-137.81</v>
+        <v>-149.9</v>
       </c>
       <c r="K68" t="n">
-        <v>-61.19</v>
+        <v>-66.56</v>
       </c>
       <c r="L68" t="n">
-        <v>150.78</v>
+        <v>164.01</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>-80.08</v>
+        <v>-88.55</v>
       </c>
       <c r="K69" t="n">
-        <v>74.03</v>
+        <v>81.86</v>
       </c>
       <c r="L69" t="n">
-        <v>109.06</v>
+        <v>120.59</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>29</v>
       </c>
       <c r="J70" t="n">
-        <v>34.02</v>
+        <v>41.14</v>
       </c>
       <c r="K70" t="n">
-        <v>-94.20999999999999</v>
+        <v>-113.9</v>
       </c>
       <c r="L70" t="n">
-        <v>100.16</v>
+        <v>121.1</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>-140.95</v>
+        <v>-168.18</v>
       </c>
       <c r="K71" t="n">
-        <v>-72.28</v>
+        <v>-86.23999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>158.41</v>
+        <v>189</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>12.62</v>
+        <v>15.84</v>
       </c>
       <c r="K72" t="n">
-        <v>-149.4</v>
+        <v>-187.53</v>
       </c>
       <c r="L72" t="n">
-        <v>149.93</v>
+        <v>188.2</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>-36.49</v>
+        <v>-44.86</v>
       </c>
       <c r="K73" t="n">
-        <v>136.71</v>
+        <v>168.09</v>
       </c>
       <c r="L73" t="n">
-        <v>141.49</v>
+        <v>173.98</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>33.44</v>
+        <v>33.49</v>
       </c>
       <c r="K74" t="n">
-        <v>-36.53</v>
+        <v>-36.59</v>
       </c>
       <c r="L74" t="n">
-        <v>49.53</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>29</v>
       </c>
       <c r="J75" t="n">
-        <v>-30.08</v>
+        <v>-31.46</v>
       </c>
       <c r="K75" t="n">
-        <v>-14</v>
+        <v>-14.64</v>
       </c>
       <c r="L75" t="n">
-        <v>33.18</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>-45.08</v>
+        <v>-41.98</v>
       </c>
       <c r="K76" t="n">
-        <v>-37.18</v>
+        <v>-34.62</v>
       </c>
       <c r="L76" t="n">
-        <v>58.44</v>
+        <v>54.42</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>32.98</v>
+        <v>35.89</v>
       </c>
       <c r="K77" t="n">
-        <v>-56.29</v>
+        <v>-61.26</v>
       </c>
       <c r="L77" t="n">
-        <v>65.23999999999999</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>70.61</v>
+        <v>72.09</v>
       </c>
       <c r="K78" t="n">
-        <v>-41.04</v>
+        <v>-41.9</v>
       </c>
       <c r="L78" t="n">
-        <v>81.67</v>
+        <v>83.38</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-13.03</v>
+        <v>-14.39</v>
       </c>
       <c r="K79" t="n">
-        <v>-48.94</v>
+        <v>-54.05</v>
       </c>
       <c r="L79" t="n">
-        <v>50.65</v>
+        <v>55.94</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>57.98</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>-20.13</v>
+        <v>-24.45</v>
       </c>
       <c r="L80" t="n">
-        <v>61.38</v>
+        <v>74.55</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>8.279999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>-74.17</v>
+        <v>-84.01000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>74.63</v>
+        <v>84.53</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>11.51</v>
+        <v>13.77</v>
       </c>
       <c r="K82" t="n">
-        <v>-58.64</v>
+        <v>-70.18000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>59.75</v>
+        <v>71.52</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-84.03</v>
+        <v>-101.15</v>
       </c>
       <c r="K83" t="n">
-        <v>-31.39</v>
+        <v>-37.78</v>
       </c>
       <c r="L83" t="n">
-        <v>89.7</v>
+        <v>107.98</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>139.12</v>
+        <v>152.81</v>
       </c>
       <c r="K84" t="n">
-        <v>-66.56</v>
+        <v>-73.11</v>
       </c>
       <c r="L84" t="n">
-        <v>154.22</v>
+        <v>169.4</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>30</v>
       </c>
       <c r="J85" t="n">
-        <v>-31.95</v>
+        <v>-40.58</v>
       </c>
       <c r="K85" t="n">
-        <v>-70.92</v>
+        <v>-90.06</v>
       </c>
       <c r="L85" t="n">
-        <v>77.79000000000001</v>
+        <v>98.78</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-134.2</v>
+        <v>-168.02</v>
       </c>
       <c r="K86" t="n">
-        <v>-2.96</v>
+        <v>-3.7</v>
       </c>
       <c r="L86" t="n">
-        <v>134.23</v>
+        <v>168.06</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>18.89</v>
+        <v>22.75</v>
       </c>
       <c r="K87" t="n">
-        <v>127.21</v>
+        <v>153.26</v>
       </c>
       <c r="L87" t="n">
-        <v>128.61</v>
+        <v>154.94</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>-27.69</v>
+        <v>-32.21</v>
       </c>
       <c r="K88" t="n">
-        <v>172.26</v>
+        <v>200.38</v>
       </c>
       <c r="L88" t="n">
-        <v>174.47</v>
+        <v>202.95</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-09.xlsx
+++ b/output/2024-07-09.xlsx
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-53.92</v>
+        <v>-55.14</v>
       </c>
       <c r="K63" t="n">
-        <v>-66.62</v>
+        <v>-68.13</v>
       </c>
       <c r="L63" t="n">
-        <v>85.70999999999999</v>
+        <v>87.65000000000001</v>
       </c>
     </row>
     <row r="64">
